--- a/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
+++ b/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Personal" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'1. Inversion Inicial'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2. P&amp;L 3 Anos'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'3. Punto Equilibrio'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'4. Escenarios'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'5. Personal'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -120,7 +126,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -142,11 +148,55 @@
         <color rgb="00D4D0C8"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D4D0C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D4D0C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D4D0C8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D4D0C8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D4D0C8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -221,6 +271,8 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -584,7 +636,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -615,6 +667,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -638,6 +691,8 @@
           <t>LOCAL Y ACONDICIONAMIENTO</t>
         </is>
       </c>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="29" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -731,6 +786,8 @@
           <t>EQUIPAMIENTO COCINA</t>
         </is>
       </c>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="29" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
@@ -884,6 +941,8 @@
           <t>EQUIPAMIENTO SALA Y BARRA</t>
         </is>
       </c>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="29" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
@@ -1022,6 +1081,8 @@
           <t>MARKETING Y LANZAMIENTO</t>
         </is>
       </c>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="29" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
@@ -1074,6 +1135,8 @@
           <t>GASTOS LEGALES Y CONSTITUCION</t>
         </is>
       </c>
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="29" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
@@ -1137,6 +1200,8 @@
           <t>FONDO DE MANIOBRA (3 meses operaciones)</t>
         </is>
       </c>
+      <c r="B43" s="28" t="n"/>
+      <c r="C43" s="29" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
@@ -1153,6 +1218,7 @@
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
@@ -1168,6 +1234,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
@@ -1184,19 +1251,28 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A46"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A13:C13"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A34:C34"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A46"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1204,7 +1280,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1236,6 +1312,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1264,6 +1341,9 @@
           <t>INGRESOS</t>
         </is>
       </c>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="28" t="n"/>
+      <c r="D6" s="29" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -1335,6 +1415,9 @@
           <t>COSTES VARIABLES</t>
         </is>
       </c>
+      <c r="B11" s="28" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="29" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
@@ -1438,6 +1521,9 @@
           <t>COSTES FIJOS</t>
         </is>
       </c>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="29" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
@@ -1631,6 +1717,7 @@
         <v>215127.5</v>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="15" t="inlineStr">
         <is>
@@ -1679,12 +1766,16 @@
         <v>39514.96875</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="24" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>RATIOS CLAVE</t>
         </is>
       </c>
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="28" t="n"/>
+      <c r="D36" s="29" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
@@ -1750,6 +1841,7 @@
         <v>0.08290578284815106</v>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
@@ -1759,16 +1851,25 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A18:D18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1776,7 +1877,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1807,6 +1908,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -1830,6 +1932,8 @@
           <t>DATOS BASE (Ano 1)</t>
         </is>
       </c>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="29" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
@@ -1898,12 +2002,15 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
           <t>PUNTO DE EQUILIBRIO</t>
         </is>
       </c>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="29" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="13" t="inlineStr">
@@ -1914,9 +2021,10 @@
       <c r="B14" s="21" t="n">
         <v>17950</v>
       </c>
-      <c r="C14" s="13">
-        <f> CF anuales / MC unitario</f>
-        <v/>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>= CF anuales / MC unitario</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1">
@@ -1928,9 +2036,10 @@
       <c r="B15" s="21" t="n">
         <v>57.9</v>
       </c>
-      <c r="C15" s="13">
-        <f> 17950 / 310 dias</f>
-        <v/>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>= 17950 / 310 dias</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1">
@@ -1948,12 +2057,15 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
           <t>INTERPRETACION</t>
         </is>
       </c>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="29" t="n"/>
     </row>
     <row r="19" ht="50" customHeight="1">
       <c r="A19" s="22" t="inlineStr">
@@ -1971,16 +2083,25 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A6:C6"/>
     <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1988,7 +2109,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2020,6 +2141,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -2154,6 +2276,7 @@
         <v>42600</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="23" t="inlineStr">
         <is>
@@ -2170,13 +2293,22 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2184,7 +2316,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2218,6 +2350,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -2382,6 +2515,7 @@
         <v>48557.6</v>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="24" t="inlineStr">
         <is>
@@ -2400,6 +2534,7 @@
         <v>209171.2</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="23" t="inlineStr">
         <is>
@@ -2416,12 +2551,21 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2429,9 +2573,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -2444,6 +2588,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="27" t="inlineStr">
         <is>
@@ -2451,6 +2596,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
@@ -2596,7 +2742,7 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>29+ anos de experiencia en hosteleria y 15+ anos en consultoria.</t>
+          <t>En cocina desde los 17 años · consultor gastronómico desde 2010.</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2753,24 @@
         </is>
       </c>
     </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/plan-negocio-bar-restaurante · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
+++ b/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -395,6 +395,12 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="4" fontId="9" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -853,7 +859,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SIN IVA. Con el mix 65/35 equivale a 20,72 € de PVP: dentro del rango 15-22 € que declara este mismo libro y del 18-25 € que fija el documento del plan</t>
+          <t>SIN IVA. El PVP equivalente lo calcula la celda «PVP equivalente con IVA» de abajo (al 10 % en sala son 20,02 € con los supuestos de partida): dentro del rango 15-22 € que declara este mismo libro y del 18-25 € que fija el documento del plan</t>
         </is>
       </c>
     </row>
@@ -909,12 +915,12 @@
         </is>
       </c>
       <c r="B9" s="35">
-        <f>IFERROR(IF($B$5="","",$B$5*(B11*(1+$B$39)+B12*(1+$B$40))),"")</f>
-        <v>20.7207</v>
+        <f>IFERROR(IF($B$5="","",$B$5*(B11*(1+$B$39)+B12*(1+($B$62*((1-$B$16)*$B$63+$B$16*$B$40)+(1-$B$62)*$B$39)))),"")</f>
+        <v>20.02</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Es el ticket sin IVA con el IVA de cada familia: "&amp;TEXT($B$39,"0%")&amp;" en comida y "&amp;TEXT($B$40,"0%")&amp;" en bebida. Compáralo con el rango del sector, que va con IVA.","")</f>
-        <v>Es el ticket sin IVA con el IVA de cada familia: 10% en comida y 21% en bebida. Compáralo con el rango del sector, que va con IVA.</v>
+        <f>IFERROR("Ticket sin IVA más el IVA: "&amp;TEXT($B$39*100,"0")&amp;" % en comida y "&amp;TEXT(($B$62*((1-$B$16)*$B$63+$B$16*$B$40)+(1-$B$62)*$B$39)*100,"0")&amp;" % en bebida"&amp;IF(ABS(($B$62*((1-$B$16)*$B$63+$B$16*$B$40)+(1-$B$62)*$B$39)-$B$39)&lt;0.00001,"","; el de bebida es un tipo MEDIO ponderado por el peso del alcohol, su tipo y el canal de delivery, no un tipo de la ley, y aquí va redondeado")&amp;". Compáralo con el rango del sector, que va con IVA.","")</f>
+        <v>Ticket sin IVA más el IVA: 10 % en comida y 10 % en bebida. Compáralo con el rango del sector, que va con IVA.</v>
       </c>
     </row>
     <row r="10">
@@ -1294,7 +1300,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Art. 29.1 LIS: los DOS primeros ejercicios con base imponible positiva</t>
+          <t>Art. 29.1 LIS: el PRIMER ejercicio con base imponible positiva y el SIGUIENTE. El libro lo aproxima contando los dos primeros ejercicios con base positiva: coincide con la ley salvo que entre ellos haya un ejercicio en pérdidas</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1315,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A partir del tercer ejercicio con base positiva</t>
+          <t>A partir del tercer ejercicio con base positiva. Es el tipo general del art. 29.1 LIS: si tu cifra de negocios queda por debajo de 1 M € (microempresa) o de 10 M € (reducida dimensión), desde 2025 hay tipos más bajos que se implantan de forma gradual; confirma el de tu ejercicio con tu asesor y cámbialo aquí</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1345,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bebidas alcohólicas, suministros, equipamiento y servicios</t>
+          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por el alcohol que sale por delivery (es una entrega de bienes). El alcohol servido en sala va al reducido: su tipo está en el bloque de desglose del IVA. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo</t>
         </is>
       </c>
     </row>
@@ -1433,7 +1439,13 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
+    <row r="49">
+      <c r="A49" s="30" t="inlineStr">
+        <is>
+          <t>ARRANQUE Y AFORO</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="A50" s="30" t="inlineStr">
         <is>
@@ -1603,11 +1615,25 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los cafés, refrescos, aguas y zumos servidos en hostelería van al IVA reducido; sólo la bebida alcohólica va al general. El resto de la línea de bebida se repercute al tipo de restauración</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
+          <t>Peso del alcohol dentro de la línea de bebida. Se usa igual en ventas y en compras, y es una aproximación (el alcohol suele pesar algo más en el coste que en la venta). En sala todo se repercute al 10 %, refrescos incluidos. En la factura del proveedor, el alcohol va al tipo general; el agua, el café y los zumos naturales al 10 %; los refrescos y zumos con azúcares o edulcorantes añadidos al 21 % desde 2021, que el libro aproxima al 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>IVA de la bebida ALCOHÓLICA servida en sala</t>
+        </is>
+      </c>
+      <c r="B63" s="34" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>10 %, igual que el resto del consumo en sala: el art. 91.Uno.2.2.º de la Ley 37/1992 del IVA grava al tipo reducido los servicios de hostelería y «el suministro de comidas y bebidas para consumir en el acto», sin excluir el alcohol. El 21 % es el tipo GENERAL y, fuera del consumo en el acto, alcanza al alcohol y también a los refrescos y zumos con azúcares o edulcorantes añadidos vendidos para llevar o a domicilio (art. 91.Uno.1.1.º de la misma ley). El libro lo aplica sólo a la parte ALCOHÓLICA de la bebida que sale por el canal de la celda «Ventas por delivery sobre el total»; los refrescos azucarados repartidos irían también al general y el libro no los separa</t>
+        </is>
+      </c>
+    </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
@@ -1681,7 +1707,7 @@
     <dataValidation sqref="B5 B22 B24 B26 B27 B30 B31 B42 B65 B66 B68" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="B7 B8 B11 B13 B14 B15 B16 B17 B18 B20 B28 B32 B37 B38 B39 B40 B41 B48 B52 B55 B62 B67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
+    <dataValidation sqref="B7 B8 B11 B13 B14 B15 B16 B17 B18 B20 B28 B32 B37 B38 B39 B40 B41 B48 B52 B55 B62 B63 B67" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
     </dataValidation>
@@ -2779,102 +2805,130 @@
       <c r="E49" s="44" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="49" t="inlineStr">
+      <c r="A50" s="44" t="inlineStr">
         <is>
           <t>IVA soportado sobre la inversión (recuperable)</t>
         </is>
       </c>
-      <c r="B50" s="50">
+      <c r="B50" s="48">
         <f>IFERROR(IF(B48="","",SUMIF($E$7:$E$45,"Sí",$B$7:$B$45)*'0. Supuestos'!$B$41),"")</f>
         <v>22734.6</v>
       </c>
-      <c r="D50" t="str">
+      <c r="C50" s="44" t="n"/>
+      <c r="D50" s="44" t="str">
         <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
+      <c r="E50" s="44" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="41" t="inlineStr">
         <is>
           <t>NECESIDAD TOTAL DE CAJA AL ARRANQUE</t>
         </is>
       </c>
-      <c r="B51" s="51">
+      <c r="B51" s="42">
         <f>IFERROR(B48+B50,"")</f>
         <v>201899.40000000002</v>
       </c>
-      <c r="D51" s="30" t="inlineStr">
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="41" t="inlineStr">
         <is>
           <t>Es la cifra que tiene que cubrir la hoja de Financiación</t>
         </is>
       </c>
+      <c r="E51" s="44" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="41" t="inlineStr">
         <is>
           <t>BASES DE AMORTIZACIÓN (no suman a la inversión)</t>
         </is>
       </c>
+      <c r="B52" s="44" t="n"/>
+      <c r="C52" s="44" t="n"/>
+      <c r="D52" s="44" t="n"/>
+      <c r="E52" s="44" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="49" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>Obra, instalaciones y acondicionamiento</t>
         </is>
       </c>
-      <c r="B53" s="50">
+      <c r="B53" s="48">
         <f>IFERROR(IF(B8="","",B8+B9+B10+B20+B26),"")</f>
         <v>43500.0</v>
       </c>
-      <c r="D53" t="str">
+      <c r="C53" s="44" t="n"/>
+      <c r="D53" s="44" t="str">
         <f>IFERROR("Se amortiza en "&amp;TEXT('0. Supuestos'!$B$44,"0")&amp;" años","")</f>
         <v>Se amortiza en 10 años</v>
       </c>
+      <c r="E53" s="44" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="49" t="inlineStr">
+      <c r="A54" s="44" t="inlineStr">
         <is>
           <t>Maquinaria, mobiliario y equipos</t>
         </is>
       </c>
-      <c r="B54" s="50">
+      <c r="B54" s="48">
         <f>IFERROR(IF(B15="","",B15+B16+B17+B18+B19+B21+B22+B23+B24+B27+B28+B29+B30+B31+B32+B33+B34+B35),"")</f>
         <v>40460.0</v>
       </c>
-      <c r="D54" t="str">
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="44" t="str">
         <f>IFERROR("Se amortiza en "&amp;TEXT('0. Supuestos'!$B$45,"0")&amp;" años","")</f>
         <v>Se amortiza en 10 años</v>
       </c>
+      <c r="E54" s="44" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="30" t="inlineStr">
+      <c r="A55" s="41" t="inlineStr">
         <is>
           <t>Amortización anual del inmovilizado</t>
         </is>
       </c>
-      <c r="B55" s="51">
+      <c r="B55" s="42">
         <f>IFERROR(B53/MAX(1,'0. Supuestos'!$B$44)+B54/MAX(1,'0. Supuestos'!$B$45),"")</f>
         <v>8396.0</v>
       </c>
-      <c r="D55" s="52" t="str">
+      <c r="C55" s="44" t="n"/>
+      <c r="D55" s="41" t="str">
         <f>IFERROR("No se amortizan el fondo de maniobra, la fianza, el alquiler previo, el marketing de lanzamiento, los gastos de constitución ni las existencias iniciales: no son inmovilizado. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan el fondo de maniobra, la fianza, el alquiler previo, el marketing de lanzamiento, los gastos de constitución ni las existencias iniciales: no son inmovilizado. Suman 95205 € de los 179165 € de inversión.</v>
       </c>
-    </row>
-    <row r="56"/>
+      <c r="E55" s="44" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="n"/>
+      <c r="B56" s="44" t="n"/>
+      <c r="C56" s="44" t="n"/>
+      <c r="D56" s="44" t="n"/>
+      <c r="E56" s="44" t="n"/>
+    </row>
     <row r="57" ht="45" customHeight="1">
-      <c r="A57" s="31" t="inlineStr">
+      <c r="A57" s="63" t="inlineStr">
         <is>
           <t>NOTA: Todos los importes son estimaciones basadas en precios de mercado en España 2026. Ajusta cada partida a tu situación real.</t>
         </is>
       </c>
+      <c r="B57" s="44" t="n"/>
+      <c r="C57" s="44" t="n"/>
+      <c r="D57" s="44" t="n"/>
+      <c r="E57" s="44" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="31" t="inlineStr">
+      <c r="A58" s="63" t="inlineStr">
         <is>
           <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
         </is>
       </c>
+      <c r="B58" s="44" t="n"/>
+      <c r="C58" s="44" t="n"/>
+      <c r="D58" s="44" t="n"/>
+      <c r="E58" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -3500,7 +3554,11 @@
         <f>IFERROR(B25/$B$10,"")</f>
         <v>0.0478553704360156</v>
       </c>
-      <c r="F25" s="44" t="n"/>
+      <c r="F25" s="44" t="inlineStr">
+        <is>
+          <t>Luz y gas van al 21 %; la factura del agua, al 10 %. El libro aplica a toda esta partida el tipo de la columna de al lado (21 %): si el agua pesa mucho en tu local, sepárala en su línea</t>
+        </is>
+      </c>
       <c r="G25" s="46">
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
@@ -3998,406 +4056,463 @@
       <c r="G42" s="44" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="30" t="inlineStr">
+      <c r="A43" s="41" t="inlineStr">
         <is>
           <t>RESULTADO ANTES DE IMPUESTOS</t>
         </is>
       </c>
-      <c r="B43" s="51">
+      <c r="B43" s="42">
         <f>IFERROR(IF(B10="","",B21-B40),"")</f>
         <v>57566.399999999965</v>
       </c>
-      <c r="C43" s="51">
+      <c r="C43" s="42">
         <f>IFERROR(IF(C10="","",C21-C40),"")</f>
         <v>82484.56</v>
       </c>
-      <c r="D43" s="51">
+      <c r="D43" s="42">
         <f>IFERROR(IF(D10="","",D21-D40),"")</f>
         <v>97991.57058668719</v>
       </c>
-      <c r="E43" s="57">
+      <c r="E43" s="43">
         <f>IFERROR(B43/$B$10,"")</f>
         <v>0.12753987947536327</v>
       </c>
+      <c r="F43" s="44" t="n"/>
+      <c r="G43" s="44" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="49" t="inlineStr">
+      <c r="A44" s="44" t="inlineStr">
         <is>
           <t>Bases negativas pendientes al inicio</t>
         </is>
       </c>
-      <c r="B44" s="50">
+      <c r="B44" s="48">
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$42),"")</f>
         <v>0.0</v>
       </c>
-      <c r="C44" s="50">
+      <c r="C44" s="48">
         <f>IFERROR(IF(C10="","",B49),"")</f>
         <v>0.0</v>
       </c>
-      <c r="D44" s="50">
+      <c r="D44" s="48">
         <f>IFERROR(IF(D10="","",C49),"")</f>
         <v>0.0</v>
       </c>
-      <c r="F44" s="49" t="inlineStr">
+      <c r="E44" s="44" t="n"/>
+      <c r="F44" s="44" t="inlineStr">
         <is>
           <t>Art. 26 LIS: las pérdidas de un ejercicio se compensan con los beneficios de los siguientes</t>
         </is>
       </c>
+      <c r="G44" s="44" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="49" t="inlineStr">
+      <c r="A45" s="44" t="inlineStr">
         <is>
           <t>Base imponible (después de compensar)</t>
         </is>
       </c>
-      <c r="B45" s="50">
+      <c r="B45" s="48">
         <f>IFERROR(IF(B10="","",MAX(0,B43-B44)),"")</f>
         <v>57566.399999999965</v>
       </c>
-      <c r="C45" s="50">
+      <c r="C45" s="48">
         <f>IFERROR(IF(C10="","",MAX(0,C43-C44)),"")</f>
         <v>82484.56</v>
       </c>
-      <c r="D45" s="50">
+      <c r="D45" s="48">
         <f>IFERROR(IF(D10="","",MAX(0,D43-D44)),"")</f>
         <v>97991.57058668719</v>
       </c>
+      <c r="E45" s="44" t="n"/>
+      <c r="F45" s="44" t="n"/>
+      <c r="G45" s="44" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="49" t="inlineStr">
+      <c r="A46" s="44" t="inlineStr">
         <is>
           <t>Ejercicios con base positiva (acumulado)</t>
         </is>
       </c>
-      <c r="B46" s="58">
+      <c r="B46" s="55">
         <f>IFERROR(IF(B10="","",IF(B45&gt;0,1,0)),"")</f>
         <v>1.0</v>
       </c>
-      <c r="C46" s="58">
+      <c r="C46" s="55">
         <f>IFERROR(IF(C10="","",B46+IF(C45&gt;0,1,0)),"")</f>
         <v>2.0</v>
       </c>
-      <c r="D46" s="58">
+      <c r="D46" s="55">
         <f>IFERROR(IF(D10="","",C46+IF(D45&gt;0,1,0)),"")</f>
         <v>3.0</v>
       </c>
+      <c r="E46" s="44" t="n"/>
+      <c r="F46" s="44" t="n"/>
+      <c r="G46" s="44" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="49" t="inlineStr">
+      <c r="A47" s="44" t="inlineStr">
         <is>
           <t>Tipo de Impuesto de Sociedades aplicado</t>
         </is>
       </c>
-      <c r="B47" s="36">
+      <c r="B47" s="46">
         <f>IFERROR(IF(B10="","",IF(B45&lt;=0,"",IF(B46&lt;=2,'0. Supuestos'!$B$37,'0. Supuestos'!$B$38))),"")</f>
         <v>0.15</v>
       </c>
-      <c r="C47" s="36">
+      <c r="C47" s="46">
         <f>IFERROR(IF(C10="","",IF(C45&lt;=0,"",IF(C46&lt;=2,'0. Supuestos'!$B$37,'0. Supuestos'!$B$38))),"")</f>
         <v>0.15</v>
       </c>
-      <c r="D47" s="36">
+      <c r="D47" s="46">
         <f>IFERROR(IF(D10="","",IF(D45&lt;=0,"",IF(D46&lt;=2,'0. Supuestos'!$B$37,'0. Supuestos'!$B$38))),"")</f>
         <v>0.25</v>
       </c>
-      <c r="F47" s="49" t="inlineStr">
-        <is>
-          <t>Art. 29.1 LIS: el tipo reducido de entidad de nueva creación se aplica a los DOS primeros ejercicios con base positiva, no al primer año</t>
-        </is>
-      </c>
+      <c r="E47" s="44" t="n"/>
+      <c r="F47" s="44" t="inlineStr">
+        <is>
+          <t>Art. 29.1 LIS: el 15 % de entidad de nueva creación se aplica al PRIMER ejercicio con base positiva y al SIGUIENTE, no al primer año de vida. El libro lo aproxima contando los dos primeros ejercicios con base positiva</t>
+        </is>
+      </c>
+      <c r="G47" s="44" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="49" t="inlineStr">
+      <c r="A48" s="44" t="inlineStr">
         <is>
           <t>Impuesto de Sociedades</t>
         </is>
       </c>
-      <c r="B48" s="50">
+      <c r="B48" s="48">
         <f>IFERROR(IF(B10="","",IF(B47="",0,B45*B47)),"")</f>
         <v>8634.959999999994</v>
       </c>
-      <c r="C48" s="50">
+      <c r="C48" s="48">
         <f>IFERROR(IF(C10="","",IF(C47="",0,C45*C47)),"")</f>
         <v>12372.684</v>
       </c>
-      <c r="D48" s="50">
+      <c r="D48" s="48">
         <f>IFERROR(IF(D10="","",IF(D47="",0,D45*D47)),"")</f>
         <v>24497.892646671797</v>
       </c>
+      <c r="E48" s="44" t="n"/>
+      <c r="F48" s="44" t="n"/>
+      <c r="G48" s="44" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="49" t="inlineStr">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>Bases negativas pendientes al cierre</t>
         </is>
       </c>
-      <c r="B49" s="50">
+      <c r="B49" s="48">
         <f>IFERROR(IF(B10="","",MAX(0,B44-B43)),"")</f>
         <v>0.0</v>
       </c>
-      <c r="C49" s="50">
+      <c r="C49" s="48">
         <f>IFERROR(IF(C10="","",MAX(0,C44-C43)),"")</f>
         <v>0.0</v>
       </c>
-      <c r="D49" s="50">
+      <c r="D49" s="48">
         <f>IFERROR(IF(D10="","",MAX(0,D44-D43)),"")</f>
         <v>0.0</v>
       </c>
+      <c r="E49" s="44" t="n"/>
+      <c r="F49" s="44" t="n"/>
+      <c r="G49" s="44" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="30" t="inlineStr">
+      <c r="A50" s="41" t="inlineStr">
         <is>
           <t>RESULTADO NETO</t>
         </is>
       </c>
-      <c r="B50" s="51">
+      <c r="B50" s="42">
         <f>IFERROR(IF(B10="","",B43-B48),"")</f>
         <v>48931.43999999997</v>
       </c>
-      <c r="C50" s="51">
+      <c r="C50" s="42">
         <f>IFERROR(IF(C10="","",C43-C48),"")</f>
         <v>70111.876</v>
       </c>
-      <c r="D50" s="51">
+      <c r="D50" s="42">
         <f>IFERROR(IF(D10="","",D43-D48),"")</f>
         <v>73493.67794001539</v>
       </c>
-      <c r="E50" s="57">
+      <c r="E50" s="43">
         <f>IFERROR(B50/$B$10,"")</f>
         <v>0.10840889755405879</v>
       </c>
+      <c r="F50" s="44" t="n"/>
+      <c r="G50" s="44" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="30" t="inlineStr">
+      <c r="A51" s="41" t="inlineStr">
         <is>
           <t>RATIOS CLAVE</t>
         </is>
       </c>
+      <c r="B51" s="44" t="n"/>
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="44" t="n"/>
+      <c r="E51" s="44" t="n"/>
+      <c r="F51" s="44" t="n"/>
+      <c r="G51" s="44" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="30" t="inlineStr">
+      <c r="A52" s="41" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="B52" s="30" t="inlineStr">
+      <c r="B52" s="41" t="inlineStr">
         <is>
           <t>Año 1</t>
         </is>
       </c>
-      <c r="C52" s="30" t="inlineStr">
+      <c r="C52" s="41" t="inlineStr">
         <is>
           <t>Año 2</t>
         </is>
       </c>
-      <c r="D52" s="30" t="inlineStr">
+      <c r="D52" s="41" t="inlineStr">
         <is>
           <t>Año 3</t>
         </is>
       </c>
-      <c r="E52" s="30" t="inlineStr">
+      <c r="E52" s="41" t="inlineStr">
         <is>
           <t>Umbral</t>
         </is>
       </c>
-      <c r="F52" s="30" t="inlineStr">
+      <c r="F52" s="41" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
+      <c r="G52" s="44" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="49" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>Margen bruto / Ventas</t>
         </is>
       </c>
-      <c r="B53" s="36">
+      <c r="B53" s="46">
         <f>IFERROR(IF(B10="","",B21/B10),"")</f>
         <v>0.6849999999999999</v>
       </c>
-      <c r="C53" s="36">
+      <c r="C53" s="46">
         <f>IFERROR(IF(C10="","",C21/C10),"")</f>
         <v>0.685</v>
       </c>
-      <c r="D53" s="36">
+      <c r="D53" s="46">
         <f>IFERROR(IF(D10="","",D21/D10),"")</f>
         <v>0.685</v>
       </c>
-      <c r="E53" s="59" t="n">
+      <c r="E53" s="77" t="n">
         <v>0.65</v>
       </c>
-      <c r="F53" s="49" t="inlineStr">
+      <c r="F53" s="44" t="inlineStr">
         <is>
           <t>Por debajo, revisa precios de carta y escandallos</t>
         </is>
       </c>
+      <c r="G53" s="44" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="49" t="inlineStr">
+      <c r="A54" s="44" t="inlineStr">
         <is>
           <t>Coste de mercancía (comida + bebida)</t>
         </is>
       </c>
-      <c r="B54" s="50">
+      <c r="B54" s="48">
         <f>IFERROR(IF(B10="","",B14+B15),"")</f>
         <v>122769.92</v>
       </c>
-      <c r="C54" s="50">
+      <c r="C54" s="48">
         <f>IFERROR(IF(C10="","",C14+C15),"")</f>
         <v>135046.912</v>
       </c>
-      <c r="D54" s="50">
+      <c r="D54" s="48">
         <f>IFERROR(IF(D10="","",D14+D15),"")</f>
         <v>143149.72671999998</v>
       </c>
+      <c r="E54" s="44" t="n"/>
+      <c r="F54" s="44" t="n"/>
+      <c r="G54" s="44" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="49" t="inlineStr">
+      <c r="A55" s="44" t="inlineStr">
         <is>
           <t>Coste de mercancía / Ventas</t>
         </is>
       </c>
-      <c r="B55" s="36">
+      <c r="B55" s="46">
         <f>IFERROR(IF(B10="","",B54/B10),"")</f>
         <v>0.272</v>
       </c>
-      <c r="C55" s="36">
+      <c r="C55" s="46">
         <f>IFERROR(IF(C10="","",C54/C10),"")</f>
         <v>0.272</v>
       </c>
-      <c r="D55" s="36">
+      <c r="D55" s="46">
         <f>IFERROR(IF(D10="","",D54/D10),"")</f>
         <v>0.27199999999999996</v>
       </c>
-      <c r="E55" s="59" t="n">
+      <c r="E55" s="77" t="n">
         <v>0.32</v>
       </c>
-      <c r="F55" s="49" t="inlineStr">
+      <c r="F55" s="44" t="inlineStr">
         <is>
           <t>Techo del propio libro: «Food cost objetivo 28-32 %»</t>
         </is>
       </c>
+      <c r="G55" s="44" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="49" t="inlineStr">
+      <c r="A56" s="44" t="inlineStr">
         <is>
           <t>Coste de personal / Ventas</t>
         </is>
       </c>
-      <c r="B56" s="36">
+      <c r="B56" s="46">
         <f>IFERROR(IF(B10="","",B24/B10),"")</f>
         <v>0.3366253101736973</v>
       </c>
-      <c r="C56" s="36">
+      <c r="C56" s="46">
         <f>IFERROR(IF(C10="","",C24/C10),"")</f>
         <v>0.31810769875286005</v>
       </c>
-      <c r="D56" s="36">
+      <c r="D56" s="46">
         <f>IFERROR(IF(D10="","",D24/D10),"")</f>
         <v>0.3115022530725513</v>
       </c>
-      <c r="E56" s="59" t="n">
+      <c r="E56" s="77" t="n">
         <v>0.34</v>
       </c>
-      <c r="F56" s="49" t="inlineStr">
+      <c r="F56" s="44" t="inlineStr">
         <is>
           <t>Techo MÁS ESTRICTO de los que publica este producto: «el labor cost no debe superar el 34 %». Es el que manda</t>
         </is>
       </c>
+      <c r="G56" s="44" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="49" t="inlineStr">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>Alquiler / Ventas</t>
         </is>
       </c>
-      <c r="B57" s="36">
+      <c r="B57" s="46">
         <f>IFERROR(IF(B10="","",B23/B10),"")</f>
         <v>0.07975895072669266</v>
       </c>
-      <c r="C57" s="36">
+      <c r="C57" s="46">
         <f>IFERROR(IF(C10="","",C23/C10),"")</f>
         <v>0.07250813702426606</v>
       </c>
-      <c r="D57" s="36">
+      <c r="D57" s="46">
         <f>IFERROR(IF(D10="","",D23/D10),"")</f>
         <v>0.06840390285308118</v>
       </c>
-      <c r="E57" s="59" t="n">
+      <c r="E57" s="77" t="n">
         <v>0.1</v>
       </c>
-      <c r="F57" s="49" t="inlineStr">
+      <c r="F57" s="44" t="inlineStr">
         <is>
           <t>Techo del propio libro: «Alquiler: no superar 8-10 % de los ingresos»</t>
         </is>
       </c>
+      <c r="G57" s="44" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="49" t="inlineStr">
+      <c r="A58" s="44" t="inlineStr">
         <is>
           <t>Resultado neto / Ventas</t>
         </is>
       </c>
-      <c r="B58" s="36">
+      <c r="B58" s="46">
         <f>IFERROR(IF(B10="","",B50/B10),"")</f>
         <v>0.10840889755405879</v>
       </c>
-      <c r="C58" s="36">
+      <c r="C58" s="46">
         <f>IFERROR(IF(C10="","",C50/C10),"")</f>
         <v>0.14121337533434308</v>
       </c>
-      <c r="D58" s="36">
+      <c r="D58" s="46">
         <f>IFERROR(IF(D10="","",D50/D10),"")</f>
         <v>0.13964595572567912</v>
       </c>
-      <c r="E58" s="59" t="n">
+      <c r="E58" s="77" t="n">
         <v>0.05</v>
       </c>
-      <c r="F58" s="49" t="inlineStr">
+      <c r="F58" s="44" t="inlineStr">
         <is>
           <t>Suelo del propio libro: «Margen neto medio sector: 5-10 %»</t>
         </is>
       </c>
+      <c r="G58" s="44" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="49" t="inlineStr">
+      <c r="A59" s="44" t="inlineStr">
         <is>
           <t>Punto de equilibrio alcanzado</t>
         </is>
       </c>
-      <c r="B59" t="str">
+      <c r="B59" s="44" t="str">
         <f>IFERROR(IF(B10="","",IF(B10="","",IF(B10&gt;='3. Punto Equilibrio'!$B$17,"Sí","No"))),"")</f>
         <v>Sí</v>
       </c>
-      <c r="C59" t="str">
+      <c r="C59" s="44" t="str">
         <f>IFERROR(IF(C10="","",IF(C10="","",IF(C10&gt;='3. Punto Equilibrio'!$C$17,"Sí","No"))),"")</f>
         <v>Sí</v>
       </c>
-      <c r="D59" t="str">
+      <c r="D59" s="44" t="str">
         <f>IFERROR(IF(D10="","",IF(D10="","",IF(D10&gt;='3. Punto Equilibrio'!$D$17,"Sí","No"))),"")</f>
         <v>Sí</v>
       </c>
-      <c r="F59" s="49" t="inlineStr">
+      <c r="E59" s="44" t="n"/>
+      <c r="F59" s="44" t="inlineStr">
         <is>
           <t>Compara las ventas de CADA año con el umbral de ese mismo año, que calcula la hoja de Punto de Equilibrio con los costes fijos del año</t>
         </is>
       </c>
-    </row>
-    <row r="60"/>
+      <c r="G59" s="44" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="n"/>
+      <c r="B60" s="44" t="n"/>
+      <c r="C60" s="44" t="n"/>
+      <c r="D60" s="44" t="n"/>
+      <c r="E60" s="44" t="n"/>
+      <c r="F60" s="44" t="n"/>
+      <c r="G60" s="44" t="n"/>
+    </row>
     <row r="61" ht="135" customHeight="1">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="A61" s="63" t="inlineStr">
         <is>
           <t>Todas las cifras van SIN IVA. Las columnas de los años 2 y 3 están en euros del año 1 salvo que subas la actualización de costes en la hoja de Supuestos. La columna «IVA soportado» dice a qué tipo se compra cada partida y la lee la hoja de Tesorería: los seguros y las comisiones de los medios de pago están exentos, y las nóminas, la amortización y los intereses no llevan IVA.</t>
         </is>
       </c>
+      <c r="B61" s="44" t="n"/>
+      <c r="C61" s="44" t="n"/>
+      <c r="D61" s="44" t="n"/>
+      <c r="E61" s="44" t="n"/>
+      <c r="F61" s="44" t="n"/>
+      <c r="G61" s="44" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="44" t="inlineStr">
         <is>
           <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
         </is>
       </c>
+      <c r="B62" s="44" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="44" t="n"/>
+      <c r="E62" s="44" t="n"/>
+      <c r="F62" s="44" t="n"/>
+      <c r="G62" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -4506,7 +4621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -5233,11 +5348,176 @@
       <c r="F40" s="44" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="44" t="inlineStr">
         <is>
           <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
         </is>
       </c>
+      <c r="B41" s="44" t="n"/>
+      <c r="C41" s="44" t="n"/>
+      <c r="D41" s="44" t="n"/>
+      <c r="E41" s="44" t="n"/>
+      <c r="F41" s="44" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="44" t="n"/>
+      <c r="B42" s="44" t="n"/>
+      <c r="C42" s="44" t="n"/>
+      <c r="D42" s="44" t="n"/>
+      <c r="E42" s="44" t="n"/>
+      <c r="F42" s="44" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="44" t="n"/>
+      <c r="B43" s="44" t="n"/>
+      <c r="C43" s="44" t="n"/>
+      <c r="D43" s="44" t="n"/>
+      <c r="E43" s="44" t="n"/>
+      <c r="F43" s="44" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="n"/>
+      <c r="B44" s="44" t="n"/>
+      <c r="C44" s="44" t="n"/>
+      <c r="D44" s="44" t="n"/>
+      <c r="E44" s="44" t="n"/>
+      <c r="F44" s="44" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="44" t="n"/>
+      <c r="B45" s="44" t="n"/>
+      <c r="C45" s="44" t="n"/>
+      <c r="D45" s="44" t="n"/>
+      <c r="E45" s="44" t="n"/>
+      <c r="F45" s="44" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="n"/>
+      <c r="B46" s="44" t="n"/>
+      <c r="C46" s="44" t="n"/>
+      <c r="D46" s="44" t="n"/>
+      <c r="E46" s="44" t="n"/>
+      <c r="F46" s="44" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="n"/>
+      <c r="B47" s="44" t="n"/>
+      <c r="C47" s="44" t="n"/>
+      <c r="D47" s="44" t="n"/>
+      <c r="E47" s="44" t="n"/>
+      <c r="F47" s="44" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="44" t="n"/>
+      <c r="B48" s="44" t="n"/>
+      <c r="C48" s="44" t="n"/>
+      <c r="D48" s="44" t="n"/>
+      <c r="E48" s="44" t="n"/>
+      <c r="F48" s="44" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="44" t="n"/>
+      <c r="B49" s="44" t="n"/>
+      <c r="C49" s="44" t="n"/>
+      <c r="D49" s="44" t="n"/>
+      <c r="E49" s="44" t="n"/>
+      <c r="F49" s="44" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="44" t="n"/>
+      <c r="B50" s="44" t="n"/>
+      <c r="C50" s="44" t="n"/>
+      <c r="D50" s="44" t="n"/>
+      <c r="E50" s="44" t="n"/>
+      <c r="F50" s="44" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="44" t="n"/>
+      <c r="B51" s="44" t="n"/>
+      <c r="C51" s="44" t="n"/>
+      <c r="D51" s="44" t="n"/>
+      <c r="E51" s="44" t="n"/>
+      <c r="F51" s="44" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="44" t="n"/>
+      <c r="B52" s="44" t="n"/>
+      <c r="C52" s="44" t="n"/>
+      <c r="D52" s="44" t="n"/>
+      <c r="E52" s="44" t="n"/>
+      <c r="F52" s="44" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="44" t="n"/>
+      <c r="B53" s="44" t="n"/>
+      <c r="C53" s="44" t="n"/>
+      <c r="D53" s="44" t="n"/>
+      <c r="E53" s="44" t="n"/>
+      <c r="F53" s="44" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="44" t="n"/>
+      <c r="B54" s="44" t="n"/>
+      <c r="C54" s="44" t="n"/>
+      <c r="D54" s="44" t="n"/>
+      <c r="E54" s="44" t="n"/>
+      <c r="F54" s="44" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="44" t="n"/>
+      <c r="B55" s="44" t="n"/>
+      <c r="C55" s="44" t="n"/>
+      <c r="D55" s="44" t="n"/>
+      <c r="E55" s="44" t="n"/>
+      <c r="F55" s="44" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="44" t="n"/>
+      <c r="B56" s="44" t="n"/>
+      <c r="C56" s="44" t="n"/>
+      <c r="D56" s="44" t="n"/>
+      <c r="E56" s="44" t="n"/>
+      <c r="F56" s="44" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="44" t="n"/>
+      <c r="B57" s="44" t="n"/>
+      <c r="C57" s="44" t="n"/>
+      <c r="D57" s="44" t="n"/>
+      <c r="E57" s="44" t="n"/>
+      <c r="F57" s="44" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="44" t="n"/>
+      <c r="B58" s="44" t="n"/>
+      <c r="C58" s="44" t="n"/>
+      <c r="D58" s="44" t="n"/>
+      <c r="E58" s="44" t="n"/>
+      <c r="F58" s="44" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="n"/>
+      <c r="B59" s="44" t="n"/>
+      <c r="C59" s="44" t="n"/>
+      <c r="D59" s="44" t="n"/>
+      <c r="E59" s="44" t="n"/>
+      <c r="F59" s="44" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="44" t="n"/>
+      <c r="B60" s="44" t="n"/>
+      <c r="C60" s="44" t="n"/>
+      <c r="D60" s="44" t="n"/>
+      <c r="E60" s="44" t="n"/>
+      <c r="F60" s="44" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="44" t="n"/>
+      <c r="B61" s="44" t="n"/>
+      <c r="C61" s="44" t="n"/>
+      <c r="D61" s="44" t="n"/>
+      <c r="E61" s="44" t="n"/>
+      <c r="F61" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -5562,248 +5842,290 @@
       <c r="F15" s="44" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="49" t="inlineStr">
+      <c r="A16" s="44" t="inlineStr">
         <is>
           <t>TOTAL COSTES VARIABLES</t>
         </is>
       </c>
-      <c r="B16" s="50">
+      <c r="B16" s="48">
         <f>IFERROR(IF(B9="","",SUM(B10:B15)),"")</f>
         <v>87147.89999999998</v>
       </c>
-      <c r="C16" s="50">
+      <c r="C16" s="48">
         <f>IFERROR(IF(C9="","",SUM(C10:C15)),"")</f>
         <v>142178.4</v>
       </c>
-      <c r="D16" s="50">
+      <c r="D16" s="48">
         <f>IFERROR(IF(D9="","",SUM(D10:D15)),"")</f>
         <v>177156.0</v>
       </c>
+      <c r="E16" s="44" t="n"/>
+      <c r="F16" s="44" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>MARGEN BRUTO</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="48">
         <f>IFERROR(IF(B9="","",B9-B16),"")</f>
         <v>189512.10000000003</v>
       </c>
-      <c r="C17" s="50">
+      <c r="C17" s="48">
         <f>IFERROR(IF(C9="","",C9-C16),"")</f>
         <v>309181.6</v>
       </c>
-      <c r="D17" s="50">
+      <c r="D17" s="48">
         <f>IFERROR(IF(D9="","",D9-D16),"")</f>
         <v>385244.0</v>
       </c>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>COSTES FIJOS (los del P&amp;L)</t>
         </is>
       </c>
-      <c r="B18" s="50">
+      <c r="B18" s="48">
         <f>IFERROR(IF(B9="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
         <v>251615.2</v>
       </c>
-      <c r="C18" s="50">
+      <c r="C18" s="48">
         <f>IFERROR(IF(C9="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
         <v>251615.2</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="48">
         <f>IFERROR(IF(D9="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
         <v>251615.2</v>
       </c>
-      <c r="E18" s="49" t="inlineStr">
+      <c r="E18" s="44" t="inlineStr">
         <is>
           <t>Los costes fijos no cambian con el escenario: por eso son fijos</t>
         </is>
       </c>
+      <c r="F18" s="44" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>RESULTADO ANTES DE IMPUESTOS</t>
         </is>
       </c>
-      <c r="B19" s="51">
+      <c r="B19" s="42">
         <f>IFERROR(IF(B9="","",B17-B18),"")</f>
         <v>-62103.09999999998</v>
       </c>
-      <c r="C19" s="51">
+      <c r="C19" s="42">
         <f>IFERROR(IF(C9="","",C17-C18),"")</f>
         <v>57566.399999999965</v>
       </c>
-      <c r="D19" s="51">
+      <c r="D19" s="42">
         <f>IFERROR(IF(D9="","",D17-D18),"")</f>
         <v>133628.8</v>
       </c>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>Impuesto de Sociedades</t>
         </is>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="48">
         <f>IFERROR(IF(B9="","",MAX(0,B19-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
         <v>0.0</v>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="48">
         <f>IFERROR(IF(C9="","",MAX(0,C19-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
         <v>8634.959999999994</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="48">
         <f>IFERROR(IF(D9="","",MAX(0,D19-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
         <v>20044.319999999996</v>
       </c>
-      <c r="E20" s="49" t="inlineStr">
+      <c r="E20" s="44" t="inlineStr">
         <is>
           <t>Al tipo de entidad de nueva creación, compensando las bases negativas anteriores</t>
         </is>
       </c>
+      <c r="F20" s="44" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="30" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>RESULTADO NETO</t>
         </is>
       </c>
-      <c r="B21" s="51">
+      <c r="B21" s="42">
         <f>IFERROR(IF(B9="","",B19-B20),"")</f>
         <v>-62103.09999999998</v>
       </c>
-      <c r="C21" s="51">
+      <c r="C21" s="42">
         <f>IFERROR(IF(C9="","",C19-C20),"")</f>
         <v>48931.43999999997</v>
       </c>
-      <c r="D21" s="51">
+      <c r="D21" s="42">
         <f>IFERROR(IF(D9="","",D19-D20),"")</f>
         <v>113584.48</v>
       </c>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>Cubiertos/día para el equilibrio</t>
         </is>
       </c>
-      <c r="B22" s="67">
+      <c r="B22" s="60">
         <f>IFERROR(IF(B9="","",IF(B7-B16/(B6*B8)&lt;=0,"",B18/(B7-B16/(B6*B8))/B8)),"")</f>
         <v>77.00659535723575</v>
       </c>
-      <c r="C22" s="67">
+      <c r="C22" s="60">
         <f>IFERROR(IF(C9="","",IF(C7-C16/(C6*C8)&lt;=0,"",C18/(C7-C16/(C6*C8))/C8)),"")</f>
         <v>65.10483159411817</v>
       </c>
-      <c r="D22" s="67">
+      <c r="D22" s="60">
         <f>IFERROR(IF(D9="","",IF(D7-D16/(D6*D8)&lt;=0,"",D18/(D7-D16/(D6*D8))/D8)),"")</f>
         <v>62.04754389425923</v>
       </c>
+      <c r="E22" s="44" t="n"/>
+      <c r="F22" s="44" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="30" t="inlineStr">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>LO QUE CADA ESCENARIO EXIGE</t>
         </is>
       </c>
+      <c r="B23" s="44" t="n"/>
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+      <c r="F23" s="44" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>Coste de personal / Ventas</t>
         </is>
       </c>
-      <c r="B24" s="36">
+      <c r="B24" s="46">
         <f>IFERROR(IF(B9="","",'2. P&amp;L 3 Años'!$B$24/B9),"")</f>
         <v>0.5491910648449361</v>
       </c>
-      <c r="C24" s="36">
+      <c r="C24" s="46">
         <f>IFERROR(IF(C9="","",'2. P&amp;L 3 Años'!$B$24/C9),"")</f>
         <v>0.3366253101736973</v>
       </c>
-      <c r="D24" s="36">
+      <c r="D24" s="46">
         <f>IFERROR(IF(D9="","",'2. P&amp;L 3 Años'!$B$24/D9),"")</f>
         <v>0.27016216216216216</v>
       </c>
-      <c r="E24" s="49" t="inlineStr">
+      <c r="E24" s="44" t="inlineStr">
         <is>
           <t>La MISMA plantilla en los tres escenarios. Si en el pesimista se dispara, el ajuste hay que hacerlo en la hoja de Personal, no aquí</t>
         </is>
       </c>
+      <c r="F24" s="44" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>Cubiertos al año por jornada equivalente</t>
         </is>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="55">
         <f>IFERROR(IF(B9="","",B6*B8/'5. Personal'!$C$13),"")</f>
         <v>3222.222222222222</v>
       </c>
-      <c r="C25" s="58">
+      <c r="C25" s="55">
         <f>IFERROR(IF(C9="","",C6*C8/'5. Personal'!$C$13),"")</f>
         <v>4592.592592592592</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="55">
         <f>IFERROR(IF(D9="","",D6*D8/'5. Personal'!$C$13),"")</f>
         <v>5629.62962962963</v>
       </c>
-      <c r="E25" s="49" t="inlineStr">
+      <c r="E25" s="44" t="inlineStr">
         <is>
           <t>Cubiertos que tendría que sacar cada jornada completa del cuadro de Personal. En el optimista dice si hace falta contratar</t>
         </is>
       </c>
+      <c r="F25" s="44" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Saldo de caja al cierre del año 1</t>
         </is>
       </c>
-      <c r="B26" s="51">
+      <c r="B26" s="42">
         <f>IFERROR(IF(B9="","",'1. Inversión Inicial'!$B$47+B21+'2. P&amp;L 3 Años'!$B$38-'7. Financiación'!$B$45),"")</f>
         <v>7097.7000000000335</v>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="42">
         <f>IFERROR(IF(C9="","",'6. Tesorería 12 meses'!$M$22),"")</f>
-        <v>166219.8243604959</v>
-      </c>
-      <c r="D26" s="51">
+        <v>155793.4083604959</v>
+      </c>
+      <c r="D26" s="42">
         <f>IFERROR(IF(D9="","",'1. Inversión Inicial'!$B$47+D21+'2. P&amp;L 3 Años'!$B$38-'7. Financiación'!$B$45),"")</f>
         <v>182785.28</v>
       </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="E26" s="41" t="inlineStr">
         <is>
           <t>En «Realista» es el saldo REAL del mes 12 de la hoja de tesorería, con su desfase de cobros y pagos y su liquidación de IVA. En «Pesimista» y «Optimista» es un saldo estimado (sin efecto de cobros/pagos ni IVA) — ver Tesorería: fondo de maniobra más el resultado del año, devolviendo la amortización (que no se paga) y restando el principal del préstamo. En rojo, el escenario se queda sin caja</t>
         </is>
       </c>
-    </row>
-    <row r="27"/>
+      <c r="F26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+    </row>
     <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="63" t="inlineStr">
         <is>
           <t>La columna «Realista» lee sus tres datos de la hoja de Supuestos, así que reproduce EXACTAMENTE el año 1 del P&amp;L. Los otros dos escenarios usan las mismas tasas de coste: lo único que cambia son los cubiertos, el ticket y los días. Los COSTES FIJOS sí son los mismos en los tres: los varios e imprevistos, que son un porcentaje de las ventas, van arriba con los variables y cada escenario carga los suyos.</t>
         </is>
       </c>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="44" t="inlineStr">
         <is>
           <t>NOTA: El escenario pesimista refleja un arranque lento con menor afluencia. El optimista asume alta ocupación y ticket medio superior. Los costes fijos son constantes en los 3 escenarios.</t>
         </is>
       </c>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+      <c r="F29" s="44" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
         </is>
       </c>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="44" t="n"/>
+      <c r="D30" s="44" t="n"/>
+      <c r="E30" s="44" t="n"/>
+      <c r="F30" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -5814,10 +6136,10 @@
   </mergeCells>
   <conditionalFormatting sqref="B24:D24">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(B24),B24&gt;'2. P&amp;L 3 Anos'!$E$56)</formula>
+      <formula>AND(ISNUMBER(B24),B24&gt;'2. P&amp;L 3 Años'!$E$56)</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
-      <formula>AND(ISNUMBER(B24),B24&lt;='2. P&amp;L 3 Anos'!$E$56)</formula>
+      <formula>AND(ISNUMBER(B24),B24&lt;='2. P&amp;L 3 Años'!$E$56)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:D26">
@@ -6350,153 +6672,267 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="49" t="inlineStr">
+      <c r="A17" s="44" t="inlineStr">
         <is>
           <t>Coste de personal del año 2</t>
         </is>
       </c>
-      <c r="B17" s="50">
+      <c r="B17" s="48">
         <f>IFERROR(IF(G13="","",G13*(1+'0. Supuestos'!$B$48)+B15),"")</f>
         <v>157939.2</v>
       </c>
+      <c r="C17" s="44" t="n"/>
+      <c r="D17" s="44" t="n"/>
+      <c r="E17" s="44" t="n"/>
+      <c r="F17" s="44" t="n"/>
+      <c r="G17" s="44" t="n"/>
+      <c r="H17" s="44" t="n"/>
+      <c r="I17" s="44" t="n"/>
+      <c r="J17" s="44" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="49" t="inlineStr">
+      <c r="A18" s="44" t="inlineStr">
         <is>
           <t>Coste de personal del año 3</t>
         </is>
       </c>
-      <c r="B18" s="50">
+      <c r="B18" s="48">
         <f>IFERROR(IF(B17="","",B17*(1+'0. Supuestos'!$B$48)+B16),"")</f>
         <v>163939.2</v>
       </c>
+      <c r="C18" s="44" t="n"/>
+      <c r="D18" s="44" t="n"/>
+      <c r="E18" s="44" t="n"/>
+      <c r="F18" s="44" t="n"/>
+      <c r="G18" s="44" t="n"/>
+      <c r="H18" s="44" t="n"/>
+      <c r="I18" s="44" t="n"/>
+      <c r="J18" s="44" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="30" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>COBERTURA POR HORAS DE SERVICIO</t>
         </is>
       </c>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+      <c r="F19" s="44" t="n"/>
+      <c r="G19" s="44" t="n"/>
+      <c r="H19" s="44" t="n"/>
+      <c r="I19" s="44" t="n"/>
+      <c r="J19" s="44" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="49" t="inlineStr">
+      <c r="A20" s="44" t="inlineStr">
         <is>
           <t>Jornada completa del convenio (horas/semana)</t>
         </is>
       </c>
-      <c r="B20" s="71" t="n">
+      <c r="B20" s="65" t="n">
         <v>40</v>
       </c>
-      <c r="J20" s="72" t="inlineStr">
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+      <c r="F20" s="44" t="n"/>
+      <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
+      <c r="I20" s="44" t="n"/>
+      <c r="J20" s="55" t="inlineStr">
         <is>
           <t>Art. 34.1 del Estatuto de los Trabajadores; tu convenio provincial puede fijar menos</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="49" t="inlineStr">
+      <c r="A21" s="44" t="inlineStr">
         <is>
           <t>Semanas trabajadas al año por persona</t>
         </is>
       </c>
-      <c r="B21" s="71" t="n">
+      <c r="B21" s="65" t="n">
         <v>46</v>
       </c>
-      <c r="J21" s="72" t="inlineStr">
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+      <c r="F21" s="44" t="n"/>
+      <c r="G21" s="44" t="n"/>
+      <c r="H21" s="44" t="n"/>
+      <c r="I21" s="44" t="n"/>
+      <c r="J21" s="55" t="inlineStr">
         <is>
           <t>52 semanas menos las vacaciones del art. 38 ET (30 días naturales)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="49" t="inlineStr">
+      <c r="A22" s="44" t="inlineStr">
         <is>
           <t>Horas de servicio al día que hay que cubrir</t>
         </is>
       </c>
-      <c r="B22" s="73" t="n">
+      <c r="B22" s="62" t="n">
         <v>13</v>
       </c>
-      <c r="J22" s="74" t="inlineStr">
+      <c r="C22" s="44" t="n"/>
+      <c r="D22" s="44" t="n"/>
+      <c r="E22" s="44" t="n"/>
+      <c r="F22" s="44" t="n"/>
+      <c r="G22" s="44" t="n"/>
+      <c r="H22" s="44" t="n"/>
+      <c r="I22" s="44" t="n"/>
+      <c r="J22" s="60" t="inlineStr">
         <is>
           <t>De la apertura al cierre, barra incluida. Cuéntalas sobre tu horario real</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="49" t="inlineStr">
+      <c r="A23" s="44" t="inlineStr">
         <is>
           <t>Personas necesarias a la vez en cada franja</t>
         </is>
       </c>
-      <c r="B23" s="73" t="n">
+      <c r="B23" s="62" t="n">
         <v>2</v>
       </c>
-      <c r="J23" s="74" t="inlineStr">
+      <c r="C23" s="44" t="n"/>
+      <c r="D23" s="44" t="n"/>
+      <c r="E23" s="44" t="n"/>
+      <c r="F23" s="44" t="n"/>
+      <c r="G23" s="44" t="n"/>
+      <c r="H23" s="44" t="n"/>
+      <c r="I23" s="44" t="n"/>
+      <c r="J23" s="60" t="inlineStr">
         <is>
           <t>Media de presencia simultánea entre cocina, barra y sala. En los dos servicios fuertes hará falta más y a media tarde menos</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="49" t="inlineStr">
+      <c r="A24" s="44" t="inlineStr">
         <is>
           <t>Horas de servicio a cubrir al año</t>
         </is>
       </c>
-      <c r="B24" s="58">
+      <c r="B24" s="55">
         <f>IFERROR(B22*B23*'0. Supuestos'!$B$6,"")</f>
         <v>8060.0</v>
       </c>
+      <c r="C24" s="44" t="n"/>
+      <c r="D24" s="44" t="n"/>
+      <c r="E24" s="44" t="n"/>
+      <c r="F24" s="44" t="n"/>
+      <c r="G24" s="44" t="n"/>
+      <c r="H24" s="44" t="n"/>
+      <c r="I24" s="44" t="n"/>
+      <c r="J24" s="44" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="49" t="inlineStr">
+      <c r="A25" s="44" t="inlineStr">
         <is>
           <t>Horas contratadas al año</t>
         </is>
       </c>
-      <c r="B25" s="58">
+      <c r="B25" s="55">
         <f>IFERROR(IF(I13="","",I13),"")</f>
         <v>9936.0</v>
       </c>
+      <c r="C25" s="44" t="n"/>
+      <c r="D25" s="44" t="n"/>
+      <c r="E25" s="44" t="n"/>
+      <c r="F25" s="44" t="n"/>
+      <c r="G25" s="44" t="n"/>
+      <c r="H25" s="44" t="n"/>
+      <c r="I25" s="44" t="n"/>
+      <c r="J25" s="44" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Cobertura (contratadas / necesarias)</t>
         </is>
       </c>
-      <c r="B26" s="57">
+      <c r="B26" s="43">
         <f>IFERROR(B25/B24,"")</f>
         <v>1.2327543424317617</v>
       </c>
-      <c r="J26" s="30" t="inlineStr">
+      <c r="C26" s="44" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="44" t="n"/>
+      <c r="F26" s="44" t="n"/>
+      <c r="G26" s="44" t="n"/>
+      <c r="H26" s="44" t="n"/>
+      <c r="I26" s="44" t="n"/>
+      <c r="J26" s="41" t="inlineStr">
         <is>
           <t>Por debajo del 100 % la plantilla no llega a cubrir el horario que declara el plan: o se contrata más o se recorta el horario</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
+    <row r="27">
+      <c r="A27" s="44" t="n"/>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="44" t="n"/>
+      <c r="D27" s="44" t="n"/>
+      <c r="E27" s="44" t="n"/>
+      <c r="F27" s="44" t="n"/>
+      <c r="G27" s="44" t="n"/>
+      <c r="H27" s="44" t="n"/>
+      <c r="I27" s="44" t="n"/>
+      <c r="J27" s="44" t="n"/>
+    </row>
     <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="31" t="inlineStr">
+      <c r="A28" s="63" t="inlineStr">
         <is>
           <t>Las columnas «Bruto mes», «Seg. Social», «Coste mes» y «Coste año» son TOTALES de la fila: en un puesto con dos personas incluyen a las dos. «Jornada» es el porcentaje sobre la jornada completa del convenio y sirve para comparar el salario con el suelo legal en proporción. El tipo de Seguridad Social y el número de pagas están en la hoja «0. Supuestos».</t>
         </is>
       </c>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="44" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="44" t="n"/>
+      <c r="F28" s="44" t="n"/>
+      <c r="G28" s="44" t="n"/>
+      <c r="H28" s="44" t="n"/>
+      <c r="I28" s="44" t="n"/>
+      <c r="J28" s="44" t="n"/>
     </row>
     <row r="29" ht="150" customHeight="1">
-      <c r="A29" s="31" t="inlineStr">
+      <c r="A29" s="63" t="inlineStr">
         <is>
           <t>El suelo salarial es el MAYOR entre el SMI y el salario de convenio, los dos en la hoja «0. Supuestos»; las jornadas parciales lo llevan en proporción. El convenio aplicable es el PROVINCIAL de hostelería: no existe una tabla salarial estatal única, así que la celda del convenio se entrega vacía para que copies la de tu provincia.</t>
         </is>
       </c>
+      <c r="B29" s="44" t="n"/>
+      <c r="C29" s="44" t="n"/>
+      <c r="D29" s="44" t="n"/>
+      <c r="E29" s="44" t="n"/>
+      <c r="F29" s="44" t="n"/>
+      <c r="G29" s="44" t="n"/>
+      <c r="H29" s="44" t="n"/>
+      <c r="I29" s="44" t="n"/>
+      <c r="J29" s="44" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="44" t="inlineStr">
         <is>
           <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
         </is>
       </c>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="44" t="n"/>
+      <c r="D30" s="44" t="n"/>
+      <c r="E30" s="44" t="n"/>
+      <c r="F30" s="44" t="n"/>
+      <c r="G30" s="44" t="n"/>
+      <c r="H30" s="44" t="n"/>
+      <c r="I30" s="44" t="n"/>
+      <c r="J30" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -6627,7 +7063,7 @@
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="63" t="inlineStr">
         <is>
-          <t>3. Sólo «3. Punto de Equilibrio» se deriva entera de lo anterior. En las otras tres hojas sí hay celdas verdes que puedes tocar: el escenario pesimista y el optimista en «4. Escenarios», la estacionalidad y la rampa de arranque en «6. Tesorería 12 meses», y las cuatro fuentes alternativas de financiación en «7. Financiación». Todo lo demás se calcula.</t>
+          <t>3. Sólo «3. Punto Equilibrio» se deriva entera de lo anterior. En las otras tres hojas sí hay celdas verdes que puedes tocar: el escenario pesimista y el optimista en «4. Escenarios», la estacionalidad y la rampa de arranque en «6. Tesorería 12 meses», y las cuatro fuentes alternativas de financiación en «7. Financiación». Todo lo demás se calcula.</t>
         </is>
       </c>
       <c r="B7" s="44" t="n"/>
@@ -6635,10 +7071,10 @@
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="44" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="105" customHeight="1">
       <c r="A8" s="63" t="inlineStr">
         <is>
-          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide entre 1,10 en comida y entre 1,21 en bebida alcohólica; el IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
+          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide entre 1,10: en sala, la comida y la bebida (alcohol incluido) van al tipo reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA). El 21 % es el tipo general y en hostelería sólo alcanza a lo que sale del local como entrega de bienes excluida del tipo reducido: el alcohol y los refrescos o zumos con azúcares añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica al alcohol del canal de delivery. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
         </is>
       </c>
       <c r="B8" s="44" t="n"/>
@@ -6948,564 +7384,630 @@
       </c>
       <c r="B30" s="60">
         <f>IFERROR(IF('6. Tesorería 12 meses'!$B$31="","",'6. Tesorería 12 meses'!$B$31),"")</f>
-        <v>2.5818056068787465</v>
+        <v>2.7487932827490225</v>
       </c>
       <c r="C30" s="44" t="n"/>
       <c r="D30" s="44" t="n"/>
       <c r="E30" s="44" t="n"/>
     </row>
-    <row r="31"/>
+    <row r="31">
+      <c r="A31" s="44" t="n"/>
+      <c r="B31" s="44" t="n"/>
+      <c r="C31" s="44" t="n"/>
+      <c r="D31" s="44" t="n"/>
+      <c r="E31" s="44" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="41" t="inlineStr">
         <is>
           <t>QUÉ HA CAMBIADO RESPECTO DE LA VERSIÓN 1.1</t>
         </is>
       </c>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="44" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="44" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="30" t="inlineStr">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>v1.1</t>
         </is>
       </c>
-      <c r="C33" s="30" t="inlineStr">
-        <is>
-          <t>v2.0</t>
-        </is>
-      </c>
-      <c r="D33" s="30" t="inlineStr">
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>v2.1</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
         <is>
           <t>Por qué</t>
         </is>
       </c>
+      <c r="E33" s="44" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="75" t="inlineStr">
+      <c r="A34" s="79" t="inlineStr">
         <is>
           <t>Coste de personal imputado al P&amp;L</t>
         </is>
       </c>
-      <c r="B34" s="75" t="inlineStr">
+      <c r="B34" s="79" t="inlineStr">
         <is>
           <t>115.200 €</t>
         </is>
       </c>
-      <c r="C34" s="75" t="inlineStr">
+      <c r="C34" s="79" t="inlineStr">
         <is>
           <t>Sale de la hoja Personal, por fórmula</t>
         </is>
       </c>
-      <c r="D34" s="31" t="inlineStr">
-        <is>
-          <t>TEC-01/DOM-01: el P&amp;L decía «ver hoja Personal» y usaba otra cifra</t>
-        </is>
-      </c>
+      <c r="D34" s="63" t="inlineStr">
+        <is>
+          <t>El P&amp;L decía «ver hoja Personal» y usaba otra cifra; ahora lee la hoja</t>
+        </is>
+      </c>
+      <c r="E34" s="44" t="n"/>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="75" t="inlineStr">
+      <c r="A35" s="79" t="inlineStr">
         <is>
           <t>Plantilla</t>
         </is>
       </c>
-      <c r="B35" s="75" t="inlineStr">
+      <c r="B35" s="79" t="inlineStr">
         <is>
           <t>7 personas / 209.171 €</t>
         </is>
       </c>
-      <c r="C35" s="75" t="inlineStr">
-        <is>
-          <t>6 puestos (dos parciales) / ~147.100 €</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>§7-bis.17: dimensionada por horas de servicio para 56 plazas; con la plantilla anterior el coste laboral era el 66,3 % de las ventas</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="75" t="inlineStr">
+      <c r="C35" s="79" t="inlineStr">
+        <is>
+          <t>7 puestos, tres a tiempo parcial (uno de ellos, suplencias) / 151.939 €</t>
+        </is>
+      </c>
+      <c r="D35" s="63" t="inlineStr">
+        <is>
+          <t>Dimensionada por horas de servicio para 56 plazas; con la plantilla anterior el coste laboral era el 66,3 % de las ventas</t>
+        </is>
+      </c>
+      <c r="E35" s="44" t="n"/>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="79" t="inlineStr">
         <is>
           <t>Cubiertos/día del año 1</t>
         </is>
       </c>
-      <c r="B36" s="75" t="inlineStr">
+      <c r="B36" s="79" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="C36" s="75" t="inlineStr">
+      <c r="C36" s="79" t="inlineStr">
         <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D36" s="31" t="inlineStr">
-        <is>
-          <t>1,43 rotaciones sobre 56 plazas, por debajo del techo de 1,8 que usa el propio documento</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="75" t="inlineStr">
+      <c r="D36" s="63" t="inlineStr">
+        <is>
+          <t>1,43 rotaciones sobre las 56 plazas del propio pack; el documento pide un MÍNIMO de 1,8 en temporada alta, así que el caso base se proyecta por debajo a propósito</t>
+        </is>
+      </c>
+      <c r="E36" s="44" t="n"/>
+    </row>
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="79" t="inlineStr">
         <is>
           <t>Ticket medio</t>
         </is>
       </c>
-      <c r="B37" s="75" t="inlineStr">
+      <c r="B37" s="79" t="inlineStr">
         <is>
           <t>18,50 € (sin declarar IVA)</t>
         </is>
       </c>
-      <c r="C37" s="75" t="inlineStr">
-        <is>
-          <t>17,20 € SIN IVA</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>TEC-11/DOM-30: equivale a 19,58 € de PVP, dentro del rango 15-22 € del propio libro</t>
-        </is>
-      </c>
+      <c r="C37" s="79" t="inlineStr">
+        <is>
+          <t>18,20 € SIN IVA</t>
+        </is>
+      </c>
+      <c r="D37" s="63" t="inlineStr">
+        <is>
+          <t>El ticket de la versión 1.1 no decía si llevaba IVA; ahora se declara sin IVA y equivale a 20,02 € de PVP al 10 % en sala, dentro del rango 15-22 € del propio libro</t>
+        </is>
+      </c>
+      <c r="E37" s="44" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="75" t="inlineStr">
+      <c r="A38" s="79" t="inlineStr">
         <is>
           <t>Alquiler</t>
         </is>
       </c>
-      <c r="B38" s="75" t="inlineStr">
+      <c r="B38" s="79" t="inlineStr">
         <is>
           <t>3.000 €/mes</t>
         </is>
       </c>
-      <c r="C38" s="75" t="inlineStr">
-        <is>
-          <t>2.900 €/mes</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="inlineStr">
-        <is>
-          <t>Con 3.000 € el ratio alquiler/ventas incumplía el techo de 8-10 % que fija el propio libro</t>
-        </is>
-      </c>
+      <c r="C38" s="79" t="inlineStr">
+        <is>
+          <t>3.000 €/mes (sin cambio)</t>
+        </is>
+      </c>
+      <c r="D38" s="63" t="inlineStr">
+        <is>
+          <t>Con el ticket recalibrado son el 8,0 % de las ventas, dentro del techo de 8-10 % del propio libro</t>
+        </is>
+      </c>
+      <c r="E38" s="44" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="75" t="inlineStr">
+      <c r="A39" s="79" t="inlineStr">
         <is>
           <t>Suministros</t>
         </is>
       </c>
-      <c r="B39" s="75" t="inlineStr">
+      <c r="B39" s="79" t="inlineStr">
         <is>
           <t>1.200 €/mes</t>
         </is>
       </c>
-      <c r="C39" s="75" t="inlineStr">
+      <c r="C39" s="79" t="inlineStr">
         <is>
           <t>1.800 €/mes</t>
         </is>
       </c>
-      <c r="D39" s="31" t="inlineStr">
-        <is>
-          <t>Una cocina con horno, cámaras y campana no consume el 3,4 % de las ventas</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="75" t="inlineStr">
+      <c r="D39" s="63" t="inlineStr">
+        <is>
+          <t>Una cocina con horno, cámaras y campana no consume el 3,2 % de las ventas</t>
+        </is>
+      </c>
+      <c r="E39" s="44" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="79" t="inlineStr">
         <is>
           <t>Fondo de maniobra</t>
         </is>
       </c>
-      <c r="B40" s="75" t="inlineStr">
+      <c r="B40" s="79" t="inlineStr">
         <is>
           <t>30.000 € etiquetados «3 meses»</t>
         </is>
       </c>
-      <c r="C40" s="75" t="inlineStr">
+      <c r="C40" s="79" t="inlineStr">
         <is>
           <t>3 × costes fijos de caja mensuales, por fórmula</t>
         </is>
       </c>
-      <c r="D40" s="31" t="inlineStr">
-        <is>
-          <t>TEC-07/DOM-12/NUEVO-01: los 30.000 € cubrían 1,8 meses</t>
-        </is>
-      </c>
+      <c r="D40" s="63" t="inlineStr">
+        <is>
+          <t>Los 30.000 € cubrían 1,8 meses, no 3</t>
+        </is>
+      </c>
+      <c r="E40" s="44" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="75" t="inlineStr">
+      <c r="A41" s="79" t="inlineStr">
         <is>
           <t>Amortización</t>
         </is>
       </c>
-      <c r="B41" s="75" t="inlineStr">
+      <c r="B41" s="79" t="inlineStr">
         <is>
           <t>5.000 €/año (base implícita 50.000 €)</t>
         </is>
       </c>
-      <c r="C41" s="75" t="inlineStr">
+      <c r="C41" s="79" t="inlineStr">
         <is>
           <t>Base amortizable real / vida útil, por fórmula</t>
         </is>
       </c>
-      <c r="D41" s="31" t="inlineStr">
-        <is>
-          <t>TEC-20: el inmovilizado del propio libro suma bastante más, y el fondo de maniobra no se amortiza</t>
-        </is>
-      </c>
+      <c r="D41" s="63" t="inlineStr">
+        <is>
+          <t>El inmovilizado del propio libro suma bastante más, y el fondo de maniobra no se amortiza</t>
+        </is>
+      </c>
+      <c r="E41" s="44" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="75" t="inlineStr">
+      <c r="A42" s="79" t="inlineStr">
         <is>
           <t>Cuota del préstamo en el P&amp;L</t>
         </is>
       </c>
-      <c r="B42" s="75" t="inlineStr">
+      <c r="B42" s="79" t="inlineStr">
         <is>
           <t>7.200 €/año de cuota completa</t>
         </is>
       </c>
-      <c r="C42" s="75" t="inlineStr">
+      <c r="C42" s="79" t="inlineStr">
         <is>
           <t>sólo los intereses; el principal va a tesorería</t>
         </is>
       </c>
-      <c r="D42" s="31" t="inlineStr">
-        <is>
-          <t>TEC-10/DOM-15: meter la cuota entera antes del resultado convierte el P&amp;L en un flujo de caja</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="75" t="inlineStr">
+      <c r="D42" s="63" t="inlineStr">
+        <is>
+          <t>Meter la cuota entera antes del resultado convierte el P&amp;L en un flujo de caja</t>
+        </is>
+      </c>
+      <c r="E42" s="44" t="n"/>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="79" t="inlineStr">
         <is>
           <t>Impuesto de Sociedades</t>
         </is>
       </c>
-      <c r="B43" s="75" t="inlineStr">
+      <c r="B43" s="79" t="inlineStr">
         <is>
           <t>25 % en los años 2 y 3, sin compensar la BIN</t>
         </is>
       </c>
-      <c r="C43" s="75" t="inlineStr">
+      <c r="C43" s="79" t="inlineStr">
         <is>
           <t>15 % los dos primeros ejercicios con base positiva y compensación de bases negativas</t>
         </is>
       </c>
-      <c r="D43" s="31" t="inlineStr">
-        <is>
-          <t>TEC-06/DOM-15: arts. 26 y 29.1 LIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="75" t="inlineStr">
+      <c r="D43" s="63" t="inlineStr">
+        <is>
+          <t>Artículos 26 y 29.1 de la Ley del Impuesto sobre Sociedades</t>
+        </is>
+      </c>
+      <c r="E43" s="44" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" s="79" t="inlineStr">
         <is>
           <t>Comisiones de delivery</t>
         </is>
       </c>
-      <c r="B44" s="75" t="inlineStr">
+      <c r="B44" s="79" t="inlineStr">
         <is>
           <t>5 % de TODA la facturación, sin interruptor</t>
         </is>
       </c>
-      <c r="C44" s="75" t="inlineStr">
+      <c r="C44" s="79" t="inlineStr">
         <is>
           <t>% del canal × comisión de la plataforma, a 0 por defecto</t>
         </is>
       </c>
-      <c r="D44" s="31" t="inlineStr">
-        <is>
-          <t>TEC-23/DOM-34</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="75" t="inlineStr">
+      <c r="D44" s="63" t="inlineStr">
+        <is>
+          <t>Si no repartes, no arrastras un coste inventado</t>
+        </is>
+      </c>
+      <c r="E44" s="44" t="n"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" s="79" t="inlineStr">
         <is>
           <t>Coste de la bebida</t>
         </is>
       </c>
-      <c r="B45" s="75" t="inlineStr">
+      <c r="B45" s="79" t="inlineStr">
         <is>
           <t>food cost del 30 % sobre el total MÁS un 22 % sobre la bebida</t>
         </is>
       </c>
-      <c r="C45" s="75" t="inlineStr">
+      <c r="C45" s="79" t="inlineStr">
         <is>
           <t>cada familia paga su propio coste</t>
         </is>
       </c>
-      <c r="D45" s="31" t="inlineStr">
-        <is>
-          <t>TEC-04/DOM-04: 33.119,63 € cobrados dos veces en el año 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="46"/>
+      <c r="D45" s="63" t="inlineStr">
+        <is>
+          <t>33.119,63 € cobrados dos veces en el año 1</t>
+        </is>
+      </c>
+      <c r="E45" s="44" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="44" t="n"/>
+      <c r="B46" s="44" t="n"/>
+      <c r="C46" s="44" t="n"/>
+      <c r="D46" s="44" t="n"/>
+      <c r="E46" s="44" t="n"/>
+    </row>
     <row r="47">
-      <c r="A47" s="30" t="inlineStr">
+      <c r="A47" s="41" t="inlineStr">
         <is>
           <t>DATOS DE REFERENCIA DEL SECTOR</t>
         </is>
       </c>
+      <c r="B47" s="44" t="n"/>
+      <c r="C47" s="44" t="n"/>
+      <c r="D47" s="44" t="n"/>
+      <c r="E47" s="44" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="30" t="inlineStr">
+      <c r="A48" s="41" t="inlineStr">
         <is>
           <t>Referencia</t>
         </is>
       </c>
-      <c r="B48" s="30" t="inlineStr">
+      <c r="B48" s="41" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="C48" s="30" t="inlineStr">
+      <c r="C48" s="41" t="inlineStr">
         <is>
           <t>Fuente</t>
         </is>
       </c>
-      <c r="D48" s="30" t="inlineStr">
+      <c r="D48" s="41" t="inlineStr">
         <is>
           <t>Nota</t>
         </is>
       </c>
+      <c r="E48" s="44" t="n"/>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>Ticket medio de restaurante casual (PVP)</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="44" t="inlineStr">
         <is>
           <t>15-22 €</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D49" s="31" t="inlineStr">
+      <c r="D49" s="63" t="inlineStr">
         <is>
           <t>El PVP equivalente de este plan lo calcula la hoja 0. Supuestos</t>
         </is>
       </c>
+      <c r="E49" s="44" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="44" t="inlineStr">
         <is>
           <t>Alquiler de local de 80-120 m² en zona urbana</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="44" t="inlineStr">
         <is>
           <t>2.000-4.500 €/mes</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D50" s="31" t="n"/>
+      <c r="D50" s="63" t="n"/>
+      <c r="E50" s="44" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="44" t="inlineStr">
         <is>
           <t>Food cost objetivo</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="44" t="inlineStr">
         <is>
           <t>28-32 %</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D51" s="31" t="n"/>
+      <c r="D51" s="63" t="n"/>
+      <c r="E51" s="44" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="44" t="inlineStr">
         <is>
           <t>Coste de personal sobre ventas</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="44" t="inlineStr">
         <is>
           <t>máx. 34 %</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D52" s="31" t="inlineStr">
+      <c r="D52" s="63" t="inlineStr">
         <is>
           <t>Se aplica el más estricto de los techos que publica este producto</t>
         </is>
       </c>
+      <c r="E52" s="44" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="44" t="inlineStr">
         <is>
           <t>Margen neto medio del sector</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="44" t="inlineStr">
         <is>
           <t>5-10 %</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D53" s="31" t="n"/>
+      <c r="D53" s="63" t="n"/>
+      <c r="E53" s="44" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="44" t="inlineStr">
         <is>
           <t>Punto de equilibrio</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="44" t="inlineStr">
         <is>
           <t>alcanzable en menos de 12 meses</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D54" s="31" t="n"/>
+      <c r="D54" s="63" t="n"/>
+      <c r="E54" s="44" t="n"/>
     </row>
     <row r="55" ht="75" customHeight="1">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="44" t="inlineStr">
         <is>
           <t>Inversión media de apertura</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="44" t="inlineStr">
         <is>
           <t>80.000-150.000 €</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D55" s="31" t="inlineStr">
+      <c r="D55" s="63" t="inlineStr">
         <is>
           <t>Es el rango de referencia del sector. La inversión de ESTE plan la calcula la hoja 1: si queda por encima, es porque incluye el fondo de maniobra, las existencias iniciales y el IVA que hay que adelantar, que ese rango no siempre cuenta</t>
         </is>
       </c>
+      <c r="E55" s="44" t="n"/>
     </row>
     <row r="56" ht="45" customHeight="1">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="44" t="inlineStr">
         <is>
           <t>Tasa de cierre de restaurantes en el primer año</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="44" t="inlineStr">
         <is>
           <t>25 %</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D56" s="31" t="inlineStr">
+      <c r="D56" s="63" t="inlineStr">
         <is>
           <t>Es el dato que más pesa en un comité de riesgos: por eso el plan lleva fondo de maniobra, escenario pesimista y tesorería mes a mes</t>
         </is>
       </c>
+      <c r="E56" s="44" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="44" t="inlineStr">
         <is>
           <t>Tasa de cierre de restaurantes a los cinco años</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="44" t="inlineStr">
         <is>
           <t>50 %</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="44" t="inlineStr">
         <is>
           <t>Fichero v1.1</t>
         </is>
       </c>
-      <c r="D57" s="31" t="n"/>
+      <c r="D57" s="63" t="n"/>
+      <c r="E57" s="44" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="44" t="inlineStr">
         <is>
           <t>Convenio colectivo aplicable</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="44" t="inlineStr">
         <is>
           <t>PROVINCIAL de hostelería</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="44" t="inlineStr">
         <is>
           <t>DOM-24 / checklist F37</t>
         </is>
       </c>
-      <c r="D58" s="31" t="inlineStr">
+      <c r="D58" s="63" t="inlineStr">
         <is>
           <t>No existe una tabla salarial estatal única: copia la tabla de tu provincia en la celda de Supuestos</t>
         </is>
       </c>
-    </row>
-    <row r="59"/>
+      <c r="E58" s="44" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="44" t="n"/>
+      <c r="B59" s="44" t="n"/>
+      <c r="C59" s="44" t="n"/>
+      <c r="D59" s="44" t="n"/>
+      <c r="E59" s="44" t="n"/>
+    </row>
     <row r="60">
-      <c r="A60" s="76" t="inlineStr">
+      <c r="A60" s="80" t="inlineStr">
         <is>
           <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
         </is>
       </c>
+      <c r="B60" s="44" t="n"/>
+      <c r="C60" s="44" t="n"/>
+      <c r="D60" s="44" t="n"/>
+      <c r="E60" s="44" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="76" t="inlineStr">
+      <c r="A61" s="80" t="inlineStr">
         <is>
           <t>Más plantillas y kits del catálogo en aichef.pro/productos-digitales</t>
         </is>
       </c>
+      <c r="B61" s="44" t="n"/>
+      <c r="C61" s="44" t="n"/>
+      <c r="D61" s="44" t="n"/>
+      <c r="E61" s="44" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="76" t="inlineStr">
+      <c r="A62" s="80" t="inlineStr">
         <is>
           <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
         </is>
       </c>
+      <c r="B62" s="44" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="44" t="n"/>
+      <c r="E62" s="44" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="76" t="inlineStr">
-        <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/plan-negocio-bar-restaurante · info@aichef.pro</t>
-        </is>
-      </c>
+      <c r="A63" s="80" t="inlineStr">
+        <is>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/plan-negocio-bar-restaurante · info@aichef.pro</t>
+        </is>
+      </c>
+      <c r="B63" s="44" t="n"/>
+      <c r="C63" s="44" t="n"/>
+      <c r="D63" s="44" t="n"/>
+      <c r="E63" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -7893,56 +8395,56 @@
         </is>
       </c>
       <c r="B9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*B7*(1-MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>21756.56940158745</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*B7*(1-MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>21309.07874788193</v>
       </c>
       <c r="C9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(C7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+B7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>26040.07059805583</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(C7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+B7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>25504.476589672704</v>
       </c>
       <c r="D9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(D7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+C7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>33827.227126727914</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(D7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+C7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>33131.4663337198</v>
       </c>
       <c r="E9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(E7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+D7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>39387.86720235442</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(E7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+D7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>38577.7347721395</v>
       </c>
       <c r="F9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(F7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+E7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>46282.156727013295</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(F7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+E7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>45330.2220636761</v>
       </c>
       <c r="G9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(G7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+F7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>49729.30148934273</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(G7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+F7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>48706.465709444405</v>
       </c>
       <c r="H9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(H7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+G7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>48033.98439311514</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(H7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+G7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>47046.01801480426</v>
       </c>
       <c r="I9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(I7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+H7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>35036.553322036925</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(I7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+H7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>34315.9190225631</v>
       </c>
       <c r="J9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(J7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+I7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>48033.98439311514</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(J7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+I7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>47046.01801480426</v>
       </c>
       <c r="K9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(K7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+J7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>49729.30148934273</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(K7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+J7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>48706.465709444405</v>
       </c>
       <c r="L9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(L7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+K7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>49164.1957906002</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(L7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+K7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>48152.98314456435</v>
       </c>
       <c r="M9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(M7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+L7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
-        <v>59901.20406670829</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(M7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+L7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <v>58669.1518772853</v>
       </c>
       <c r="N9" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B9:M9)),"")</f>
-        <v>506922.4160000001</v>
+        <v>496496.00000000023</v>
       </c>
       <c r="O9" s="44" t="inlineStr">
         <is>
@@ -8290,60 +8792,60 @@
         </is>
       </c>
       <c r="B16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*B7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>2384.6796307856957</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*B7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>1937.1889770801754</v>
       </c>
       <c r="C16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*C7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>2854.1827892624633</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*C7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>2318.588780879337</v>
       </c>
       <c r="D16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*D7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>3707.7122778917337</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*D7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>3011.9514848836184</v>
       </c>
       <c r="E16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*E7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>4317.199227682156</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*E7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>3507.066797467227</v>
       </c>
       <c r="F16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*F7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>5072.8639418532075</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*F7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>4120.92927851601</v>
       </c>
       <c r="G16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*G7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>5450.696298938732</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*G7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>4427.8605190404005</v>
       </c>
       <c r="H16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*H7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>5264.877106929458</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*H7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>4276.910728618569</v>
       </c>
       <c r="I16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*I7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>3840.2633015250162</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*I7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>3119.6290020511915</v>
       </c>
       <c r="J16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*J7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>5264.877106929458</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*J7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>4276.910728618569</v>
       </c>
       <c r="K16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*K7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>5450.696298938732</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*K7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>4427.8605190404005</v>
       </c>
       <c r="L16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*L7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>5388.756568268975</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*L7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>4377.543922233123</v>
       </c>
       <c r="M16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*M7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
-        <v>6565.611450994383</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*M7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <v>5333.559261571391</v>
       </c>
       <c r="N16" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B16:M16)),"")</f>
-        <v>55562.41600000001</v>
+        <v>45136.000000000015</v>
       </c>
       <c r="O16" s="44" t="inlineStr">
         <is>
-          <t>La bebida NO va toda al tipo general: sólo la alcohólica. El peso está en la hoja de Supuestos</t>
+          <t>La bebida va al tipo que sale de la hoja de Supuestos: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por delivery, al general</t>
         </is>
       </c>
     </row>
@@ -8428,13 +8930,13 @@
       <c r="G18" s="44" t="n"/>
       <c r="H18" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",MAX(0,-E19)),"")</f>
-        <v>20952.371755583692</v>
+        <v>22631.217210680457</v>
       </c>
       <c r="I18" s="44" t="n"/>
       <c r="J18" s="44" t="n"/>
       <c r="K18" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",MAX(0,-H19)),"")</f>
-        <v>15173.589372849365</v>
+        <v>19637.337701396587</v>
       </c>
       <c r="L18" s="44" t="n"/>
       <c r="M18" s="44" t="n"/>
@@ -8456,19 +8958,19 @@
       <c r="D19" s="44" t="n"/>
       <c r="E19" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B16:D16)-SUM(B17:D17)-E18),"")</f>
-        <v>-20952.371755583692</v>
+        <v>-22631.217210680457</v>
       </c>
       <c r="F19" s="44" t="n"/>
       <c r="G19" s="44" t="n"/>
       <c r="H19" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(E16:G16)-SUM(E17:G17)-H18),"")</f>
-        <v>-15173.589372849365</v>
+        <v>-19637.337701396587</v>
       </c>
       <c r="I19" s="44" t="n"/>
       <c r="J19" s="44" t="n"/>
       <c r="K19" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(H16:J16)-SUM(H17:J17)-K18),"")</f>
-        <v>-9713.993743490582</v>
+        <v>-16874.309128133405</v>
       </c>
       <c r="L19" s="44" t="n"/>
       <c r="M19" s="44" t="n"/>
@@ -8524,55 +9026,55 @@
       </c>
       <c r="B21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B9:B15)+IF(B20="",0,B20)),"")</f>
-        <v>1869.1027349207834</v>
+        <v>1421.6120812152622</v>
       </c>
       <c r="C21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(C9:C15)+IF(C20="",0,C20)),"")</f>
-        <v>-717.2880818098056</v>
+        <v>-1252.882090192932</v>
       </c>
       <c r="D21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(D9:D15)+IF(D20="",0,D20)),"")</f>
-        <v>5717.302694653235</v>
+        <v>5021.5419016451215</v>
       </c>
       <c r="E21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(E9:E15)+IF(E20="",0,E20)),"")</f>
-        <v>8819.056745815282</v>
+        <v>8008.9243156003595</v>
       </c>
       <c r="F21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(F9:F15)+IF(F20="",0,F20)),"")</f>
-        <v>13957.50893515265</v>
+        <v>13005.574271815452</v>
       </c>
       <c r="G21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(G9:G15)+IF(G20="",0,G20)),"")</f>
-        <v>15227.70090368917</v>
+        <v>14204.865123790843</v>
       </c>
       <c r="H21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(H9:H15)+IF(H20="",0,H20)),"")</f>
-        <v>1591.1074105651169</v>
+        <v>603.1410322542324</v>
       </c>
       <c r="I21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(I9:I15)+IF(I20="",0,I20)),"")</f>
-        <v>-18.20739974434764</v>
+        <v>-738.8416992181701</v>
       </c>
       <c r="J21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(J9:J15)+IF(J20="",0,J20)),"")</f>
-        <v>17083.31500389429</v>
+        <v>16095.348625583407</v>
       </c>
       <c r="K21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(K9:K15)+IF(K20="",0,K20)),"")</f>
-        <v>14674.540767561464</v>
+        <v>13651.70498766313</v>
       </c>
       <c r="L21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(L9:L15)+IF(L20="",0,L20)),"")</f>
-        <v>13574.118808050183</v>
+        <v>12562.906162014327</v>
       </c>
       <c r="M21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(M9:M15)+IF(M20="",0,M20)),"")</f>
-        <v>13636.765837747855</v>
+        <v>12404.713648324865</v>
       </c>
       <c r="N21" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B21:M21)),"")</f>
-        <v>105415.02436049587</v>
+        <v>94988.6083604959</v>
       </c>
       <c r="O21" s="44" t="n"/>
     </row>
@@ -8584,51 +9086,51 @@
       </c>
       <c r="B22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'1. Inversión Inicial'!$B$47+B21),"")</f>
-        <v>62673.90273492079</v>
+        <v>62226.41208121527</v>
       </c>
       <c r="C22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",B22+C21),"")</f>
-        <v>61956.614653110984</v>
+        <v>60973.52999102234</v>
       </c>
       <c r="D22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",C22+D21),"")</f>
-        <v>67673.91734776422</v>
+        <v>65995.07189266746</v>
       </c>
       <c r="E22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",D22+E21),"")</f>
-        <v>76492.9740935795</v>
+        <v>74003.99620826782</v>
       </c>
       <c r="F22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",E22+F21),"")</f>
-        <v>90450.48302873215</v>
+        <v>87009.57048008328</v>
       </c>
       <c r="G22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",F22+G21),"")</f>
-        <v>105678.18393242132</v>
+        <v>101214.43560387412</v>
       </c>
       <c r="H22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",G22+H21),"")</f>
-        <v>107269.29134298644</v>
+        <v>101817.57663612836</v>
       </c>
       <c r="I22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",H22+I21),"")</f>
-        <v>107251.08394324209</v>
+        <v>101078.73493691019</v>
       </c>
       <c r="J22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",I22+J21),"")</f>
-        <v>124334.39894713639</v>
+        <v>117174.08356249359</v>
       </c>
       <c r="K22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",J22+K21),"")</f>
-        <v>139008.93971469786</v>
+        <v>130825.78855015672</v>
       </c>
       <c r="L22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",K22+L21),"")</f>
-        <v>152583.05852274803</v>
+        <v>143388.69471217104</v>
       </c>
       <c r="M22" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",L22+M21),"")</f>
-        <v>166219.8243604959</v>
+        <v>155793.4083604959</v>
       </c>
       <c r="N22" s="44" t="n"/>
       <c r="O22" s="44" t="n"/>
@@ -8641,7 +9143,7 @@
       </c>
       <c r="B23" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",IF(COUNT(B22:M22)=0,"",MIN(B22:M22))),"")</f>
-        <v>61956.614653110984</v>
+        <v>60973.52999102234</v>
       </c>
       <c r="C23" s="44" t="n"/>
       <c r="D23" s="44" t="inlineStr">
@@ -8718,7 +9220,7 @@
       </c>
       <c r="B26" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",N21),"")</f>
-        <v>105415.02436049587</v>
+        <v>94988.6083604959</v>
       </c>
       <c r="C26" s="44" t="n"/>
       <c r="D26" s="44" t="inlineStr">
@@ -8858,7 +9360,7 @@
       </c>
       <c r="B31" s="61">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",IF(B26&gt;=B30,B30/B26,IF(B26+B27&gt;=B30,1+(B30-B26)/B27,IF(B26+B27+B28&gt;=B30,2+(B30-B26-B27)/B28,"Más de 3 años")))),"")</f>
-        <v>2.5818056068787465</v>
+        <v>2.7487932827490225</v>
       </c>
       <c r="C31" s="44" t="n"/>
       <c r="D31" s="41" t="inlineStr">
@@ -9549,10 +10051,10 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <conditionalFormatting sqref="N5">
     <cfRule type="expression" priority="1" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(N5),N5&lt;&gt;1)</formula>
+      <formula>AND(ISNUMBER(N5),ABS(N5-1)&gt;=0.005)</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
-      <formula>AND(ISNUMBER(N5),N5=1)</formula>
+      <formula>AND(ISNUMBER(N5),ABS(N5-1)&lt;0.005)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:M22">

--- a/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
+++ b/astro-site/public/dl/plan-negocio-bar-restaurante/plan-financiero-bar-restaurante.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -400,6 +400,9 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -915,12 +918,12 @@
         </is>
       </c>
       <c r="B9" s="35">
-        <f>IFERROR(IF($B$5="","",$B$5*(B11*(1+$B$39)+B12*(1+($B$62*((1-$B$16)*$B$63+$B$16*$B$40)+(1-$B$62)*$B$39)))),"")</f>
+        <f>IFERROR(IF($B$5="","",$B$5*(1+SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))),"")</f>
         <v>20.02</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Ticket sin IVA más el IVA: "&amp;TEXT($B$39*100,"0")&amp;" % en comida y "&amp;TEXT(($B$62*((1-$B$16)*$B$63+$B$16*$B$40)+(1-$B$62)*$B$39)*100,"0")&amp;" % en bebida"&amp;IF(ABS(($B$62*((1-$B$16)*$B$63+$B$16*$B$40)+(1-$B$62)*$B$39)-$B$39)&lt;0.00001,"","; el de bebida es un tipo MEDIO ponderado por el peso del alcohol, su tipo y el canal de delivery, no un tipo de la ley, y aquí va redondeado")&amp;". Compáralo con el rango del sector, que va con IVA.","")</f>
-        <v>Ticket sin IVA más el IVA: 10 % en comida y 10 % en bebida. Compáralo con el rango del sector, que va con IVA.</v>
+        <f>IFERROR("Ticket sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)*100,"0")&amp;" %. En sala todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por delivery y el pan común, si los tienes, mueven la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
+        <v>Ticket sin IVA más el IVA medio ponderado de tus líneas de venta: 10 %. En sala todo va al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992, alcohol incluido); el alcohol que sale por delivery y el pan común, si los tienes, mueven la media. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.</v>
       </c>
     </row>
     <row r="10">
@@ -952,7 +955,7 @@
         </is>
       </c>
       <c r="B12" s="36">
-        <f>IFERROR(1-B11,"")</f>
+        <f>IFERROR(IF(COUNT(B11)=0,"",1-B11),"")</f>
         <v>0.35</v>
       </c>
       <c r="C12" t="inlineStr">
@@ -1099,7 +1102,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SMI 2026 · RD 126/2026 · suelo legal por jornada completa</t>
+          <t>SMI 2026: 17.094 € al año (1.221 €/mes en 14 pagas), suelo legal por jornada completa. Comprueba el importe vigente si presentas el plan en otro ejercicio</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1348,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por el alcohol que sale por delivery (es una entrega de bienes). El alcohol servido en sala va al reducido: su tipo está en el bloque de desglose del IVA. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo</t>
+          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por el alcohol que sale por delivery (es una entrega de bienes). El alcohol servido en sala va al reducido: su tipo está en el bloque de desglose del IVA. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo. El libro manda al general sólo el alcohol: si compras refrescos o zumos con azúcares añadidos, su factura también va al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992)</t>
         </is>
       </c>
     </row>
@@ -1524,7 +1527,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Imprevistos de obra sobre el bloque de local</t>
+          <t>Imprevistos sobre las partidas de OBRA del bloque de local (%)</t>
         </is>
       </c>
       <c r="B55" s="34" t="n">
@@ -1830,11 +1833,11 @@
       </c>
       <c r="B6" s="42">
         <f>IFERROR(IF(COUNT(B7:B13)=0,"",SUM(B7:B13)),"")</f>
-        <v>53800.0</v>
+        <v>53650.0</v>
       </c>
       <c r="C6" s="43">
         <f>IFERROR(B6/$B$48,"")</f>
-        <v>0.3002821982889496</v>
+        <v>0.29969589106599004</v>
       </c>
       <c r="D6" s="44" t="n"/>
       <c r="E6" s="44" t="n"/>
@@ -1850,7 +1853,7 @@
       </c>
       <c r="C7" s="46">
         <f>IFERROR(B7/$B$48,"")</f>
-        <v>0.008372180249691902</v>
+        <v>0.008379195463168407</v>
       </c>
       <c r="D7" s="44" t="inlineStr">
         <is>
@@ -1874,7 +1877,7 @@
       </c>
       <c r="C8" s="46">
         <f>IFERROR(B8/$B$48,"")</f>
-        <v>0.13953633749486505</v>
+        <v>0.13965325771947346</v>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
@@ -1898,7 +1901,7 @@
       </c>
       <c r="C9" s="46">
         <f>IFERROR(B9/$B$48,"")</f>
-        <v>0.019535087249281106</v>
+        <v>0.019551456080726285</v>
       </c>
       <c r="D9" s="44" t="inlineStr">
         <is>
@@ -1922,7 +1925,7 @@
       </c>
       <c r="C10" s="46">
         <f>IFERROR(B10/$B$48,"")</f>
-        <v>0.04465162799835681</v>
+        <v>0.044689042470231505</v>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
@@ -1947,7 +1950,7 @@
       </c>
       <c r="C11" s="46">
         <f>IFERROR(B11/$B$48,"")</f>
-        <v>0.050233081498151415</v>
+        <v>0.050275172779010446</v>
       </c>
       <c r="D11" s="44" t="str">
         <f>IFERROR(""&amp;TEXT('0. Supuestos'!$B$25,"0")&amp;" meses de renta, al tipo de la hoja de Supuestos. Es un activo recuperable al cerrar: ni se amortiza ni lleva IVA","")</f>
@@ -1971,11 +1974,11 @@
       </c>
       <c r="C12" s="46">
         <f>IFERROR(B12/$B$48,"")</f>
-        <v>0.016744360499383805</v>
+        <v>0.016758390926336814</v>
       </c>
       <c r="D12" s="44" t="str">
-        <f>IFERROR("Renta de los "&amp;TEXT('0. Supuestos'!$B$54,"0")&amp;" meses de obra y licencias. NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación","")</f>
-        <v>Renta de los 1 meses de obra y licencias. NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación</v>
+        <f>IFERROR("Renta "&amp;IF('0. Supuestos'!$B$54=1,"del mes","de los "&amp;TEXT('0. Supuestos'!$B$54,"0")&amp;" meses")&amp;" de obra y licencias. NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación","")</f>
+        <v>Renta del mes de obra y licencias. NO se solapa con el P&amp;L, que arranca el día de la apertura: los doce meses del P&amp;L son los doce de explotación</v>
       </c>
       <c r="E12" s="44" t="inlineStr">
         <is>
@@ -1990,16 +1993,16 @@
         </is>
       </c>
       <c r="B13" s="48">
-        <f>IFERROR(IF(COUNT(B7:B10)=0,"",ROUND(SUM(B7:B10)*'0. Supuestos'!$B$55,0)),"")</f>
-        <v>3800.0</v>
+        <f>IFERROR(IF(COUNT(B8,B9,B10)=0,"",ROUND((B8+B9+B10)*'0. Supuestos'!$B$55,0)),"")</f>
+        <v>3650.0</v>
       </c>
       <c r="C13" s="46">
         <f>IFERROR(B13/$B$48,"")</f>
-        <v>0.021209523299219487</v>
+        <v>0.020389375627043124</v>
       </c>
       <c r="D13" s="44" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de obra y acondicionamiento de este bloque. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
-        <v>Al 10% de las partidas de obra y acondicionamiento de este bloque. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <v>Al 10% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Obra civil y reforma local, Proyecto técnico + licencia actividad y Decoración e interiorismo), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E13" s="44" t="inlineStr">
         <is>
@@ -2019,7 +2022,7 @@
       </c>
       <c r="C14" s="43">
         <f>IFERROR(B14/$B$48,"")</f>
-        <v>0.14344335494472127</v>
+        <v>0.1435635489356187</v>
       </c>
       <c r="D14" s="44" t="n"/>
       <c r="E14" s="44" t="n"/>
@@ -2035,7 +2038,7 @@
       </c>
       <c r="C15" s="46">
         <f>IFERROR(B15/$B$48,"")</f>
-        <v>0.025116540749075707</v>
+        <v>0.025137586389505223</v>
       </c>
       <c r="D15" s="44" t="inlineStr">
         <is>
@@ -2059,7 +2062,7 @@
       </c>
       <c r="C16" s="46">
         <f>IFERROR(B16/$B$48,"")</f>
-        <v>0.030697994248870313</v>
+        <v>0.03072371669828416</v>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
@@ -2083,7 +2086,7 @@
       </c>
       <c r="C17" s="46">
         <f>IFERROR(B17/$B$48,"")</f>
-        <v>0.004465162799835681</v>
+        <v>0.00446890424702315</v>
       </c>
       <c r="D17" s="44" t="inlineStr">
         <is>
@@ -2107,7 +2110,7 @@
       </c>
       <c r="C18" s="46">
         <f>IFERROR(B18/$B$48,"")</f>
-        <v>0.012279197699548125</v>
+        <v>0.012289486679313665</v>
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
@@ -2131,7 +2134,7 @@
       </c>
       <c r="C19" s="46">
         <f>IFERROR(B19/$B$48,"")</f>
-        <v>0.019535087249281106</v>
+        <v>0.019551456080726285</v>
       </c>
       <c r="D19" s="44" t="inlineStr">
         <is>
@@ -2155,7 +2158,7 @@
       </c>
       <c r="C20" s="46">
         <f>IFERROR(B20/$B$48,"")</f>
-        <v>0.016744360499383805</v>
+        <v>0.016758390926336814</v>
       </c>
       <c r="D20" s="44" t="inlineStr">
         <is>
@@ -2179,7 +2182,7 @@
       </c>
       <c r="C21" s="46">
         <f>IFERROR(B21/$B$48,"")</f>
-        <v>0.015628069799424885</v>
+        <v>0.015641164864581027</v>
       </c>
       <c r="D21" s="44" t="inlineStr">
         <is>
@@ -2203,7 +2206,7 @@
       </c>
       <c r="C22" s="46">
         <f>IFERROR(B22/$B$48,"")</f>
-        <v>0.011162906999589203</v>
+        <v>0.011172260617557876</v>
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
@@ -2227,7 +2230,7 @@
       </c>
       <c r="C23" s="46">
         <f>IFERROR(B23/$B$48,"")</f>
-        <v>0.003348872099876761</v>
+        <v>0.003351678185267363</v>
       </c>
       <c r="D23" s="48" t="n"/>
       <c r="E23" s="47" t="inlineStr">
@@ -2247,7 +2250,7 @@
       </c>
       <c r="C24" s="46">
         <f>IFERROR(B24/$B$48,"")</f>
-        <v>0.004465162799835681</v>
+        <v>0.00446890424702315</v>
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
@@ -2272,7 +2275,7 @@
       </c>
       <c r="C25" s="43">
         <f>IFERROR(B25/$B$48,"")</f>
-        <v>0.12145242815553053</v>
+        <v>0.1215541955190297</v>
       </c>
       <c r="D25" s="44" t="n"/>
       <c r="E25" s="44" t="n"/>
@@ -2288,7 +2291,7 @@
       </c>
       <c r="C26" s="46">
         <f>IFERROR(B26/$B$48,"")</f>
-        <v>0.022325813999178407</v>
+        <v>0.022344521235115752</v>
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
@@ -2312,7 +2315,7 @@
       </c>
       <c r="C27" s="46">
         <f>IFERROR(B27/$B$48,"")</f>
-        <v>0.020093232599260567</v>
+        <v>0.02011006911160418</v>
       </c>
       <c r="D27" s="44" t="inlineStr">
         <is>
@@ -2336,7 +2339,7 @@
       </c>
       <c r="C28" s="46">
         <f>IFERROR(B28/$B$48,"")</f>
-        <v>0.005358195359802818</v>
+        <v>0.0053626850964277805</v>
       </c>
       <c r="D28" s="44" t="inlineStr">
         <is>
@@ -2360,7 +2363,7 @@
       </c>
       <c r="C29" s="46">
         <f>IFERROR(B29/$B$48,"")</f>
-        <v>0.019535087249281106</v>
+        <v>0.019551456080726285</v>
       </c>
       <c r="D29" s="44" t="inlineStr">
         <is>
@@ -2384,7 +2387,7 @@
       </c>
       <c r="C30" s="46">
         <f>IFERROR(B30/$B$48,"")</f>
-        <v>0.002790726749897301</v>
+        <v>0.002793065154389469</v>
       </c>
       <c r="D30" s="48" t="n"/>
       <c r="E30" s="47" t="inlineStr">
@@ -2404,7 +2407,7 @@
       </c>
       <c r="C31" s="46">
         <f>IFERROR(B31/$B$48,"")</f>
-        <v>0.006697744199753522</v>
+        <v>0.006703356370534726</v>
       </c>
       <c r="D31" s="44" t="inlineStr">
         <is>
@@ -2428,7 +2431,7 @@
       </c>
       <c r="C32" s="46">
         <f>IFERROR(B32/$B$48,"")</f>
-        <v>0.004465162799835681</v>
+        <v>0.00446890424702315</v>
       </c>
       <c r="D32" s="44" t="inlineStr">
         <is>
@@ -2452,7 +2455,7 @@
       </c>
       <c r="C33" s="46">
         <f>IFERROR(B33/$B$48,"")</f>
-        <v>0.008372180249691902</v>
+        <v>0.008379195463168407</v>
       </c>
       <c r="D33" s="44" t="inlineStr">
         <is>
@@ -2476,7 +2479,7 @@
       </c>
       <c r="C34" s="46">
         <f>IFERROR(B34/$B$48,"")</f>
-        <v>0.008372180249691902</v>
+        <v>0.008379195463168407</v>
       </c>
       <c r="D34" s="44" t="inlineStr">
         <is>
@@ -2500,7 +2503,7 @@
       </c>
       <c r="C35" s="46">
         <f>IFERROR(B35/$B$48,"")</f>
-        <v>0.02344210469913733</v>
+        <v>0.023461747296871543</v>
       </c>
       <c r="D35" s="44" t="inlineStr">
         <is>
@@ -2525,7 +2528,7 @@
       </c>
       <c r="C36" s="43">
         <f>IFERROR(B36/$B$48,"")</f>
-        <v>0.022325813999178407</v>
+        <v>0.022344521235115752</v>
       </c>
       <c r="D36" s="44" t="n"/>
       <c r="E36" s="44" t="n"/>
@@ -2541,7 +2544,7 @@
       </c>
       <c r="C37" s="46">
         <f>IFERROR(B37/$B$48,"")</f>
-        <v>0.008372180249691902</v>
+        <v>0.008379195463168407</v>
       </c>
       <c r="D37" s="44" t="inlineStr">
         <is>
@@ -2565,7 +2568,7 @@
       </c>
       <c r="C38" s="46">
         <f>IFERROR(B38/$B$48,"")</f>
-        <v>0.005581453499794602</v>
+        <v>0.005586130308778938</v>
       </c>
       <c r="D38" s="44" t="inlineStr">
         <is>
@@ -2589,7 +2592,7 @@
       </c>
       <c r="C39" s="46">
         <f>IFERROR(B39/$B$48,"")</f>
-        <v>0.008372180249691902</v>
+        <v>0.008379195463168407</v>
       </c>
       <c r="D39" s="44" t="inlineStr">
         <is>
@@ -2614,7 +2617,7 @@
       </c>
       <c r="C40" s="43">
         <f>IFERROR(B40/$B$48,"")</f>
-        <v>0.006139598849774062</v>
+        <v>0.006144743339656832</v>
       </c>
       <c r="D40" s="44" t="n"/>
       <c r="E40" s="44" t="n"/>
@@ -2630,7 +2633,7 @@
       </c>
       <c r="C41" s="46">
         <f>IFERROR(B41/$B$48,"")</f>
-        <v>0.003348872099876761</v>
+        <v>0.003351678185267363</v>
       </c>
       <c r="D41" s="44" t="inlineStr">
         <is>
@@ -2654,7 +2657,7 @@
       </c>
       <c r="C42" s="46">
         <f>IFERROR(B42/$B$48,"")</f>
-        <v>0.002790726749897301</v>
+        <v>0.002793065154389469</v>
       </c>
       <c r="D42" s="48" t="n"/>
       <c r="E42" s="47" t="inlineStr">
@@ -2675,7 +2678,7 @@
       </c>
       <c r="C43" s="43">
         <f>IFERROR(B43/$B$48,"")</f>
-        <v>0.06697744199753522</v>
+        <v>0.06703356370534726</v>
       </c>
       <c r="D43" s="44" t="n"/>
       <c r="E43" s="44" t="n"/>
@@ -2691,7 +2694,7 @@
       </c>
       <c r="C44" s="46">
         <f>IFERROR(B44/$B$48,"")</f>
-        <v>0.036279447748664914</v>
+        <v>0.0363098470070631</v>
       </c>
       <c r="D44" s="44" t="inlineStr">
         <is>
@@ -2715,7 +2718,7 @@
       </c>
       <c r="C45" s="46">
         <f>IFERROR(B45/$B$48,"")</f>
-        <v>0.030697994248870313</v>
+        <v>0.03072371669828416</v>
       </c>
       <c r="D45" s="44" t="inlineStr">
         <is>
@@ -2740,7 +2743,7 @@
       </c>
       <c r="C46" s="43">
         <f>IFERROR(B46/$B$48,"")</f>
-        <v>0.3393791637643109</v>
+        <v>0.33966353619924167</v>
       </c>
       <c r="D46" s="44" t="n"/>
       <c r="E46" s="44" t="n"/>
@@ -2757,10 +2760,10 @@
       </c>
       <c r="C47" s="46">
         <f>IFERROR(B47/$B$48,"")</f>
-        <v>0.3393791637643109</v>
+        <v>0.33966353619924167</v>
       </c>
       <c r="D47" s="44" t="str">
-        <f>IFERROR("Cubre "&amp;TEXT('0. Supuestos'!$B$35,"0")&amp;" meses de costes fijos DE CAJA del año 1 (los del P&amp;L menos la amortización, que no se paga), que es el mínimo que exigen las Instrucciones de este libro","")</f>
+        <f>IFERROR("Cubre "&amp;TEXT('0. Supuestos'!$B$35,"0")&amp;IF('0. Supuestos'!$B$35=1," mes"," meses")&amp;" de costes fijos DE CAJA del año 1 (los del P&amp;L menos la amortización, que no se paga), que es el mínimo que exigen las Instrucciones de este libro","")</f>
         <v>Cubre 3 meses de costes fijos DE CAJA del año 1 (los del P&amp;L menos la amortización, que no se paga), que es el mínimo que exigen las Instrucciones de este libro</v>
       </c>
       <c r="E47" s="44" t="inlineStr">
@@ -2777,7 +2780,7 @@
       </c>
       <c r="B48" s="42">
         <f>IFERROR(B6+B14+B25+B36+B40+B43+B46,"")</f>
-        <v>179164.80000000002</v>
+        <v>179014.80000000002</v>
       </c>
       <c r="C48" s="44" t="n"/>
       <c r="D48" s="41" t="str">
@@ -2794,7 +2797,7 @@
       </c>
       <c r="B49" s="42">
         <f>IFERROR(B48-B46,"")</f>
-        <v>118360.0</v>
+        <v>118210.0</v>
       </c>
       <c r="C49" s="44" t="n"/>
       <c r="D49" s="41" t="inlineStr">
@@ -2812,12 +2815,12 @@
       </c>
       <c r="B50" s="48">
         <f>IFERROR(IF(B48="","",SUMIF($E$7:$E$45,"Sí",$B$7:$B$45)*'0. Supuestos'!$B$41),"")</f>
-        <v>22734.6</v>
+        <v>22703.1</v>
       </c>
       <c r="C50" s="44" t="n"/>
       <c r="D50" s="44" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
-        <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Se recupera con el modelo 303, pero hay que adelantarlo</v>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E50" s="44" t="n"/>
     </row>
@@ -2829,7 +2832,7 @@
       </c>
       <c r="B51" s="42">
         <f>IFERROR(B48+B50,"")</f>
-        <v>201899.40000000002</v>
+        <v>201717.90000000002</v>
       </c>
       <c r="C51" s="44" t="n"/>
       <c r="D51" s="41" t="inlineStr">
@@ -2857,8 +2860,8 @@
         </is>
       </c>
       <c r="B53" s="48">
-        <f>IFERROR(IF(B8="","",B8+B9+B10+B20+B26),"")</f>
-        <v>43500.0</v>
+        <f>IFERROR(IF(B8="","",B8+B9+B10+B13+B20+B26),"")</f>
+        <v>47150.0</v>
       </c>
       <c r="C53" s="44" t="n"/>
       <c r="D53" s="44" t="str">
@@ -2892,12 +2895,12 @@
       </c>
       <c r="B55" s="42">
         <f>IFERROR(B53/MAX(1,'0. Supuestos'!$B$44)+B54/MAX(1,'0. Supuestos'!$B$45),"")</f>
-        <v>8396.0</v>
+        <v>8761.0</v>
       </c>
       <c r="C55" s="44" t="n"/>
       <c r="D55" s="41" t="str">
-        <f>IFERROR("No se amortizan el fondo de maniobra, la fianza, el alquiler previo, el marketing de lanzamiento, los gastos de constitución ni las existencias iniciales: no son inmovilizado. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
-        <v>No se amortizan el fondo de maniobra, la fianza, el alquiler previo, el marketing de lanzamiento, los gastos de constitución ni las existencias iniciales: no son inmovilizado. Suman 95205 € de los 179165 € de inversión.</v>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B48-B53-B54,"0")&amp;" € de los "&amp;TEXT(B48,"0")&amp;" € de inversión.","")</f>
+        <v>No se amortizan, por no ser inmovilizado, Honorarios inmobiliaria, Fianza del alquiler, Alquiler de los meses previos a la apertura, Diseño marca e identidad visual, Web + Google My Business, Campaña lanzamiento RRSS + inauguración, Constitución SL (notaría + registro), Licencias y permisos varios, Primera compra de despensa y cámaras, Primera compra de bodega y barra ni Colchón operativo hasta alcanzar el equilibrio. Suman 91405 € de los 179015 € de inversión.</v>
       </c>
       <c r="E55" s="44" t="n"/>
     </row>
@@ -2943,7 +2946,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="E7:E47" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Escribe «Sí» o «No»: de esta columna sale el IVA soportado de la inversión." type="list">
+    <dataValidation sqref="E7:E10 E15:E24 E26:E35 E37:E39 E41:E42 E44:E45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Escribe «Sí» o «No»: de esta columna sale el IVA soportado de la inversión." type="list">
       <formula1>"Sí,No"</formula1>
     </dataValidation>
     <dataValidation sqref="B7 B8 B9 B10 B15 B16 B17 B18 B19 B20 B21 B22 B23 B24 B26 B27 B28 B29 B30 B31 B32 B33 B34 B35 B37 B38 B39 B41 B42 B44 B45" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
@@ -2969,7 +2972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2979,6 +2982,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3036,9 +3040,10 @@
       </c>
       <c r="G5" s="54" t="inlineStr">
         <is>
-          <t>Tipo de IVA soportado (%)</t>
-        </is>
-      </c>
+          <t>Tipo de IVA de la línea (%)</t>
+        </is>
+      </c>
+      <c r="H5" s="44" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="41" t="inlineStr">
@@ -3052,6 +3057,7 @@
       <c r="E6" s="44" t="n"/>
       <c r="F6" s="44" t="n"/>
       <c r="G6" s="44" t="n"/>
+      <c r="H6" s="44" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="44" t="inlineStr">
@@ -3078,6 +3084,7 @@
         </is>
       </c>
       <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="44" t="inlineStr">
@@ -3104,6 +3111,7 @@
         </is>
       </c>
       <c r="G8" s="44" t="n"/>
+      <c r="H8" s="44" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="44" t="inlineStr">
@@ -3126,6 +3134,7 @@
       <c r="E9" s="44" t="n"/>
       <c r="F9" s="44" t="n"/>
       <c r="G9" s="44" t="n"/>
+      <c r="H9" s="44" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="41" t="inlineStr">
@@ -3145,11 +3154,13 @@
         <f>IFERROR(IF(D7*D8*D9=0,"",D7*D8*D9),"")</f>
         <v>526285.76</v>
       </c>
-      <c r="E10" s="43" t="n">
-        <v>1</v>
+      <c r="E10" s="43">
+        <f>IFERROR(IF(B10="","",1),"")</f>
+        <v>1.0</v>
       </c>
       <c r="F10" s="44" t="n"/>
       <c r="G10" s="44" t="n"/>
+      <c r="H10" s="44" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="44" t="inlineStr">
@@ -3178,7 +3189,11 @@
           <t>Menú del mediodía, carta y raciones</t>
         </is>
       </c>
-      <c r="G11" s="44" t="n"/>
+      <c r="G11" s="46">
+        <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$39),"")</f>
+        <v>0.1</v>
+      </c>
+      <c r="H11" s="44" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="44" t="inlineStr">
@@ -3207,7 +3222,11 @@
           <t>Se calcula como el resto: comida + bebida = 100 %</t>
         </is>
       </c>
-      <c r="G12" s="44" t="n"/>
+      <c r="G12" s="46">
+        <f>IFERROR(IF(B10="","",('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)),"")</f>
+        <v>0.1</v>
+      </c>
+      <c r="H12" s="44" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="41" t="inlineStr">
@@ -3221,6 +3240,7 @@
       <c r="E13" s="44" t="n"/>
       <c r="F13" s="44" t="n"/>
       <c r="G13" s="44" t="n"/>
+      <c r="H13" s="44" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="44" t="inlineStr">
@@ -3252,6 +3272,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$39),"")</f>
         <v>0.1</v>
       </c>
+      <c r="H14" s="44" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="44" t="inlineStr">
@@ -3283,6 +3304,7 @@
         <f>IFERROR(IF(B10="","",('0. Supuestos'!$B$62*'0. Supuestos'!$B$40+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)),"")</f>
         <v>0.166</v>
       </c>
+      <c r="H15" s="44" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="44" t="inlineStr">
@@ -3311,6 +3333,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H16" s="44" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="44" t="inlineStr">
@@ -3343,6 +3366,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H17" s="44" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="44" t="inlineStr">
@@ -3374,6 +3398,7 @@
       <c r="G18" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="H18" s="44" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="44" t="inlineStr">
@@ -3405,6 +3430,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H19" s="44" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="41" t="inlineStr">
@@ -3430,6 +3456,7 @@
       </c>
       <c r="F20" s="44" t="n"/>
       <c r="G20" s="44" t="n"/>
+      <c r="H20" s="44" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="41" t="inlineStr">
@@ -3455,6 +3482,7 @@
       </c>
       <c r="F21" s="44" t="n"/>
       <c r="G21" s="44" t="n"/>
+      <c r="H21" s="44" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="41" t="inlineStr">
@@ -3468,6 +3496,7 @@
       <c r="E22" s="44" t="n"/>
       <c r="F22" s="44" t="n"/>
       <c r="G22" s="44" t="n"/>
+      <c r="H22" s="44" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="44" t="inlineStr">
@@ -3500,6 +3529,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H23" s="44" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="44" t="inlineStr">
@@ -3531,6 +3561,7 @@
       <c r="G24" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="H24" s="44" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="44" t="inlineStr">
@@ -3563,6 +3594,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H25" s="44" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="44" t="inlineStr">
@@ -3594,6 +3626,7 @@
       <c r="G26" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="H26" s="44" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="44" t="inlineStr">
@@ -3621,6 +3654,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H27" s="44" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="44" t="inlineStr">
@@ -3648,6 +3682,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H28" s="44" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="44" t="inlineStr">
@@ -3675,6 +3710,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H29" s="44" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="44" t="inlineStr">
@@ -3702,6 +3738,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H30" s="44" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="44" t="inlineStr">
@@ -3733,6 +3770,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H31" s="44" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="44" t="inlineStr">
@@ -3764,6 +3802,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H32" s="44" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="44" t="inlineStr">
@@ -3795,6 +3834,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H33" s="44" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="44" t="inlineStr">
@@ -3826,6 +3866,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H34" s="44" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="44" t="inlineStr">
@@ -3857,6 +3898,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H35" s="44" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="44" t="inlineStr">
@@ -3888,6 +3930,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H36" s="44" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="44" t="inlineStr">
@@ -3919,6 +3962,7 @@
         <f>IFERROR(IF(B10="","",'0. Supuestos'!$B$41),"")</f>
         <v>0.21</v>
       </c>
+      <c r="H37" s="44" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="44" t="inlineStr">
@@ -3928,19 +3972,19 @@
       </c>
       <c r="B38" s="48">
         <f>IFERROR(IF(B10="","",'1. Inversión Inicial'!$B$55),"")</f>
-        <v>8396.0</v>
+        <v>8761.0</v>
       </c>
       <c r="C38" s="48">
         <f>IFERROR(IF(C10="","",B38),"")</f>
-        <v>8396.0</v>
+        <v>8761.0</v>
       </c>
       <c r="D38" s="48">
         <f>IFERROR(IF(D10="","",B38),"")</f>
-        <v>8396.0</v>
+        <v>8761.0</v>
       </c>
       <c r="E38" s="46">
         <f>IFERROR(B38/$B$10,"")</f>
-        <v>0.01860155973059199</v>
+        <v>0.01941022686990429</v>
       </c>
       <c r="F38" s="44" t="inlineStr">
         <is>
@@ -3950,6 +3994,7 @@
       <c r="G38" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="H38" s="44" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="44" t="inlineStr">
@@ -3981,6 +4026,7 @@
       <c r="G39" s="46" t="n">
         <v>0</v>
       </c>
+      <c r="H39" s="44" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="41" t="inlineStr">
@@ -3990,22 +4036,23 @@
       </c>
       <c r="B40" s="42">
         <f>IFERROR(IF(B10="","",SUM(B23:B39)),"")</f>
-        <v>251615.2</v>
+        <v>251980.2</v>
       </c>
       <c r="C40" s="42">
         <f>IFERROR(IF(C10="","",SUM(C23:C39)),"")</f>
-        <v>257615.2</v>
+        <v>257980.2</v>
       </c>
       <c r="D40" s="42">
         <f>IFERROR(IF(D10="","",SUM(D23:D39)),"")</f>
-        <v>262514.17501331284</v>
+        <v>262879.17501331284</v>
       </c>
       <c r="E40" s="43">
         <f>IFERROR(B40/$B$10,"")</f>
-        <v>0.5574601205246367</v>
+        <v>0.5582687876639489</v>
       </c>
       <c r="F40" s="44" t="n"/>
       <c r="G40" s="44" t="n"/>
+      <c r="H40" s="44" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="44" t="inlineStr">
@@ -4032,6 +4079,7 @@
         </is>
       </c>
       <c r="G41" s="44" t="n"/>
+      <c r="H41" s="44" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="44" t="inlineStr">
@@ -4054,6 +4102,7 @@
       <c r="E42" s="44" t="n"/>
       <c r="F42" s="44" t="n"/>
       <c r="G42" s="44" t="n"/>
+      <c r="H42" s="44" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="41" t="inlineStr">
@@ -4063,22 +4112,23 @@
       </c>
       <c r="B43" s="42">
         <f>IFERROR(IF(B10="","",B21-B40),"")</f>
-        <v>57566.399999999965</v>
+        <v>57201.399999999965</v>
       </c>
       <c r="C43" s="42">
         <f>IFERROR(IF(C10="","",C21-C40),"")</f>
-        <v>82484.56</v>
+        <v>82119.56</v>
       </c>
       <c r="D43" s="42">
         <f>IFERROR(IF(D10="","",D21-D40),"")</f>
-        <v>97991.57058668719</v>
+        <v>97626.57058668719</v>
       </c>
       <c r="E43" s="43">
         <f>IFERROR(B43/$B$10,"")</f>
-        <v>0.12753987947536327</v>
+        <v>0.12673121233605097</v>
       </c>
       <c r="F43" s="44" t="n"/>
       <c r="G43" s="44" t="n"/>
+      <c r="H43" s="44" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="44" t="inlineStr">
@@ -4105,6 +4155,7 @@
         </is>
       </c>
       <c r="G44" s="44" t="n"/>
+      <c r="H44" s="44" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="44" t="inlineStr">
@@ -4114,19 +4165,20 @@
       </c>
       <c r="B45" s="48">
         <f>IFERROR(IF(B10="","",MAX(0,B43-B44)),"")</f>
-        <v>57566.399999999965</v>
+        <v>57201.399999999965</v>
       </c>
       <c r="C45" s="48">
         <f>IFERROR(IF(C10="","",MAX(0,C43-C44)),"")</f>
-        <v>82484.56</v>
+        <v>82119.56</v>
       </c>
       <c r="D45" s="48">
         <f>IFERROR(IF(D10="","",MAX(0,D43-D44)),"")</f>
-        <v>97991.57058668719</v>
+        <v>97626.57058668719</v>
       </c>
       <c r="E45" s="44" t="n"/>
       <c r="F45" s="44" t="n"/>
       <c r="G45" s="44" t="n"/>
+      <c r="H45" s="44" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="44" t="inlineStr">
@@ -4149,6 +4201,7 @@
       <c r="E46" s="44" t="n"/>
       <c r="F46" s="44" t="n"/>
       <c r="G46" s="44" t="n"/>
+      <c r="H46" s="44" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="44" t="inlineStr">
@@ -4175,6 +4228,7 @@
         </is>
       </c>
       <c r="G47" s="44" t="n"/>
+      <c r="H47" s="44" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="44" t="inlineStr">
@@ -4184,19 +4238,20 @@
       </c>
       <c r="B48" s="48">
         <f>IFERROR(IF(B10="","",IF(B47="",0,B45*B47)),"")</f>
-        <v>8634.959999999994</v>
+        <v>8580.209999999994</v>
       </c>
       <c r="C48" s="48">
         <f>IFERROR(IF(C10="","",IF(C47="",0,C45*C47)),"")</f>
-        <v>12372.684</v>
+        <v>12317.934</v>
       </c>
       <c r="D48" s="48">
         <f>IFERROR(IF(D10="","",IF(D47="",0,D45*D47)),"")</f>
-        <v>24497.892646671797</v>
+        <v>24406.642646671797</v>
       </c>
       <c r="E48" s="44" t="n"/>
       <c r="F48" s="44" t="n"/>
       <c r="G48" s="44" t="n"/>
+      <c r="H48" s="44" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="44" t="inlineStr">
@@ -4219,6 +4274,7 @@
       <c r="E49" s="44" t="n"/>
       <c r="F49" s="44" t="n"/>
       <c r="G49" s="44" t="n"/>
+      <c r="H49" s="44" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="41" t="inlineStr">
@@ -4228,22 +4284,23 @@
       </c>
       <c r="B50" s="42">
         <f>IFERROR(IF(B10="","",B43-B48),"")</f>
-        <v>48931.43999999997</v>
+        <v>48621.18999999997</v>
       </c>
       <c r="C50" s="42">
         <f>IFERROR(IF(C10="","",C43-C48),"")</f>
-        <v>70111.876</v>
+        <v>69801.626</v>
       </c>
       <c r="D50" s="42">
         <f>IFERROR(IF(D10="","",D43-D48),"")</f>
-        <v>73493.67794001539</v>
+        <v>73219.92794001539</v>
       </c>
       <c r="E50" s="43">
         <f>IFERROR(B50/$B$10,"")</f>
-        <v>0.10840889755405879</v>
+        <v>0.10772153048564333</v>
       </c>
       <c r="F50" s="44" t="n"/>
       <c r="G50" s="44" t="n"/>
+      <c r="H50" s="44" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="41" t="inlineStr">
@@ -4257,6 +4314,7 @@
       <c r="E51" s="44" t="n"/>
       <c r="F51" s="44" t="n"/>
       <c r="G51" s="44" t="n"/>
+      <c r="H51" s="44" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="41" t="inlineStr">
@@ -4290,6 +4348,7 @@
         </is>
       </c>
       <c r="G52" s="44" t="n"/>
+      <c r="H52" s="44" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="44" t="inlineStr">
@@ -4318,6 +4377,7 @@
         </is>
       </c>
       <c r="G53" s="44" t="n"/>
+      <c r="H53" s="44" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="44" t="inlineStr">
@@ -4340,6 +4400,7 @@
       <c r="E54" s="44" t="n"/>
       <c r="F54" s="44" t="n"/>
       <c r="G54" s="44" t="n"/>
+      <c r="H54" s="44" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="44" t="inlineStr">
@@ -4368,6 +4429,7 @@
         </is>
       </c>
       <c r="G55" s="44" t="n"/>
+      <c r="H55" s="44" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="44" t="inlineStr">
@@ -4396,6 +4458,7 @@
         </is>
       </c>
       <c r="G56" s="44" t="n"/>
+      <c r="H56" s="44" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="44" t="inlineStr">
@@ -4424,6 +4487,7 @@
         </is>
       </c>
       <c r="G57" s="44" t="n"/>
+      <c r="H57" s="44" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="44" t="inlineStr">
@@ -4433,15 +4497,15 @@
       </c>
       <c r="B58" s="46">
         <f>IFERROR(IF(B10="","",B50/B10),"")</f>
-        <v>0.10840889755405879</v>
+        <v>0.10772153048564333</v>
       </c>
       <c r="C58" s="46">
         <f>IFERROR(IF(C10="","",C50/C10),"")</f>
-        <v>0.14121337533434308</v>
+        <v>0.14058849618123812</v>
       </c>
       <c r="D58" s="46">
         <f>IFERROR(IF(D10="","",D50/D10),"")</f>
-        <v>0.13964595572567912</v>
+        <v>0.1391258010477338</v>
       </c>
       <c r="E58" s="77" t="n">
         <v>0.05</v>
@@ -4452,6 +4516,7 @@
         </is>
       </c>
       <c r="G58" s="44" t="n"/>
+      <c r="H58" s="44" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="44" t="inlineStr">
@@ -4460,15 +4525,15 @@
         </is>
       </c>
       <c r="B59" s="44" t="str">
-        <f>IFERROR(IF(B10="","",IF(B10="","",IF(B10&gt;='3. Punto Equilibrio'!$B$17,"Sí","No"))),"")</f>
+        <f>IFERROR(IF(B10="","",IF(B10&gt;='3. Punto Equilibrio'!$B$17,"Sí","No")),"")</f>
         <v>Sí</v>
       </c>
       <c r="C59" s="44" t="str">
-        <f>IFERROR(IF(C10="","",IF(C10="","",IF(C10&gt;='3. Punto Equilibrio'!$C$17,"Sí","No"))),"")</f>
+        <f>IFERROR(IF(C10="","",IF(C10&gt;='3. Punto Equilibrio'!$C$17,"Sí","No")),"")</f>
         <v>Sí</v>
       </c>
       <c r="D59" s="44" t="str">
-        <f>IFERROR(IF(D10="","",IF(D10="","",IF(D10&gt;='3. Punto Equilibrio'!$D$17,"Sí","No"))),"")</f>
+        <f>IFERROR(IF(D10="","",IF(D10&gt;='3. Punto Equilibrio'!$D$17,"Sí","No")),"")</f>
         <v>Sí</v>
       </c>
       <c r="E59" s="44" t="n"/>
@@ -4478,6 +4543,7 @@
         </is>
       </c>
       <c r="G59" s="44" t="n"/>
+      <c r="H59" s="44" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="44" t="n"/>
@@ -4487,11 +4553,12 @@
       <c r="E60" s="44" t="n"/>
       <c r="F60" s="44" t="n"/>
       <c r="G60" s="44" t="n"/>
-    </row>
-    <row r="61" ht="135" customHeight="1">
+      <c r="H60" s="44" t="n"/>
+    </row>
+    <row r="61" ht="165" customHeight="1">
       <c r="A61" s="63" t="inlineStr">
         <is>
-          <t>Todas las cifras van SIN IVA. Las columnas de los años 2 y 3 están en euros del año 1 salvo que subas la actualización de costes en la hoja de Supuestos. La columna «IVA soportado» dice a qué tipo se compra cada partida y la lee la hoja de Tesorería: los seguros y las comisiones de los medios de pago están exentos, y las nóminas, la amortización y los intereses no llevan IVA.</t>
+          <t>Todas las cifras van SIN IVA. Las columnas de los años 2 y 3 están en euros del año 1 salvo que subas la actualización de costes en la hoja de Supuestos. La columna «Tipo de IVA de la línea» dice, en las líneas de VENTA, a qué tipo se repercute cada una, y en las de COSTE a qué tipo se compra la partida. La lee la hoja de Tesorería: los seguros y las comisiones de los medios de pago están exentos, y las nóminas, la amortización y los intereses no llevan IVA.</t>
         </is>
       </c>
       <c r="B61" s="44" t="n"/>
@@ -4500,6 +4567,7 @@
       <c r="E61" s="44" t="n"/>
       <c r="F61" s="44" t="n"/>
       <c r="G61" s="44" t="n"/>
+      <c r="H61" s="44" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="44" t="inlineStr">
@@ -4513,6 +4581,7 @@
       <c r="E62" s="44" t="n"/>
       <c r="F62" s="44" t="n"/>
       <c r="G62" s="44" t="n"/>
+      <c r="H62" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -4621,7 +4690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4702,15 +4771,15 @@
       </c>
       <c r="B7" s="56">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
-        <v>251615.2</v>
+        <v>251980.2</v>
       </c>
       <c r="C7" s="56">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$C$10="","",'2. P&amp;L 3 Años'!$C$40),"")</f>
-        <v>257615.2</v>
+        <v>257980.2</v>
       </c>
       <c r="D7" s="56">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$D$10="","",'2. P&amp;L 3 Años'!$D$40),"")</f>
-        <v>262514.17501331284</v>
+        <v>262879.17501331284</v>
       </c>
       <c r="E7" s="44" t="inlineStr">
         <is>
@@ -4727,15 +4796,15 @@
       </c>
       <c r="B8" s="56">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",B7/12),"")</f>
-        <v>20967.933333333334</v>
+        <v>20998.350000000002</v>
       </c>
       <c r="C8" s="56">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$C$10="","",C7/12),"")</f>
-        <v>21467.933333333334</v>
+        <v>21498.350000000002</v>
       </c>
       <c r="D8" s="56">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$D$10="","",D7/12),"")</f>
-        <v>21876.181251109403</v>
+        <v>21906.59791777607</v>
       </c>
       <c r="E8" s="44" t="n"/>
       <c r="F8" s="44" t="n"/>
@@ -4881,15 +4950,15 @@
       </c>
       <c r="B15" s="55">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",IF(B11&lt;=0,"",B7/B11)),"")</f>
-        <v>20182.49779417663</v>
+        <v>20211.775086227644</v>
       </c>
       <c r="C15" s="55">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$C$10="","",IF(C11&lt;=0,"",C7/C11)),"")</f>
-        <v>20663.768348439884</v>
+        <v>20693.0456404909</v>
       </c>
       <c r="D15" s="55">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$D$10="","",IF(D11&lt;=0,"",D7/D11)),"")</f>
-        <v>21056.7237517697</v>
+        <v>21086.001043820717</v>
       </c>
       <c r="E15" s="44" t="n"/>
       <c r="F15" s="44" t="n"/>
@@ -4902,15 +4971,15 @@
       </c>
       <c r="B16" s="60">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",B15/B12),"")</f>
-        <v>65.10483159411817</v>
+        <v>65.19927447170208</v>
       </c>
       <c r="C16" s="60">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$C$10="","",C15/C12),"")</f>
-        <v>66.65731725303188</v>
+        <v>66.7517601306158</v>
       </c>
       <c r="D16" s="60">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$D$10="","",D15/D12),"")</f>
-        <v>67.92491532828936</v>
+        <v>68.01935820587329</v>
       </c>
       <c r="E16" s="44" t="n"/>
       <c r="F16" s="44" t="n"/>
@@ -4923,15 +4992,15 @@
       </c>
       <c r="B17" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",B15*B9),"")</f>
-        <v>367321.4598540146</v>
+        <v>367854.30656934314</v>
       </c>
       <c r="C17" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$C$10="","",C15*C9),"")</f>
-        <v>376080.5839416059</v>
+        <v>376613.43065693433</v>
       </c>
       <c r="D17" s="42">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$D$10="","",D15*D9),"")</f>
-        <v>383232.3722822085</v>
+        <v>383765.21899753704</v>
       </c>
       <c r="E17" s="44" t="n"/>
       <c r="F17" s="44" t="n"/>
@@ -5105,7 +5174,7 @@
       </c>
       <c r="C26" s="44" t="n"/>
       <c r="D26" s="44" t="n"/>
-      <c r="E26" s="60" t="inlineStr">
+      <c r="E26" s="44" t="inlineStr">
         <is>
           <t>Servicios completos por plaza y día que puedes llegar a hacer con tu horario. Es el techo físico del local, no un objetivo</t>
         </is>
@@ -5151,8 +5220,8 @@
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="44" t="str">
-        <f>IFERROR("Con el ticket medio sin IVA de la fila de arriba necesitas servir "&amp;TEXT(ROUNDUP(B21,0),"0")&amp;" cubiertos al día durante los "&amp;TEXT(B12,"0")&amp;" días que abres para cubrir los costes fijos, los variables Y la cuota del préstamo; sin contar la cuota bastan "&amp;TEXT(ROUNDUP(B16,0),"0")&amp;". En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.","")</f>
-        <v>Con el ticket medio sin IVA de la fila de arriba necesitas servir 63 cubiertos al día durante los 310 días que abres para cubrir los costes fijos, los variables Y la cuota del préstamo; sin contar la cuota bastan 66. En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.</v>
+        <f>IFERROR("Con el ticket medio sin IVA de la fila de arriba necesitas "&amp;TEXT(ROUNDUP(B16,0),"0")&amp;" cubiertos al día durante los "&amp;TEXT(B12,"0")&amp;" días que abres para no perder dinero (equilibrio contable, con la amortización dentro), y "&amp;TEXT(ROUNDUP(B21,0),"0")&amp;" para que la caja aguante (equilibrio de caja: sin la amortización, que no se paga, y con la cuota del préstamo del año"&amp;IF(B13=0,"; este año sólo intereses, porque el préstamo está en carencia","")&amp;"). En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.","")</f>
+        <v>Con el ticket medio sin IVA de la fila de arriba necesitas 66 cubiertos al día durante los 310 días que abres para no perder dinero (equilibrio contable, con la amortización dentro), y 63 para que la caja aguante (equilibrio de caja: sin la amortización, que no se paga, y con la cuota del préstamo del año; este año sólo intereses, porque el préstamo está en carencia). En las filas «Ingresos necesarios al año» tienes esas mismas cifras en euros.</v>
       </c>
       <c r="B29" s="44" t="n"/>
       <c r="C29" s="44" t="n"/>
@@ -5200,10 +5269,10 @@
       <c r="E33" s="44" t="n"/>
       <c r="F33" s="44" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="54" t="inlineStr">
         <is>
-          <t>Coste variable / cubierto</t>
+          <t>Cubiertos/día necesarios: ticket medio sin IVA (columnas) × coste variable por cubierto (filas)</t>
         </is>
       </c>
       <c r="B34" s="64">
@@ -5231,19 +5300,19 @@
       </c>
       <c r="B35" s="60">
         <f>IFERROR(IF($B$34-$A35&lt;=0,"",$B$7/($B$34-$A35)/$B$12),"")</f>
-        <v>71.65758968512009</v>
+        <v>71.76153817565273</v>
       </c>
       <c r="C35" s="60">
         <f>IFERROR(IF($C$34-$A35&lt;=0,"",$B$7/($C$34-$A35)/$B$12),"")</f>
-        <v>60.903802856908065</v>
+        <v>60.99215160548435</v>
       </c>
       <c r="D35" s="60">
         <f>IFERROR(IF($D$34-$A35&lt;=0,"",$B$7/($D$34-$A35)/$B$12),"")</f>
-        <v>52.95652008285216</v>
+        <v>53.033340282229</v>
       </c>
       <c r="E35" s="60">
         <f>IFERROR(IF($E$34-$A35&lt;=0,"",$B$7/($E$34-$A35)/$B$12),"")</f>
-        <v>46.84390129156436</v>
+        <v>46.91185435628946</v>
       </c>
       <c r="F35" s="44" t="n"/>
     </row>
@@ -5254,19 +5323,19 @@
       </c>
       <c r="B36" s="60">
         <f>IFERROR(IF($B$34-$A36&lt;=0,"",$B$7/($B$34-$A36)/$B$12),"")</f>
-        <v>74.48506906585278</v>
+        <v>74.59311917653383</v>
       </c>
       <c r="C36" s="60">
         <f>IFERROR(IF($C$34-$A36&lt;=0,"",$B$7/($C$34-$A36)/$B$12),"")</f>
-        <v>62.93428772901173</v>
+        <v>63.025581955358504</v>
       </c>
       <c r="D36" s="60">
         <f>IFERROR(IF($D$34-$A36&lt;=0,"",$B$7/($D$34-$A36)/$B$12),"")</f>
-        <v>54.48501695705813</v>
+        <v>54.56405443646847</v>
       </c>
       <c r="E36" s="60">
         <f>IFERROR(IF($E$34-$A36&lt;=0,"",$B$7/($E$34-$A36)/$B$12),"")</f>
-        <v>48.03593160810566</v>
+        <v>48.10561386512733</v>
       </c>
       <c r="F36" s="44" t="n"/>
     </row>
@@ -5277,19 +5346,19 @@
       </c>
       <c r="B37" s="60">
         <f>IFERROR(IF($B$34-$A37&lt;=0,"",$B$7/($B$34-$A37)/$B$12),"")</f>
-        <v>77.54484909562157</v>
+        <v>77.65733780822679</v>
       </c>
       <c r="C37" s="60">
         <f>IFERROR(IF($C$34-$A37&lt;=0,"",$B$7/($C$34-$A37)/$B$12),"")</f>
-        <v>65.10483159411817</v>
+        <v>65.19927447170208</v>
       </c>
       <c r="D37" s="60">
         <f>IFERROR(IF($D$34-$A37&lt;=0,"",$B$7/($D$34-$A37)/$B$12),"")</f>
-        <v>56.10437101568198</v>
+        <v>56.185757575081894</v>
       </c>
       <c r="E37" s="60">
         <f>IFERROR(IF($E$34-$A37&lt;=0,"",$B$7/($E$34-$A37)/$B$12),"")</f>
-        <v>49.290212879326596</v>
+        <v>49.36171463160926</v>
       </c>
       <c r="F37" s="44" t="n"/>
     </row>
@@ -5300,19 +5369,19 @@
       </c>
       <c r="B38" s="60">
         <f>IFERROR(IF($B$34-$A38&lt;=0,"",$B$7/($B$34-$A38)/$B$12),"")</f>
-        <v>80.86678427959191</v>
+        <v>80.98409188367168</v>
       </c>
       <c r="C38" s="60">
         <f>IFERROR(IF($C$34-$A38&lt;=0,"",$B$7/($C$34-$A38)/$B$12),"")</f>
-        <v>67.43044360910366</v>
+        <v>67.52826008409136</v>
       </c>
       <c r="D38" s="60">
         <f>IFERROR(IF($D$34-$A38&lt;=0,"",$B$7/($D$34-$A38)/$B$12),"")</f>
-        <v>57.82293153170783</v>
+        <v>57.906811082740795</v>
       </c>
       <c r="E38" s="60">
         <f>IFERROR(IF($E$34-$A38&lt;=0,"",$B$7/($E$34-$A38)/$B$12),"")</f>
-        <v>50.61175220989373</v>
+        <v>50.68517102384698</v>
       </c>
       <c r="F38" s="44" t="n"/>
     </row>
@@ -5323,19 +5392,19 @@
       </c>
       <c r="B39" s="60">
         <f>IFERROR(IF($B$34-$A39&lt;=0,"",$B$7/($B$34-$A39)/$B$12),"")</f>
-        <v>84.48607381910898</v>
+        <v>84.60863166515315</v>
       </c>
       <c r="C39" s="60">
         <f>IFERROR(IF($C$34-$A39&lt;=0,"",$B$7/($C$34-$A39)/$B$12),"")</f>
-        <v>69.92835694546599</v>
+        <v>70.02979696294146</v>
       </c>
       <c r="D39" s="60">
         <f>IFERROR(IF($D$34-$A39&lt;=0,"",$B$7/($D$34-$A39)/$B$12),"")</f>
-        <v>59.65010310712983</v>
+        <v>59.73663320401627</v>
       </c>
       <c r="E39" s="60">
         <f>IFERROR(IF($E$34-$A39&lt;=0,"",$B$7/($E$34-$A39)/$B$12),"")</f>
-        <v>52.006108488399214</v>
+        <v>52.08154999431088</v>
       </c>
       <c r="F39" s="44" t="n"/>
     </row>
@@ -5518,6 +5587,166 @@
       <c r="D61" s="44" t="n"/>
       <c r="E61" s="44" t="n"/>
       <c r="F61" s="44" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="n"/>
+      <c r="B62" s="44" t="n"/>
+      <c r="C62" s="44" t="n"/>
+      <c r="D62" s="44" t="n"/>
+      <c r="E62" s="44" t="n"/>
+      <c r="F62" s="44" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="44" t="n"/>
+      <c r="B63" s="44" t="n"/>
+      <c r="C63" s="44" t="n"/>
+      <c r="D63" s="44" t="n"/>
+      <c r="E63" s="44" t="n"/>
+      <c r="F63" s="44" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="44" t="n"/>
+      <c r="B64" s="44" t="n"/>
+      <c r="C64" s="44" t="n"/>
+      <c r="D64" s="44" t="n"/>
+      <c r="E64" s="44" t="n"/>
+      <c r="F64" s="44" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="44" t="n"/>
+      <c r="B65" s="44" t="n"/>
+      <c r="C65" s="44" t="n"/>
+      <c r="D65" s="44" t="n"/>
+      <c r="E65" s="44" t="n"/>
+      <c r="F65" s="44" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="44" t="n"/>
+      <c r="B66" s="44" t="n"/>
+      <c r="C66" s="44" t="n"/>
+      <c r="D66" s="44" t="n"/>
+      <c r="E66" s="44" t="n"/>
+      <c r="F66" s="44" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="44" t="n"/>
+      <c r="B67" s="44" t="n"/>
+      <c r="C67" s="44" t="n"/>
+      <c r="D67" s="44" t="n"/>
+      <c r="E67" s="44" t="n"/>
+      <c r="F67" s="44" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="44" t="n"/>
+      <c r="B68" s="44" t="n"/>
+      <c r="C68" s="44" t="n"/>
+      <c r="D68" s="44" t="n"/>
+      <c r="E68" s="44" t="n"/>
+      <c r="F68" s="44" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="44" t="n"/>
+      <c r="B69" s="44" t="n"/>
+      <c r="C69" s="44" t="n"/>
+      <c r="D69" s="44" t="n"/>
+      <c r="E69" s="44" t="n"/>
+      <c r="F69" s="44" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="44" t="n"/>
+      <c r="B70" s="44" t="n"/>
+      <c r="C70" s="44" t="n"/>
+      <c r="D70" s="44" t="n"/>
+      <c r="E70" s="44" t="n"/>
+      <c r="F70" s="44" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="44" t="n"/>
+      <c r="B71" s="44" t="n"/>
+      <c r="C71" s="44" t="n"/>
+      <c r="D71" s="44" t="n"/>
+      <c r="E71" s="44" t="n"/>
+      <c r="F71" s="44" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="44" t="n"/>
+      <c r="B72" s="44" t="n"/>
+      <c r="C72" s="44" t="n"/>
+      <c r="D72" s="44" t="n"/>
+      <c r="E72" s="44" t="n"/>
+      <c r="F72" s="44" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="44" t="n"/>
+      <c r="B73" s="44" t="n"/>
+      <c r="C73" s="44" t="n"/>
+      <c r="D73" s="44" t="n"/>
+      <c r="E73" s="44" t="n"/>
+      <c r="F73" s="44" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="44" t="n"/>
+      <c r="B74" s="44" t="n"/>
+      <c r="C74" s="44" t="n"/>
+      <c r="D74" s="44" t="n"/>
+      <c r="E74" s="44" t="n"/>
+      <c r="F74" s="44" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="44" t="n"/>
+      <c r="B75" s="44" t="n"/>
+      <c r="C75" s="44" t="n"/>
+      <c r="D75" s="44" t="n"/>
+      <c r="E75" s="44" t="n"/>
+      <c r="F75" s="44" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="44" t="n"/>
+      <c r="B76" s="44" t="n"/>
+      <c r="C76" s="44" t="n"/>
+      <c r="D76" s="44" t="n"/>
+      <c r="E76" s="44" t="n"/>
+      <c r="F76" s="44" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="44" t="n"/>
+      <c r="B77" s="44" t="n"/>
+      <c r="C77" s="44" t="n"/>
+      <c r="D77" s="44" t="n"/>
+      <c r="E77" s="44" t="n"/>
+      <c r="F77" s="44" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="44" t="n"/>
+      <c r="B78" s="44" t="n"/>
+      <c r="C78" s="44" t="n"/>
+      <c r="D78" s="44" t="n"/>
+      <c r="E78" s="44" t="n"/>
+      <c r="F78" s="44" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="44" t="n"/>
+      <c r="B79" s="44" t="n"/>
+      <c r="C79" s="44" t="n"/>
+      <c r="D79" s="44" t="n"/>
+      <c r="E79" s="44" t="n"/>
+      <c r="F79" s="44" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="44" t="n"/>
+      <c r="B80" s="44" t="n"/>
+      <c r="C80" s="44" t="n"/>
+      <c r="D80" s="44" t="n"/>
+      <c r="E80" s="44" t="n"/>
+      <c r="F80" s="44" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="44" t="n"/>
+      <c r="B81" s="44" t="n"/>
+      <c r="C81" s="44" t="n"/>
+      <c r="D81" s="44" t="n"/>
+      <c r="E81" s="44" t="n"/>
+      <c r="F81" s="44" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -5577,7 +5806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -5891,15 +6120,15 @@
       </c>
       <c r="B18" s="48">
         <f>IFERROR(IF(B9="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
-        <v>251615.2</v>
+        <v>251980.2</v>
       </c>
       <c r="C18" s="48">
         <f>IFERROR(IF(C9="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
-        <v>251615.2</v>
+        <v>251980.2</v>
       </c>
       <c r="D18" s="48">
         <f>IFERROR(IF(D9="","",'2. P&amp;L 3 Años'!$B$40),"")</f>
-        <v>251615.2</v>
+        <v>251980.2</v>
       </c>
       <c r="E18" s="44" t="inlineStr">
         <is>
@@ -5916,15 +6145,15 @@
       </c>
       <c r="B19" s="42">
         <f>IFERROR(IF(B9="","",B17-B18),"")</f>
-        <v>-62103.09999999998</v>
+        <v>-62468.09999999998</v>
       </c>
       <c r="C19" s="42">
         <f>IFERROR(IF(C9="","",C17-C18),"")</f>
-        <v>57566.399999999965</v>
+        <v>57201.399999999965</v>
       </c>
       <c r="D19" s="42">
         <f>IFERROR(IF(D9="","",D17-D18),"")</f>
-        <v>133628.8</v>
+        <v>133263.8</v>
       </c>
       <c r="E19" s="44" t="n"/>
       <c r="F19" s="44" t="n"/>
@@ -5941,11 +6170,11 @@
       </c>
       <c r="C20" s="48">
         <f>IFERROR(IF(C9="","",MAX(0,C19-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
-        <v>8634.959999999994</v>
+        <v>8580.209999999994</v>
       </c>
       <c r="D20" s="48">
         <f>IFERROR(IF(D9="","",MAX(0,D19-'0. Supuestos'!$B$42)*'0. Supuestos'!$B$37),"")</f>
-        <v>20044.319999999996</v>
+        <v>19989.569999999996</v>
       </c>
       <c r="E20" s="44" t="inlineStr">
         <is>
@@ -5962,15 +6191,15 @@
       </c>
       <c r="B21" s="42">
         <f>IFERROR(IF(B9="","",B19-B20),"")</f>
-        <v>-62103.09999999998</v>
+        <v>-62468.09999999998</v>
       </c>
       <c r="C21" s="42">
         <f>IFERROR(IF(C9="","",C19-C20),"")</f>
-        <v>48931.43999999997</v>
+        <v>48621.18999999997</v>
       </c>
       <c r="D21" s="42">
         <f>IFERROR(IF(D9="","",D19-D20),"")</f>
-        <v>113584.48</v>
+        <v>113274.23</v>
       </c>
       <c r="E21" s="44" t="n"/>
       <c r="F21" s="44" t="n"/>
@@ -5983,15 +6212,15 @@
       </c>
       <c r="B22" s="60">
         <f>IFERROR(IF(B9="","",IF(B7-B16/(B6*B8)&lt;=0,"",B18/(B7-B16/(B6*B8))/B8)),"")</f>
-        <v>77.00659535723575</v>
+        <v>77.11830326401322</v>
       </c>
       <c r="C22" s="60">
         <f>IFERROR(IF(C9="","",IF(C7-C16/(C6*C8)&lt;=0,"",C18/(C7-C16/(C6*C8))/C8)),"")</f>
-        <v>65.10483159411817</v>
+        <v>65.19927447170208</v>
       </c>
       <c r="D22" s="60">
         <f>IFERROR(IF(D9="","",IF(D7-D16/(D6*D8)&lt;=0,"",D18/(D7-D16/(D6*D8))/D8)),"")</f>
-        <v>62.04754389425923</v>
+        <v>62.13755178536201</v>
       </c>
       <c r="E22" s="44" t="n"/>
       <c r="F22" s="44" t="n"/>
@@ -6061,7 +6290,7 @@
     <row r="26">
       <c r="A26" s="41" t="inlineStr">
         <is>
-          <t>Saldo de caja al cierre del año 1</t>
+          <t>Saldo de caja al cierre del año 1 (estimado, el mismo método en los tres escenarios)</t>
         </is>
       </c>
       <c r="B26" s="42">
@@ -6069,44 +6298,51 @@
         <v>7097.7000000000335</v>
       </c>
       <c r="C26" s="42">
+        <f>IFERROR(IF(C9="","",'1. Inversión Inicial'!$B$47+C21+'2. P&amp;L 3 Años'!$B$38-'7. Financiación'!$B$45),"")</f>
+        <v>118186.98999999999</v>
+      </c>
+      <c r="D26" s="42">
+        <f>IFERROR(IF(D9="","",'1. Inversión Inicial'!$B$47+D21+'2. P&amp;L 3 Años'!$B$38-'7. Financiación'!$B$45),"")</f>
+        <v>182840.03</v>
+      </c>
+      <c r="E26" s="41" t="inlineStr">
+        <is>
+          <t>Saldo ESTIMADO: fondo de maniobra más el resultado del año, devolviendo la amortización (que no se paga) y restando el principal del préstamo. No incluye el desfase de cobros y pagos ni la liquidación del IVA, así que las tres columnas se pueden comparar entre sí. En rojo, el escenario se queda sin caja</t>
+        </is>
+      </c>
+      <c r="F26" s="44" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="44" t="inlineStr">
+        <is>
+          <t>Saldo real del mes 12 de la hoja de Tesorería (sólo realista)</t>
+        </is>
+      </c>
+      <c r="B27" s="44" t="n"/>
+      <c r="C27" s="48">
         <f>IFERROR(IF(C9="","",'6. Tesorería 12 meses'!$M$22),"")</f>
         <v>155793.4083604959</v>
       </c>
-      <c r="D26" s="42">
-        <f>IFERROR(IF(D9="","",'1. Inversión Inicial'!$B$47+D21+'2. P&amp;L 3 Años'!$B$38-'7. Financiación'!$B$45),"")</f>
-        <v>182785.28</v>
-      </c>
-      <c r="E26" s="41" t="inlineStr">
-        <is>
-          <t>En «Realista» es el saldo REAL del mes 12 de la hoja de tesorería, con su desfase de cobros y pagos y su liquidación de IVA. En «Pesimista» y «Optimista» es un saldo estimado (sin efecto de cobros/pagos ni IVA) — ver Tesorería: fondo de maniobra más el resultado del año, devolviendo la amortización (que no se paga) y restando el principal del préstamo. En rojo, el escenario se queda sin caja</t>
-        </is>
-      </c>
-      <c r="F26" s="44" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="44" t="n"/>
-      <c r="B27" s="44" t="n"/>
-      <c r="C27" s="44" t="n"/>
       <c r="D27" s="44" t="n"/>
-      <c r="E27" s="44" t="n"/>
+      <c r="E27" s="44" t="inlineStr">
+        <is>
+          <t>El saldo REAL del caso base, con su desfase de cobros y pagos y su liquidación de IVA. Sólo existe para el escenario realista, que es el único con tesorería mensual propia: por eso no está en la fila de arriba, donde se compararía contra dos estimaciones</t>
+        </is>
+      </c>
       <c r="F27" s="44" t="n"/>
     </row>
-    <row r="28" ht="150" customHeight="1">
-      <c r="A28" s="63" t="inlineStr">
-        <is>
-          <t>La columna «Realista» lee sus tres datos de la hoja de Supuestos, así que reproduce EXACTAMENTE el año 1 del P&amp;L. Los otros dos escenarios usan las mismas tasas de coste: lo único que cambia son los cubiertos, el ticket y los días. Los COSTES FIJOS sí son los mismos en los tres: los varios e imprevistos, que son un porcentaje de las ventas, van arriba con los variables y cada escenario carga los suyos.</t>
-        </is>
-      </c>
+    <row r="28">
+      <c r="A28" s="44" t="n"/>
       <c r="B28" s="44" t="n"/>
       <c r="C28" s="44" t="n"/>
       <c r="D28" s="44" t="n"/>
       <c r="E28" s="44" t="n"/>
       <c r="F28" s="44" t="n"/>
     </row>
-    <row r="29">
-      <c r="A29" s="44" t="inlineStr">
-        <is>
-          <t>NOTA: El escenario pesimista refleja un arranque lento con menor afluencia. El optimista asume alta ocupación y ticket medio superior. Los costes fijos son constantes en los 3 escenarios.</t>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="63" t="inlineStr">
+        <is>
+          <t>La columna «Realista» lee sus tres datos de la hoja de Supuestos, así que reproduce EXACTAMENTE el año 1 del P&amp;L. Los otros dos escenarios usan las mismas tasas de coste: lo único que cambia son los cubiertos, el ticket y los días. Los COSTES FIJOS sí son los mismos en los tres: los varios e imprevistos, que son un porcentaje de las ventas, van arriba con los variables y cada escenario carga los suyos.</t>
         </is>
       </c>
       <c r="B29" s="44" t="n"/>
@@ -6118,7 +6354,7 @@
     <row r="30">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
+          <t>NOTA: El escenario pesimista refleja un arranque lento con menor afluencia. El optimista asume alta ocupación y ticket medio superior. Los costes fijos son constantes en los 3 escenarios.</t>
         </is>
       </c>
       <c r="B30" s="44" t="n"/>
@@ -6126,6 +6362,13 @@
       <c r="D30" s="44" t="n"/>
       <c r="E30" s="44" t="n"/>
       <c r="F30" s="44" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ChefBusiness.co — Plan de Negocio: Bar-Restaurante</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
@@ -6614,7 +6857,7 @@
     <row r="14">
       <c r="A14" s="41" t="inlineStr">
         <is>
-          <t>CRECIMIENTO DE LA PLANTILLA (coste escalonado, RD-10)</t>
+          <t>CRECIMIENTO DE LA PLANTILLA (coste escalonado)</t>
         </is>
       </c>
       <c r="B14" s="44" t="n"/>
@@ -6741,7 +6984,7 @@
       <c r="G20" s="44" t="n"/>
       <c r="H20" s="44" t="n"/>
       <c r="I20" s="44" t="n"/>
-      <c r="J20" s="55" t="inlineStr">
+      <c r="J20" s="44" t="inlineStr">
         <is>
           <t>Art. 34.1 del Estatuto de los Trabajadores; tu convenio provincial puede fijar menos</t>
         </is>
@@ -6763,9 +7006,9 @@
       <c r="G21" s="44" t="n"/>
       <c r="H21" s="44" t="n"/>
       <c r="I21" s="44" t="n"/>
-      <c r="J21" s="55" t="inlineStr">
-        <is>
-          <t>52 semanas menos las vacaciones del art. 38 ET (30 días naturales)</t>
+      <c r="J21" s="44" t="inlineStr">
+        <is>
+          <t>46 semanas: 52 menos las vacaciones (30 días naturales, art. 38 ET), los festivos y las ausencias medias</t>
         </is>
       </c>
     </row>
@@ -6785,7 +7028,7 @@
       <c r="G22" s="44" t="n"/>
       <c r="H22" s="44" t="n"/>
       <c r="I22" s="44" t="n"/>
-      <c r="J22" s="60" t="inlineStr">
+      <c r="J22" s="44" t="inlineStr">
         <is>
           <t>De la apertura al cierre, barra incluida. Cuéntalas sobre tu horario real</t>
         </is>
@@ -6807,7 +7050,7 @@
       <c r="G23" s="44" t="n"/>
       <c r="H23" s="44" t="n"/>
       <c r="I23" s="44" t="n"/>
-      <c r="J23" s="60" t="inlineStr">
+      <c r="J23" s="44" t="inlineStr">
         <is>
           <t>Media de presencia simultánea entre cocina, barra y sala. En los dos servicios fuertes hará falta más y a media tarde menos</t>
         </is>
@@ -6820,7 +7063,7 @@
         </is>
       </c>
       <c r="B24" s="55">
-        <f>IFERROR(B22*B23*'0. Supuestos'!$B$6,"")</f>
+        <f>IFERROR(IF(OR(B22="",B23="",'0. Supuestos'!$B$6=""),"",B22*B23*'0. Supuestos'!$B$6),"")</f>
         <v>8060.0</v>
       </c>
       <c r="C24" s="44" t="n"/>
@@ -6961,13 +7204,12 @@
     <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B15 B16 B20 B21 B22 D6 D7 D8 D9 D10 D11 D12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
+    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Escribe un número mayor o igual que 0; esta celda admite decimales (1,7 personas es una presencia media, no una persona y media)." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
     <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje no válido" error="Escribe un porcentaje entre 0 y 1 (0,35 = 35 %)." type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Recuento no válido" error="Escribe un número ENTERO de 1 en adelante: esta celda es un recuento y varias fórmulas dividen entre ella." type="whole" operator="between">
-      <formula1>1</formula1>
-      <formula2>100000</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -7063,7 +7305,7 @@
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="63" t="inlineStr">
         <is>
-          <t>3. Sólo «3. Punto Equilibrio» se deriva entera de lo anterior. En las otras tres hojas sí hay celdas verdes que puedes tocar: el escenario pesimista y el optimista en «4. Escenarios», la estacionalidad y la rampa de arranque en «6. Tesorería 12 meses», y las cuatro fuentes alternativas de financiación en «7. Financiación». Todo lo demás se calcula.</t>
+          <t>3. En «3. Punto Equilibrio» sólo se teclea el techo de rotaciones que da tu local; todo lo demás se deriva de lo anterior. En las otras tres hojas también hay celdas verdes que puedes tocar: el escenario pesimista y el optimista en «4. Escenarios», la estacionalidad y la rampa de arranque en «6. Tesorería 12 meses», y las cuatro fuentes alternativas de financiación en «7. Financiación». Todo lo demás se calcula.</t>
         </is>
       </c>
       <c r="B7" s="44" t="n"/>
@@ -7071,10 +7313,10 @@
       <c r="D7" s="44" t="n"/>
       <c r="E7" s="44" t="n"/>
     </row>
-    <row r="8" ht="105" customHeight="1">
+    <row r="8" ht="165" customHeight="1">
       <c r="A8" s="63" t="inlineStr">
         <is>
-          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide entre 1,10: en sala, la comida y la bebida (alcohol incluido) van al tipo reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA). El 21 % es el tipo general y en hostelería sólo alcanza a lo que sale del local como entrega de bienes excluida del tipo reducido: el alcohol y los refrescos o zumos con azúcares añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica al alcohol del canal de delivery. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
+          <t>4. Todas las cifras van SIN IVA. Para pasar un PVP a precio sin IVA, divide por el tipo que le corresponda: entre 1,10 en sala (comida y bebida, alcohol incluido: art. 91.Uno.2.2.º de la Ley 37/1992 del IVA) y, cuando se venden para llevar, los alimentos —bollería y pastelería incluidas—, que son productos alimenticios al tipo reducido por el art. 91.Uno.1.1.º; y entre 1,21 el tipo general, que en hostelería sólo alcanza a lo que sale del local como entrega de bienes excluida del reducido: el alcohol y los refrescos o zumos con azúcares añadidos para llevar o a domicilio (la comida para llevar sigue al 10 %); el libro lo aplica al alcohol del canal de delivery. El tipo de cada línea de venta está en la columna «Tipo de IVA de la línea» del P&amp;L y de ahí salen los cobros, el IVA repercutido y el PVP equivalente. El IVA de la inversión se adelanta y se recupera con el modelo 303.</t>
         </is>
       </c>
       <c r="B8" s="44" t="n"/>
@@ -7242,7 +7484,7 @@
       </c>
       <c r="B20" s="46">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$58="","",'2. P&amp;L 3 Años'!$B$58),"")</f>
-        <v>0.10840889755405879</v>
+        <v>0.10772153048564333</v>
       </c>
       <c r="C20" s="46">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$E$58="","",'2. P&amp;L 3 Años'!$E$58),"")</f>
@@ -7300,7 +7542,7 @@
       </c>
       <c r="B24" s="48">
         <f>IFERROR(IF('1. Inversión Inicial'!$B$48="","",'1. Inversión Inicial'!$B$48),"")</f>
-        <v>179164.80000000002</v>
+        <v>179014.80000000002</v>
       </c>
       <c r="C24" s="44" t="n"/>
       <c r="D24" s="44" t="n"/>
@@ -7314,7 +7556,7 @@
       </c>
       <c r="B25" s="48">
         <f>IFERROR(IF('1. Inversión Inicial'!$B$51="","",'1. Inversión Inicial'!$B$51),"")</f>
-        <v>201899.40000000002</v>
+        <v>201717.90000000002</v>
       </c>
       <c r="C25" s="44" t="n"/>
       <c r="D25" s="44" t="n"/>
@@ -7356,7 +7598,7 @@
       </c>
       <c r="B28" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$50="","",'2. P&amp;L 3 Años'!$B$50),"")</f>
-        <v>48931.43999999997</v>
+        <v>48621.18999999997</v>
       </c>
       <c r="C28" s="44" t="n"/>
       <c r="D28" s="44" t="n"/>
@@ -7365,12 +7607,12 @@
     <row r="29">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>Cubiertos/día para el punto de equilibrio</t>
+          <t>Cubiertos/día para el punto de equilibrio CONTABLE (con la amortización dentro)</t>
         </is>
       </c>
       <c r="B29" s="60">
         <f>IFERROR(IF('3. Punto Equilibrio'!$B$16="","",'3. Punto Equilibrio'!$B$16),"")</f>
-        <v>65.10483159411817</v>
+        <v>65.19927447170208</v>
       </c>
       <c r="C29" s="44" t="n"/>
       <c r="D29" s="44" t="n"/>
@@ -7379,12 +7621,12 @@
     <row r="30">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>Payback del proyecto (años)</t>
-        </is>
-      </c>
-      <c r="B30" s="60">
+          <t>Payback del proyecto (años), antes de la deuda</t>
+        </is>
+      </c>
+      <c r="B30" s="44">
         <f>IFERROR(IF('6. Tesorería 12 meses'!$B$31="","",'6. Tesorería 12 meses'!$B$31),"")</f>
-        <v>2.7487932827490225</v>
+        <v>2.3</v>
       </c>
       <c r="C30" s="44" t="n"/>
       <c r="D30" s="44" t="n"/>
@@ -7421,7 +7663,7 @@
       </c>
       <c r="C33" s="41" t="inlineStr">
         <is>
-          <t>v2.1</t>
+          <t>v2.2</t>
         </is>
       </c>
       <c r="D33" s="41" t="inlineStr">
@@ -7432,17 +7674,17 @@
       <c r="E33" s="44" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="79" t="inlineStr">
+      <c r="A34" s="81" t="inlineStr">
         <is>
           <t>Coste de personal imputado al P&amp;L</t>
         </is>
       </c>
-      <c r="B34" s="79" t="inlineStr">
+      <c r="B34" s="81" t="inlineStr">
         <is>
           <t>115.200 €</t>
         </is>
       </c>
-      <c r="C34" s="79" t="inlineStr">
+      <c r="C34" s="81" t="inlineStr">
         <is>
           <t>Sale de la hoja Personal, por fórmula</t>
         </is>
@@ -7455,17 +7697,17 @@
       <c r="E34" s="44" t="n"/>
     </row>
     <row r="35" ht="45" customHeight="1">
-      <c r="A35" s="79" t="inlineStr">
+      <c r="A35" s="81" t="inlineStr">
         <is>
           <t>Plantilla</t>
         </is>
       </c>
-      <c r="B35" s="79" t="inlineStr">
+      <c r="B35" s="81" t="inlineStr">
         <is>
           <t>7 personas / 209.171 €</t>
         </is>
       </c>
-      <c r="C35" s="79" t="inlineStr">
+      <c r="C35" s="81" t="inlineStr">
         <is>
           <t>7 puestos, tres a tiempo parcial (uno de ellos, suplencias) / 151.939 €</t>
         </is>
@@ -7478,17 +7720,17 @@
       <c r="E35" s="44" t="n"/>
     </row>
     <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="79" t="inlineStr">
+      <c r="A36" s="81" t="inlineStr">
         <is>
           <t>Cubiertos/día del año 1</t>
         </is>
       </c>
-      <c r="B36" s="79" t="inlineStr">
+      <c r="B36" s="81" t="inlineStr">
         <is>
           <t>55</t>
         </is>
       </c>
-      <c r="C36" s="79" t="inlineStr">
+      <c r="C36" s="81" t="inlineStr">
         <is>
           <t>80</t>
         </is>
@@ -7501,17 +7743,17 @@
       <c r="E36" s="44" t="n"/>
     </row>
     <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="79" t="inlineStr">
+      <c r="A37" s="81" t="inlineStr">
         <is>
           <t>Ticket medio</t>
         </is>
       </c>
-      <c r="B37" s="79" t="inlineStr">
+      <c r="B37" s="81" t="inlineStr">
         <is>
           <t>18,50 € (sin declarar IVA)</t>
         </is>
       </c>
-      <c r="C37" s="79" t="inlineStr">
+      <c r="C37" s="81" t="inlineStr">
         <is>
           <t>18,20 € SIN IVA</t>
         </is>
@@ -7524,17 +7766,17 @@
       <c r="E37" s="44" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="79" t="inlineStr">
+      <c r="A38" s="81" t="inlineStr">
         <is>
           <t>Alquiler</t>
         </is>
       </c>
-      <c r="B38" s="79" t="inlineStr">
+      <c r="B38" s="81" t="inlineStr">
         <is>
           <t>3.000 €/mes</t>
         </is>
       </c>
-      <c r="C38" s="79" t="inlineStr">
+      <c r="C38" s="81" t="inlineStr">
         <is>
           <t>3.000 €/mes (sin cambio)</t>
         </is>
@@ -7547,17 +7789,17 @@
       <c r="E38" s="44" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="79" t="inlineStr">
+      <c r="A39" s="81" t="inlineStr">
         <is>
           <t>Suministros</t>
         </is>
       </c>
-      <c r="B39" s="79" t="inlineStr">
+      <c r="B39" s="81" t="inlineStr">
         <is>
           <t>1.200 €/mes</t>
         </is>
       </c>
-      <c r="C39" s="79" t="inlineStr">
+      <c r="C39" s="81" t="inlineStr">
         <is>
           <t>1.800 €/mes</t>
         </is>
@@ -7570,17 +7812,17 @@
       <c r="E39" s="44" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="79" t="inlineStr">
+      <c r="A40" s="81" t="inlineStr">
         <is>
           <t>Fondo de maniobra</t>
         </is>
       </c>
-      <c r="B40" s="79" t="inlineStr">
+      <c r="B40" s="81" t="inlineStr">
         <is>
           <t>30.000 € etiquetados «3 meses»</t>
         </is>
       </c>
-      <c r="C40" s="79" t="inlineStr">
+      <c r="C40" s="81" t="inlineStr">
         <is>
           <t>3 × costes fijos de caja mensuales, por fórmula</t>
         </is>
@@ -7593,17 +7835,17 @@
       <c r="E40" s="44" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="79" t="inlineStr">
+      <c r="A41" s="81" t="inlineStr">
         <is>
           <t>Amortización</t>
         </is>
       </c>
-      <c r="B41" s="79" t="inlineStr">
+      <c r="B41" s="81" t="inlineStr">
         <is>
           <t>5.000 €/año (base implícita 50.000 €)</t>
         </is>
       </c>
-      <c r="C41" s="79" t="inlineStr">
+      <c r="C41" s="81" t="inlineStr">
         <is>
           <t>Base amortizable real / vida útil, por fórmula</t>
         </is>
@@ -7616,17 +7858,17 @@
       <c r="E41" s="44" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="79" t="inlineStr">
+      <c r="A42" s="81" t="inlineStr">
         <is>
           <t>Cuota del préstamo en el P&amp;L</t>
         </is>
       </c>
-      <c r="B42" s="79" t="inlineStr">
+      <c r="B42" s="81" t="inlineStr">
         <is>
           <t>7.200 €/año de cuota completa</t>
         </is>
       </c>
-      <c r="C42" s="79" t="inlineStr">
+      <c r="C42" s="81" t="inlineStr">
         <is>
           <t>sólo los intereses; el principal va a tesorería</t>
         </is>
@@ -7639,17 +7881,17 @@
       <c r="E42" s="44" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="79" t="inlineStr">
+      <c r="A43" s="81" t="inlineStr">
         <is>
           <t>Impuesto de Sociedades</t>
         </is>
       </c>
-      <c r="B43" s="79" t="inlineStr">
+      <c r="B43" s="81" t="inlineStr">
         <is>
           <t>25 % en los años 2 y 3, sin compensar la BIN</t>
         </is>
       </c>
-      <c r="C43" s="79" t="inlineStr">
+      <c r="C43" s="81" t="inlineStr">
         <is>
           <t>15 % los dos primeros ejercicios con base positiva y compensación de bases negativas</t>
         </is>
@@ -7662,17 +7904,17 @@
       <c r="E43" s="44" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="79" t="inlineStr">
+      <c r="A44" s="81" t="inlineStr">
         <is>
           <t>Comisiones de delivery</t>
         </is>
       </c>
-      <c r="B44" s="79" t="inlineStr">
+      <c r="B44" s="81" t="inlineStr">
         <is>
           <t>5 % de TODA la facturación, sin interruptor</t>
         </is>
       </c>
-      <c r="C44" s="79" t="inlineStr">
+      <c r="C44" s="81" t="inlineStr">
         <is>
           <t>% del canal × comisión de la plataforma, a 0 por defecto</t>
         </is>
@@ -7685,17 +7927,17 @@
       <c r="E44" s="44" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="79" t="inlineStr">
+      <c r="A45" s="81" t="inlineStr">
         <is>
           <t>Coste de la bebida</t>
         </is>
       </c>
-      <c r="B45" s="79" t="inlineStr">
+      <c r="B45" s="81" t="inlineStr">
         <is>
           <t>food cost del 30 % sobre el total MÁS un 22 % sobre la bebida</t>
         </is>
       </c>
-      <c r="C45" s="79" t="inlineStr">
+      <c r="C45" s="81" t="inlineStr">
         <is>
           <t>cada familia paga su propio coste</t>
         </is>
@@ -8001,7 +8243,7 @@
     <row r="63">
       <c r="A63" s="80" t="inlineStr">
         <is>
-          <t>Versión 2.1 · septiembre 2026 · aichef.pro/plan-negocio-bar-restaurante · info@aichef.pro</t>
+          <t>Versión 2.2 · septiembre 2026 · aichef.pro/plan-negocio-bar-restaurante · info@aichef.pro</t>
         </is>
       </c>
       <c r="B63" s="44" t="n"/>
@@ -8395,51 +8637,51 @@
         </is>
       </c>
       <c r="B9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*B7*(1-MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*B7*(1-MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>21309.07874788193</v>
       </c>
       <c r="C9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(C7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+B7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(C7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+B7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>25504.476589672704</v>
       </c>
       <c r="D9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(D7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+C7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(D7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+C7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>33131.4663337198</v>
       </c>
       <c r="E9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(E7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+D7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(E7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+D7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>38577.7347721395</v>
       </c>
       <c r="F9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(F7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+E7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(F7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+E7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>45330.2220636761</v>
       </c>
       <c r="G9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(G7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+F7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(G7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+F7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>48706.465709444405</v>
       </c>
       <c r="H9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(H7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+G7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(H7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+G7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>47046.01801480426</v>
       </c>
       <c r="I9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(I7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+H7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(I7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+H7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>34315.9190225631</v>
       </c>
       <c r="J9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(J7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+I7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(J7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+I7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>47046.01801480426</v>
       </c>
       <c r="K9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(K7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+J7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(K7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+J7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>48706.465709444405</v>
       </c>
       <c r="L9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(L7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+K7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(L7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+K7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>48152.98314456435</v>
       </c>
       <c r="M9" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39)))*(M7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+L7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",('2. P&amp;L 3 Años'!$B$10+'2. P&amp;L 3 Años'!$B$10*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12))*(M7*(1-MIN(30,'0. Supuestos'!$B$58)/30)+L7*MIN(30,'0. Supuestos'!$B$58)/30)),"")</f>
         <v>58669.1518772853</v>
       </c>
       <c r="N9" s="48">
@@ -8531,10 +8773,9 @@
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B11:M11)),"")</f>
         <v>-141152.1916395042</v>
       </c>
-      <c r="O11" s="44" t="inlineStr">
-        <is>
-          <t>Materia prima, consumibles, comisiones e imprevistos, cada uno con SU tipo de IVA (la columna del P&amp;L) y con los días de pago a proveedor de Supuestos</t>
-        </is>
+      <c r="O11" s="44" t="str">
+        <f>IFERROR("Materia prima, consumibles, comisiones e imprevistos, cada uno con SU tipo de IVA (la columna del P&amp;L) y con los días de pago a proveedor de Supuestos."&amp;IF('0. Supuestos'!$B$59=0,""," Con "&amp;TEXT('0. Supuestos'!$B$59,"0")&amp;" días de pago, las primeras compras se pagan ya en el año siguiente: la columna «Año» de esta fila recoge "&amp;TEXT(MAX(0,12-ROUNDUP('0. Supuestos'!$B$59/30,0)),"0")&amp;" mensualidades de compra, no el coste del ejercicio."),"")</f>
+        <v>Materia prima, consumibles, comisiones e imprevistos, cada uno con SU tipo de IVA (la columna del P&amp;L) y con los días de pago a proveedor de Supuestos. Con 30 días de pago, las primeras compras se pagan ya en el año siguiente: la columna «Año» de esta fila recoge 11 mensualidades de compra, no el coste del ejercicio.</v>
       </c>
     </row>
     <row r="12">
@@ -8792,51 +9033,51 @@
         </is>
       </c>
       <c r="B16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*B7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*B7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>1937.1889770801754</v>
       </c>
       <c r="C16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*C7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*C7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>2318.588780879337</v>
       </c>
       <c r="D16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*D7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*D7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>3011.9514848836184</v>
       </c>
       <c r="E16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*E7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*E7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>3507.066797467227</v>
       </c>
       <c r="F16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*F7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*F7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>4120.92927851601</v>
       </c>
       <c r="G16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*G7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*G7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>4427.8605190404005</v>
       </c>
       <c r="H16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*H7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*H7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>4276.910728618569</v>
       </c>
       <c r="I16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*I7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*I7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>3119.6290020511915</v>
       </c>
       <c r="J16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*J7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*J7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>4276.910728618569</v>
       </c>
       <c r="K16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*K7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*K7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>4427.8605190404005</v>
       </c>
       <c r="L16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*L7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*L7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>4377.543922233123</v>
       </c>
       <c r="M16" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*M7*('0. Supuestos'!$B$11*'0. Supuestos'!$B$39+'0. Supuestos'!$B$12*('0. Supuestos'!$B$62*((1-'0. Supuestos'!$B$16)*'0. Supuestos'!$B$63+'0. Supuestos'!$B$16*'0. Supuestos'!$B$40)+(1-'0. Supuestos'!$B$62)*'0. Supuestos'!$B$39))),"")</f>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$10*M7*SUMPRODUCT('2. P&amp;L 3 Años'!$E$11:$E$12,'2. P&amp;L 3 Años'!$G$11:$G$12)),"")</f>
         <v>5333.559261571391</v>
       </c>
       <c r="N16" s="48">
@@ -8845,7 +9086,7 @@
       </c>
       <c r="O16" s="44" t="inlineStr">
         <is>
-          <t>La bebida va al tipo que sale de la hoja de Supuestos: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por delivery, al general</t>
+          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en sala, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por delivery, al general; el pan común y las harinas panificables, al superreducido (art. 91.Dos.1.1.º)</t>
         </is>
       </c>
     </row>
@@ -8924,19 +9165,19 @@
       <c r="D18" s="44" t="n"/>
       <c r="E18" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'1. Inversión Inicial'!$B$50),"")</f>
-        <v>22734.6</v>
+        <v>22703.1</v>
       </c>
       <c r="F18" s="44" t="n"/>
       <c r="G18" s="44" t="n"/>
       <c r="H18" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",MAX(0,-E19)),"")</f>
-        <v>22631.217210680457</v>
+        <v>22599.717210680457</v>
       </c>
       <c r="I18" s="44" t="n"/>
       <c r="J18" s="44" t="n"/>
       <c r="K18" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",MAX(0,-H19)),"")</f>
-        <v>19637.337701396587</v>
+        <v>19605.837701396587</v>
       </c>
       <c r="L18" s="44" t="n"/>
       <c r="M18" s="44" t="n"/>
@@ -8958,19 +9199,19 @@
       <c r="D19" s="44" t="n"/>
       <c r="E19" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(B16:D16)-SUM(B17:D17)-E18),"")</f>
-        <v>-22631.217210680457</v>
+        <v>-22599.717210680457</v>
       </c>
       <c r="F19" s="44" t="n"/>
       <c r="G19" s="44" t="n"/>
       <c r="H19" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(E16:G16)-SUM(E17:G17)-H18),"")</f>
-        <v>-19637.337701396587</v>
+        <v>-19605.837701396587</v>
       </c>
       <c r="I19" s="44" t="n"/>
       <c r="J19" s="44" t="n"/>
       <c r="K19" s="48">
         <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",SUM(H16:J16)-SUM(H17:J17)-K18),"")</f>
-        <v>-16874.309128133405</v>
+        <v>-16842.809128133405</v>
       </c>
       <c r="L19" s="44" t="n"/>
       <c r="M19" s="44" t="n"/>
@@ -9014,7 +9255,7 @@
       </c>
       <c r="O20" s="44" t="inlineStr">
         <is>
-          <t>Sólo sale caja cuando el resultado del trimestre es positivo. Los meses sin liquidación van en blanco, no a cero</t>
+          <t>Sólo sale caja cuando el resultado del trimestre es positivo. Los meses sin liquidación van en blanco, no a cero. La celda se pinta en ROJO cuando el pago del 303 se lleva más caja de la que queda ese mes</t>
         </is>
       </c>
     </row>
@@ -9215,17 +9456,17 @@
     <row r="26">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>Flujo de caja libre del año 1 (tabla mensual)</t>
+          <t>Flujo de caja libre antes de la deuda, año 1</t>
         </is>
       </c>
       <c r="B26" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",N21),"")</f>
-        <v>94988.6083604959</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$50+'2. P&amp;L 3 Años'!$B$38+'7. Financiación'!$B$44),"")</f>
+        <v>65062.18999999997</v>
       </c>
       <c r="C26" s="44" t="n"/>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>Es la suma de los doce FLUJO DEL MES de arriba: ya lleva descontados el principal del préstamo y el IVA</t>
+          <t>Resultado neto más amortización (que no se paga) más los intereses de ese año: el principal no se resta porque este flujo es ANTES de la deuda. La MISMA base que los años 2 y 3, para que el payback compare peras con peras</t>
         </is>
       </c>
       <c r="E26" s="44" t="n"/>
@@ -9243,17 +9484,17 @@
     <row r="27">
       <c r="A27" s="44" t="inlineStr">
         <is>
-          <t>Flujo de caja libre estimado del año 2</t>
+          <t>Flujo de caja libre antes de la deuda, año 2</t>
         </is>
       </c>
       <c r="B27" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$C$50+'2. P&amp;L 3 Años'!$C$38-'7. Financiación'!$B$47),"")</f>
-        <v>60157.4595552134</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$C$50+'2. P&amp;L 3 Años'!$C$38+'7. Financiación'!$B$46),"")</f>
+        <v>86242.626</v>
       </c>
       <c r="C27" s="44" t="n"/>
       <c r="D27" s="44" t="inlineStr">
         <is>
-          <t>Resultado neto más amortización menos la devolución de principal de ese año. Sin tabla mensual, es una estimación</t>
+          <t>Resultado neto más amortización (que no se paga) más los intereses de ese año: el principal no se resta porque este flujo es ANTES de la deuda. Sin tabla mensual, es una estimación</t>
         </is>
       </c>
       <c r="E27" s="44" t="n"/>
@@ -9271,17 +9512,17 @@
     <row r="28">
       <c r="A28" s="44" t="inlineStr">
         <is>
-          <t>Flujo de caja libre estimado del año 3</t>
+          <t>Flujo de caja libre antes de la deuda, año 3</t>
         </is>
       </c>
       <c r="B28" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$D$50+'2. P&amp;L 3 Años'!$D$38-'7. Financiación'!$B$49),"")</f>
-        <v>62438.236508541595</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$D$50+'2. P&amp;L 3 Años'!$D$38+'7. Financiación'!$B$48),"")</f>
+        <v>88559.90295332819</v>
       </c>
       <c r="C28" s="44" t="n"/>
       <c r="D28" s="44" t="inlineStr">
         <is>
-          <t>Resultado neto más amortización menos la devolución de principal de ese año. Sin tabla mensual, es una estimación</t>
+          <t>Resultado neto más amortización (que no se paga) más los intereses de ese año: el principal no se resta porque este flujo es ANTES de la deuda. Sin tabla mensual, es una estimación</t>
         </is>
       </c>
       <c r="E28" s="44" t="n"/>
@@ -9299,17 +9540,17 @@
     <row r="29">
       <c r="A29" s="44" t="inlineStr">
         <is>
-          <t>Contraste: resultado + amortización - principal (año 1)</t>
+          <t>Informativo: flujo REAL de caja del año 1 (tabla mensual, antes de la deuda)</t>
         </is>
       </c>
       <c r="B29" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'2. P&amp;L 3 Años'!$B$50+'2. P&amp;L 3 Años'!$B$38-'7. Financiación'!$B$45),"")</f>
-        <v>57327.43999999997</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",N21+'7. Financiación'!$B$44+'7. Financiación'!$B$45),"")</f>
+        <v>102668.6083604959</v>
       </c>
       <c r="C29" s="44" t="n"/>
       <c r="D29" s="44" t="inlineStr">
         <is>
-          <t>La misma fórmula que los años 2 y 3, aplicada al año 1. La diferencia con la fila de arriba es el efecto del IVA y del desfase de cobros y pagos</t>
+          <t>La suma de los doce FLUJO DEL MES de arriba, devolviéndole los intereses y el principal que se pagaron ese año. NO es la que usa el payback: lleva dentro el IVA que todavía no se ha liquidado y el crédito del proveedor, dos cosas que hay que devolver y que los años 2 y 3 no tienen</t>
         </is>
       </c>
       <c r="E29" s="44" t="n"/>
@@ -9327,17 +9568,17 @@
     <row r="30">
       <c r="A30" s="44" t="inlineStr">
         <is>
-          <t>Inversión a recuperar</t>
+          <t>Inversión a recuperar (sin el IVA, que se recupera por el 303)</t>
         </is>
       </c>
       <c r="B30" s="48">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'1. Inversión Inicial'!$B$51),"")</f>
-        <v>201899.40000000002</v>
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",'1. Inversión Inicial'!$B$51-'1. Inversión Inicial'!$B$50),"")</f>
+        <v>179014.80000000002</v>
       </c>
       <c r="C30" s="44" t="n"/>
       <c r="D30" s="44" t="inlineStr">
         <is>
-          <t>La APORTACIÓN TOTAL que hay que poner sobre la mesa, IVA incluido: es lo que de verdad se desembolsa. El fondo de maniobra se recupera al cerrar, pero hasta entonces está inmovilizado</t>
+          <t>CAPEX más fondo de maniobra: la necesidad total de caja MENOS el IVA soportado de la inversión, que no se pierde (se recupera con el modelo 303 y esta misma hoja lo compensa trimestre a trimestre). El fondo de maniobra sí se recupera al cerrar, pero hasta entonces está inmovilizado</t>
         </is>
       </c>
       <c r="E30" s="44" t="n"/>
@@ -9355,17 +9596,17 @@
     <row r="31">
       <c r="A31" s="41" t="inlineStr">
         <is>
-          <t>Payback del proyecto (años)</t>
-        </is>
-      </c>
-      <c r="B31" s="61">
-        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",IF(B26&gt;=B30,B30/B26,IF(B26+B27&gt;=B30,1+(B30-B26)/B27,IF(B26+B27+B28&gt;=B30,2+(B30-B26-B27)/B28,"Más de 3 años")))),"")</f>
-        <v>2.7487932827490225</v>
+          <t>Payback del proyecto (años), antes de la deuda</t>
+        </is>
+      </c>
+      <c r="B31" s="41">
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",IF(B26&gt;=B30,ROUND(B30/B26,1),IF(B26+B27&gt;=B30,ROUND(1+(B30-B26)/B27,1),IF(B26+B27+B28&gt;=B30,ROUND(2+(B30-B26-B27)/B28,1),"Más de 3 años")))),"")</f>
+        <v>2.3</v>
       </c>
       <c r="C31" s="44" t="n"/>
       <c r="D31" s="41" t="inlineStr">
         <is>
-          <t>ÚNICO payback del pack: la aportación total entre el flujo de caja libre DESPUÉS de pagar el préstamo. El Word cita esta celda, no recalcula</t>
+          <t>Mide cuánto tarda el negocio en devolver la inversión con lo que genera ANTES de pagar al banco, con la MISMA base de flujo en los tres años; si puedes pagar la cuota lo dice el DSCR de la hoja de Financiación. El documento Word del pack sigue en la versión 1.1 y no lee esta celda: las cifras válidas son las de este libro</t>
         </is>
       </c>
       <c r="E31" s="44" t="n"/>
@@ -9381,10 +9622,21 @@
       <c r="O31" s="44" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="44" t="n"/>
-      <c r="B32" s="44" t="n"/>
+      <c r="A32" s="44" t="inlineStr">
+        <is>
+          <t>Payback sobre el CAPEX, sin fondo de maniobra (años)</t>
+        </is>
+      </c>
+      <c r="B32" s="44">
+        <f>IFERROR(IF('2. P&amp;L 3 Años'!$B$10="","",IF(B26&gt;='1. Inversión Inicial'!$B$49,ROUND('1. Inversión Inicial'!$B$49/B26,1),IF(B26+B27&gt;='1. Inversión Inicial'!$B$49,ROUND(1+('1. Inversión Inicial'!$B$49-B26)/B27,1),IF(B26+B27+B28&gt;='1. Inversión Inicial'!$B$49,ROUND(2+('1. Inversión Inicial'!$B$49-B26-B27)/B28,1),"Más de 3 años")))),"")</f>
+        <v>1.6</v>
+      </c>
       <c r="C32" s="44" t="n"/>
-      <c r="D32" s="44" t="n"/>
+      <c r="D32" s="44" t="inlineStr">
+        <is>
+          <t>El mismo cálculo sobre lo que se COMPRA (obra, equipamiento, lanzamiento y constitución), sin el fondo de maniobra: ese dinero no se gasta, se inmoviliza y vuelve al cerrar el negocio. Informativo: el payback que se publica es el de arriba</t>
+        </is>
+      </c>
       <c r="E32" s="44" t="n"/>
       <c r="F32" s="44" t="n"/>
       <c r="G32" s="44" t="n"/>
@@ -9397,12 +9649,8 @@
       <c r="N32" s="44" t="n"/>
       <c r="O32" s="44" t="n"/>
     </row>
-    <row r="33" ht="120" customHeight="1">
-      <c r="A33" s="63" t="inlineStr">
-        <is>
-          <t>El IVA del cuarto trimestre se liquida en enero del año siguiente, así que no aparece en este cuadro. El Impuesto de Sociedades del año 1 se paga en julio del año 2. La cuota del préstamo se reparte en doce partes iguales siguiendo el cuadro ANUAL de la hoja de Financiación, y las nóminas en doce mensualidades más las dos pagas extra en su mes.</t>
-        </is>
-      </c>
+    <row r="33">
+      <c r="A33" s="44" t="n"/>
       <c r="B33" s="44" t="n"/>
       <c r="C33" s="44" t="n"/>
       <c r="D33" s="44" t="n"/>
@@ -9418,8 +9666,12 @@
       <c r="N33" s="44" t="n"/>
       <c r="O33" s="44" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="44" t="n"/>
+    <row r="34" ht="120" customHeight="1">
+      <c r="A34" s="63" t="inlineStr">
+        <is>
+          <t>El IVA del cuarto trimestre se liquida en enero del año siguiente, así que no aparece en este cuadro. El Impuesto de Sociedades del año 1 se paga en julio del año 2. La cuota del préstamo se reparte en doce partes iguales siguiendo el cuadro ANUAL de la hoja de Financiación, y las nóminas en doce mensualidades más las dos pagas extra en su mes.</t>
+        </is>
+      </c>
       <c r="B34" s="44" t="n"/>
       <c r="C34" s="44" t="n"/>
       <c r="D34" s="44" t="n"/>
@@ -10065,43 +10317,40 @@
       <formula>AND(ISNUMBER(B22),B22&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B20:M20">
+    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+      <formula>AND(ISNUMBER(B20),-B20&gt;B22)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B23">
-    <cfRule type="expression" priority="5" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="6" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(B23),B23&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="7" dxfId="0" stopIfTrue="1">
       <formula>AND(ISNUMBER(B23),B23&gt;=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E19:K19">
-    <cfRule type="expression" priority="7" dxfId="1" stopIfTrue="1">
-      <formula>AND(ISNUMBER(E19),E19&lt;0)</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="0" stopIfTrue="1">
-      <formula>AND(ISNUMBER(E19),E19&gt;0)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="B26">
-    <cfRule type="expression" priority="9" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="8" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(B26),B26&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="9" dxfId="0" stopIfTrue="1">
       <formula>AND(ISNUMBER(B26),B26&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B27">
-    <cfRule type="expression" priority="11" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="10" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(B27),B27&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="11" dxfId="0" stopIfTrue="1">
       <formula>AND(ISNUMBER(B27),B27&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B28">
-    <cfRule type="expression" priority="13" dxfId="1" stopIfTrue="1">
+    <cfRule type="expression" priority="12" dxfId="1" stopIfTrue="1">
       <formula>AND(ISNUMBER(B28),B28&lt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" dxfId="0" stopIfTrue="1">
+    <cfRule type="expression" priority="13" dxfId="0" stopIfTrue="1">
       <formula>AND(ISNUMBER(B28),B28&gt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10370,7 +10619,7 @@
       </c>
       <c r="B14" s="48">
         <f>IFERROR(IF('1. Inversión Inicial'!$B$51="","",'1. Inversión Inicial'!$B$51),"")</f>
-        <v>201899.40000000002</v>
+        <v>201717.90000000002</v>
       </c>
       <c r="C14" s="44" t="inlineStr">
         <is>
@@ -10391,7 +10640,7 @@
       </c>
       <c r="B15" s="42">
         <f>IFERROR(B12-B14,"")</f>
-        <v>1100.5999999999767</v>
+        <v>1282.0999999999767</v>
       </c>
       <c r="C15" s="41" t="inlineStr">
         <is>
@@ -10412,7 +10661,7 @@
       </c>
       <c r="B16" s="46">
         <f>IFERROR(B15/B14,"")</f>
-        <v>0.0054512296718067345</v>
+        <v>0.006355905945877766</v>
       </c>
       <c r="C16" s="44" t="inlineStr">
         <is>
@@ -10453,7 +10702,7 @@
       </c>
       <c r="B18" s="48">
         <f>IFERROR(MAX(0,B14-B12+B7),"")</f>
-        <v>126899.40000000002</v>
+        <v>126717.90000000002</v>
       </c>
       <c r="C18" s="44" t="inlineStr">
         <is>
@@ -10538,7 +10787,7 @@
         </is>
       </c>
       <c r="B23" s="55">
-        <f>IFERROR(IF('0. Supuestos'!$B$34&gt;='0. Supuestos'!$B$33,0,'0. Supuestos'!$B$34),"")</f>
+        <f>IFERROR(IF(OR('0. Supuestos'!$B$34="",'0. Supuestos'!$B$33=""),"",IF('0. Supuestos'!$B$34&gt;='0. Supuestos'!$B$33,0,'0. Supuestos'!$B$34)),"")</f>
         <v>1.0</v>
       </c>
       <c r="C23" s="44" t="inlineStr">
@@ -10620,7 +10869,7 @@
       </c>
       <c r="G26" s="41" t="inlineStr">
         <is>
-          <t>Flujo de caja disponible</t>
+          <t>Flujo disponible para la deuda (después de impuestos; del año 4 en adelante, el del año 3 mantenido)</t>
         </is>
       </c>
       <c r="H26" s="41" t="inlineStr">
@@ -10654,12 +10903,12 @@
         <v>128000.0</v>
       </c>
       <c r="G27" s="56">
-        <f>IFERROR(IF(E27="","",'2. P&amp;L 3 Años'!$B$43+'2. P&amp;L 3 Años'!$B$38+'2. P&amp;L 3 Años'!$B$39),"")</f>
-        <v>73642.39999999997</v>
+        <f>IFERROR(IF(E27="","",'2. P&amp;L 3 Años'!$B$43-'2. P&amp;L 3 Años'!$B$48+'2. P&amp;L 3 Años'!$B$38+'2. P&amp;L 3 Años'!$B$39),"")</f>
+        <v>65062.18999999997</v>
       </c>
       <c r="H27" s="78">
         <f>IFERROR(IF(OR(E27="",E27=0),"",G27/E27),"")</f>
-        <v>9.588854166666662</v>
+        <v>8.471639322916664</v>
       </c>
     </row>
     <row r="28">
@@ -10687,12 +10936,12 @@
         <v>109649.5835552134</v>
       </c>
       <c r="G28" s="56">
-        <f>IFERROR(IF(E28="","",'2. P&amp;L 3 Años'!$C$43+'2. P&amp;L 3 Años'!$C$38+'2. P&amp;L 3 Años'!$C$39),"")</f>
-        <v>98560.56</v>
+        <f>IFERROR(IF(E28="","",'2. P&amp;L 3 Años'!$C$43-'2. P&amp;L 3 Años'!$C$48+'2. P&amp;L 3 Años'!$C$38+'2. P&amp;L 3 Años'!$C$39),"")</f>
+        <v>86242.626</v>
       </c>
       <c r="H28" s="78">
         <f>IFERROR(IF(OR(E28="",E28=0),"",G28/E28),"")</f>
-        <v>3.7863612443180794</v>
+        <v>3.31314814662801</v>
       </c>
     </row>
     <row r="29">
@@ -10720,12 +10969,12 @@
         <v>90198.1421237396</v>
       </c>
       <c r="G29" s="56">
-        <f>IFERROR(IF(E29="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
-        <v>112966.54559999998</v>
+        <f>IFERROR(IF(E29="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <v>88559.90295332819</v>
       </c>
       <c r="H29" s="78">
         <f>IFERROR(IF(OR(E29="",E29=0),"",G29/E29),"")</f>
-        <v>4.339790177372481</v>
+        <v>3.402170039852169</v>
       </c>
     </row>
     <row r="30">
@@ -10753,12 +11002,12 @@
         <v>69579.61420637737</v>
       </c>
       <c r="G30" s="56">
-        <f>IFERROR(IF(E30="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
-        <v>112966.54559999998</v>
+        <f>IFERROR(IF(E30="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <v>88559.90295332819</v>
       </c>
       <c r="H30" s="78">
         <f>IFERROR(IF(OR(E30="",E30=0),"",G30/E30),"")</f>
-        <v>4.339790177372481</v>
+        <v>3.402170039852169</v>
       </c>
     </row>
     <row r="31">
@@ -10786,12 +11035,12 @@
         <v>47723.97461397341</v>
       </c>
       <c r="G31" s="56">
-        <f>IFERROR(IF(E31="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
-        <v>112966.54559999998</v>
+        <f>IFERROR(IF(E31="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <v>88559.90295332819</v>
       </c>
       <c r="H31" s="78">
         <f>IFERROR(IF(OR(E31="",E31=0),"",G31/E31),"")</f>
-        <v>4.339790177372481</v>
+        <v>3.402170039852169</v>
       </c>
     </row>
     <row r="32">
@@ -10819,12 +11068,12 @@
         <v>24556.996646025214</v>
       </c>
       <c r="G32" s="56">
-        <f>IFERROR(IF(E32="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
-        <v>112966.54559999998</v>
+        <f>IFERROR(IF(E32="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <v>88559.90295332819</v>
       </c>
       <c r="H32" s="78">
         <f>IFERROR(IF(OR(E32="",E32=0),"",G32/E32),"")</f>
-        <v>4.339790177372481</v>
+        <v>3.402170039852169</v>
       </c>
     </row>
     <row r="33">
@@ -10852,12 +11101,12 @@
         <v>1.2369127944111824e-10</v>
       </c>
       <c r="G33" s="56">
-        <f>IFERROR(IF(E33="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
-        <v>112966.54559999998</v>
+        <f>IFERROR(IF(E33="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <v>88559.90295332819</v>
       </c>
       <c r="H33" s="78">
         <f>IFERROR(IF(OR(E33="",E33=0),"",G33/E33),"")</f>
-        <v>4.339790177372481</v>
+        <v>3.402170039852169</v>
       </c>
     </row>
     <row r="34">
@@ -10885,7 +11134,7 @@
         <v/>
       </c>
       <c r="G34" s="56">
-        <f>IFERROR(IF(E34="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E34="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H34" s="78">
@@ -10918,7 +11167,7 @@
         <v/>
       </c>
       <c r="G35" s="56">
-        <f>IFERROR(IF(E35="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E35="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H35" s="78">
@@ -10951,7 +11200,7 @@
         <v/>
       </c>
       <c r="G36" s="56">
-        <f>IFERROR(IF(E36="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E36="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H36" s="78">
@@ -10984,7 +11233,7 @@
         <v/>
       </c>
       <c r="G37" s="56">
-        <f>IFERROR(IF(E37="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E37="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H37" s="78">
@@ -11017,7 +11266,7 @@
         <v/>
       </c>
       <c r="G38" s="56">
-        <f>IFERROR(IF(E38="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E38="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H38" s="78">
@@ -11050,7 +11299,7 @@
         <v/>
       </c>
       <c r="G39" s="56">
-        <f>IFERROR(IF(E39="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E39="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H39" s="78">
@@ -11083,7 +11332,7 @@
         <v/>
       </c>
       <c r="G40" s="56">
-        <f>IFERROR(IF(E40="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E40="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H40" s="78">
@@ -11116,7 +11365,7 @@
         <v/>
       </c>
       <c r="G41" s="56">
-        <f>IFERROR(IF(E41="","",'2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
+        <f>IFERROR(IF(E41="","",'2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+'2. P&amp;L 3 Años'!$D$39),"")</f>
         <v/>
       </c>
       <c r="H41" s="78">
@@ -11288,8 +11537,8 @@
         </is>
       </c>
       <c r="B51" s="78">
-        <f>IFERROR(('2. P&amp;L 3 Años'!$B$43+'2. P&amp;L 3 Años'!$B$38+B44)/(B44+B45),"")</f>
-        <v>9.588854166666662</v>
+        <f>IFERROR(('2. P&amp;L 3 Años'!$B$43-'2. P&amp;L 3 Años'!$B$48+'2. P&amp;L 3 Años'!$B$38+B44)/(B44+B45),"")</f>
+        <v>8.471639322916664</v>
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
@@ -11309,8 +11558,8 @@
         </is>
       </c>
       <c r="B52" s="78">
-        <f>IFERROR(('2. P&amp;L 3 Años'!$C$43+'2. P&amp;L 3 Años'!$C$38+B46)/(B46+B47),"")</f>
-        <v>3.7863612443180794</v>
+        <f>IFERROR(('2. P&amp;L 3 Años'!$C$43-'2. P&amp;L 3 Años'!$C$48+'2. P&amp;L 3 Años'!$C$38+B46)/(B46+B47),"")</f>
+        <v>3.31314814662801</v>
       </c>
       <c r="C52" s="44" t="n"/>
       <c r="D52" s="44" t="n"/>
@@ -11326,8 +11575,8 @@
         </is>
       </c>
       <c r="B53" s="78">
-        <f>IFERROR(('2. P&amp;L 3 Años'!$D$43+'2. P&amp;L 3 Años'!$D$38+B48)/(B48+B49),"")</f>
-        <v>4.339790177372481</v>
+        <f>IFERROR(('2. P&amp;L 3 Años'!$D$43-'2. P&amp;L 3 Años'!$D$48+'2. P&amp;L 3 Años'!$D$38+B48)/(B48+B49),"")</f>
+        <v>3.402170039852169</v>
       </c>
       <c r="C53" s="44" t="n"/>
       <c r="D53" s="44" t="n"/>
@@ -11344,11 +11593,11 @@
       </c>
       <c r="B54" s="70">
         <f>IFERROR(IF(COUNT(H27:H41)=0,"",MIN(H27:H41)),"")</f>
-        <v>3.7863612443180794</v>
+        <v>3.31314814662801</v>
       </c>
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>El peor año de los que dura el préstamo, no el mejor de los tres que proyecta el P&amp;L. Es el número que decide una operación</t>
+          <t>El peor año de los que dura el préstamo, no el mejor de los tres que proyecta el P&amp;L. Es el número que decide una operación. Ojo al alcance: los años 1 a 3 salen del P&amp;L y del año 4 en adelante el cuadro MANTIENE el flujo del año 3, así que el mínimo de esos años es una proyección sostenida, no un año calculado. El flujo va después de impuestos</t>
         </is>
       </c>
       <c r="D54" s="44" t="n"/>
@@ -11367,10 +11616,10 @@
       <c r="G55" s="44" t="n"/>
       <c r="H55" s="44" t="n"/>
     </row>
-    <row r="56" ht="150" customHeight="1">
+    <row r="56" ht="165" customHeight="1">
       <c r="A56" s="63" t="inlineStr">
         <is>
-          <t>El DSCR se calcula ANTES de la deuda: al resultado antes de impuestos se le devuelven la amortización contable y los intereses, y el resultado se divide entre lo que hay que pagar ese año. Por debajo del mínimo de la hoja de Supuestos, el negocio no genera para pagar el préstamo. En el cuadro, el flujo de caja disponible de los años 4 en adelante se mantiene en el del año 3: el P&amp;L sólo proyecta tres, y aquí no se inventa un crecimiento que no está calculado.</t>
+          <t>El DSCR se calcula ANTES de la deuda y DESPUÉS de impuestos: al resultado antes de impuestos se le resta el Impuesto de Sociedades y se le devuelven la amortización contable y los intereses; el resultado se divide entre lo que hay que pagar ese año. Por debajo del mínimo de la hoja de Supuestos, el negocio no genera para pagar el préstamo. En el cuadro, el flujo de caja disponible de los años 4 en adelante se mantiene en el del año 3: el P&amp;L sólo proyecta tres, y aquí no se inventa un crecimiento que no está calculado.</t>
         </is>
       </c>
       <c r="B56" s="44" t="n"/>
